--- a/log/HELIOS_Distribuzione_task.xlsx
+++ b/log/HELIOS_Distribuzione_task.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-GO'!$A$4:$V$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-GO'!$A$4:$V$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Pre-GO'!I5:I25,A4)</f>
+        <f>COUNTIF('Pre-GO'!I5:I26,A4)</f>
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIF('Post-GO'!I5:I53,A4)</f>
+        <f>COUNTIF('Post-GO'!I5:I58,A4)</f>
         <v/>
       </c>
       <c r="D4">
@@ -654,11 +654,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Pre-GO'!I5:I25,A5)</f>
+        <f>COUNTIF('Pre-GO'!I5:I26,A5)</f>
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIF('Post-GO'!I5:I53,A5)</f>
+        <f>COUNTIF('Post-GO'!I5:I58,A5)</f>
         <v/>
       </c>
       <c r="D5">
@@ -673,11 +673,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Pre-GO'!I5:I25,A6)</f>
+        <f>COUNTIF('Pre-GO'!I5:I26,A6)</f>
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIF('Post-GO'!I5:I53,A6)</f>
+        <f>COUNTIF('Post-GO'!I5:I58,A6)</f>
         <v/>
       </c>
       <c r="D6">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Pre-GO'!I5:I25,A7)</f>
+        <f>COUNTIF('Pre-GO'!I5:I26,A7)</f>
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIF('Post-GO'!I5:I53,A7)</f>
+        <f>COUNTIF('Post-GO'!I5:I58,A7)</f>
         <v/>
       </c>
       <c r="D7">
@@ -711,11 +711,11 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF('Pre-GO'!I5:I25,A8)</f>
+        <f>COUNTIF('Pre-GO'!I5:I26,A8)</f>
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIF('Post-GO'!I5:I53,A8)</f>
+        <f>COUNTIF('Post-GO'!I5:I58,A8)</f>
         <v/>
       </c>
       <c r="D8">
@@ -795,11 +795,11 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF('Pre-GO'!K5:K25,A14)</f>
+        <f>COUNTIF('Pre-GO'!K5:K26,A14)</f>
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIF('Post-GO'!K5:K53,A14)</f>
+        <f>COUNTIF('Post-GO'!K5:K58,A14)</f>
         <v/>
       </c>
       <c r="D14">
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS('Pre-GO'!K5:K25,A14,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!K5:K53,A14,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A14,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -818,11 +818,11 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF('Pre-GO'!K5:K25,A15)</f>
+        <f>COUNTIF('Pre-GO'!K5:K26,A15)</f>
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIF('Post-GO'!K5:K53,A15)</f>
+        <f>COUNTIF('Post-GO'!K5:K58,A15)</f>
         <v/>
       </c>
       <c r="D15">
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS('Pre-GO'!K5:K25,A15,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!K5:K53,A15,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A15,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -841,11 +841,11 @@
         </is>
       </c>
       <c r="B16">
-        <f>COUNTIF('Pre-GO'!K5:K25,A16)</f>
+        <f>COUNTIF('Pre-GO'!K5:K26,A16)</f>
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIF('Post-GO'!K5:K53,A16)</f>
+        <f>COUNTIF('Post-GO'!K5:K58,A16)</f>
         <v/>
       </c>
       <c r="D16">
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS('Pre-GO'!K5:K25,A16,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!K5:K53,A16,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A16,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="B17">
-        <f>COUNTIF('Pre-GO'!K5:K25,A17)</f>
+        <f>COUNTIF('Pre-GO'!K5:K26,A17)</f>
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIF('Post-GO'!K5:K53,A17)</f>
+        <f>COUNTIF('Post-GO'!K5:K58,A17)</f>
         <v/>
       </c>
       <c r="D17">
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS('Pre-GO'!K5:K25,A17,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!K5:K53,A17,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A17,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-00")+COUNTIF('Post-GO'!D5:D53,"PK-00")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D58,"PK-00")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-00",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-00",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-00",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-00",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-00",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-00",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="B22">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-01")+COUNTIF('Post-GO'!D5:D53,"PK-01")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D58,"PK-01")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-01",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-01",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-01",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-01",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-01",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-01",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B23">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-02")+COUNTIF('Post-GO'!D5:D53,"PK-02")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D58,"PK-02")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-02",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-02",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-02",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-02",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-02",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-02",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B24">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-03")+COUNTIF('Post-GO'!D5:D53,"PK-03")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D58,"PK-03")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-03",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-03",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-03",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-03",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-03",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-03",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B25">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-04")+COUNTIF('Post-GO'!D5:D53,"PK-04")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D58,"PK-04")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-04",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-04",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-04",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-04",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-04",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-04",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B26">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-05")+COUNTIF('Post-GO'!D5:D53,"PK-05")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D58,"PK-05")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-05",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-05",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-05",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="B27">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-05b")+COUNTIF('Post-GO'!D5:D53,"PK-05b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D58,"PK-05b")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05b",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-05b",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05b",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-05b",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-05b",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-05b",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="B28">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-06")+COUNTIF('Post-GO'!D5:D53,"PK-06")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D58,"PK-06")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-06",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-06",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-06",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-06",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-06",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-06",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B29">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-07")+COUNTIF('Post-GO'!D5:D53,"PK-07")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D58,"PK-07")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-07",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-07",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-07",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-07",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-07",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-07",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -1158,23 +1158,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PK-08 · Runner con allowlist e policy permessi</t>
+          <t>PK-07b · Configurazione locale non versionata</t>
         </is>
       </c>
       <c r="B30">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-08")+COUNTIF('Post-GO'!D5:D53,"PK-08")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D58,"PK-07b")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-08",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-08",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-08",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-08",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-08",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-08",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -1185,23 +1185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PK-09 · Ruoli PoC (analyst, developer, reviewer)</t>
+          <t>PK-08 · Runner con allowlist e policy permessi</t>
         </is>
       </c>
       <c r="B31">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-09")+COUNTIF('Post-GO'!D5:D53,"PK-09")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D58,"PK-08")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-09",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-09",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-09",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-09",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-09",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-09",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -1212,23 +1212,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PK-10 · Gate umano meccanico sul PLAN</t>
+          <t>PK-09 · Ruoli PoC (analyst, developer, reviewer)</t>
         </is>
       </c>
       <c r="B32">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-10")+COUNTIF('Post-GO'!D5:D53,"PK-10")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D58,"PK-09")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-10",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-10",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-10",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-10",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-10",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-10",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -1239,23 +1239,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PK-11 · Prova del plugin Claude Code (V13/V14)</t>
+          <t>PK-10 · Gate umano meccanico sul PLAN</t>
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-11")+COUNTIF('Post-GO'!D5:D53,"PK-11")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D58,"PK-10")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-11",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-11",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-11",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-11",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-11",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-11",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -1266,23 +1266,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PK-12 · Asset ECC portato + A/B</t>
+          <t>PK-11 · Prova del plugin Claude Code (V13/V14)</t>
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-12")+COUNTIF('Post-GO'!D5:D53,"PK-12")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D58,"PK-11")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-12",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-12",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-12",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-12",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-12",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-12",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -1293,23 +1293,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PK-13 · Rapporto go/no-go (compila NARO, decide il SUPERVISORE)</t>
+          <t>PK-12 · Asset ECC portato + A/B</t>
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-13")+COUNTIF('Post-GO'!D5:D53,"PK-13")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D58,"PK-12")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-13",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-13",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-13",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-13",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-13",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-13",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -1320,23 +1320,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PK-14 · Contratti della catena e skill runner</t>
+          <t>PK-13 · Rapporto go/no-go (compila NARO, decide il SUPERVISORE)</t>
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-14")+COUNTIF('Post-GO'!D5:D53,"PK-14")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D58,"PK-13")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-14",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-14",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-14",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-14",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-14",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-14",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -1347,23 +1347,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PK-15 · Scheduler e regole comuni dei ruoli</t>
+          <t>PK-14 · Contratti della catena e skill runner</t>
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-15")+COUNTIF('Post-GO'!D5:D53,"PK-15")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D58,"PK-14")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-15",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-15",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-15",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-15",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-15",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-15",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -1374,23 +1374,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PK-16 · Porting asset ECC</t>
+          <t>PK-15 · Scheduler e regole comuni dei ruoli</t>
         </is>
       </c>
       <c r="B38">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-16")+COUNTIF('Post-GO'!D5:D53,"PK-16")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D58,"PK-15")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-16",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-16",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-16",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-16",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-16",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-16",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F38" s="5">
@@ -1401,23 +1401,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PK-17 · Ruoli di sviluppo</t>
+          <t>PK-16 · Porting asset ECC</t>
         </is>
       </c>
       <c r="B39">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-17")+COUNTIF('Post-GO'!D5:D53,"PK-17")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D58,"PK-16")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-17",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-17",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-17",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-17",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-17",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-17",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F39" s="5">
@@ -1428,23 +1428,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PK-18 · Ruoli di controllo</t>
+          <t>PK-17 · Ruoli di sviluppo</t>
         </is>
       </c>
       <c r="B40">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-18")+COUNTIF('Post-GO'!D5:D53,"PK-18")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D58,"PK-17")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-18",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-18",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-18",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-18",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-18",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-18",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F40" s="5">
@@ -1455,23 +1455,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PK-19 · Workflow core e permessi tool</t>
+          <t>PK-18 · Ruoli di controllo</t>
         </is>
       </c>
       <c r="B41">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-19")+COUNTIF('Post-GO'!D5:D53,"PK-19")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D58,"PK-18")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-19",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-19",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-19",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-19",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-19",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-19",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F41" s="5">
@@ -1482,23 +1482,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PK-20 · Stato/eventi, report e gate di merge</t>
+          <t>PK-19 · Workflow core e permessi tool</t>
         </is>
       </c>
       <c r="B42">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-20")+COUNTIF('Post-GO'!D5:D53,"PK-20")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D58,"PK-19")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-20",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-20",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-20",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-20",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-20",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-20",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F42" s="5">
@@ -1509,23 +1509,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
+          <t>PK-20 · Stato/eventi, report e gate di merge</t>
         </is>
       </c>
       <c r="B43">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-21")+COUNTIF('Post-GO'!D5:D53,"PK-21")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D58,"PK-20")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-21",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-21",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-21",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-21",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-21",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-21",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F43" s="5">
@@ -1536,23 +1536,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
+          <t>PK-19b · Modalità non presidiata: motore e allow-list dei ruoli</t>
         </is>
       </c>
       <c r="B44">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-22")+COUNTIF('Post-GO'!D5:D53,"PK-22")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D58,"PK-19b")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-22",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-22",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-22",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-22",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-22",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-22",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F44" s="5">
@@ -1563,23 +1563,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
+          <t>PK-20b · Registro delle decisioni autonome e report notturno</t>
         </is>
       </c>
       <c r="B45">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-23")+COUNTIF('Post-GO'!D5:D53,"PK-23")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D58,"PK-20b")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-23",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-23",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-23",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-23",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-23",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-23",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F45" s="5">
@@ -1590,23 +1590,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
+          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="B46">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-24")+COUNTIF('Post-GO'!D5:D53,"PK-24")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D58,"PK-21")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-24",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-24",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-24",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-24",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-24",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-24",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F46" s="5">
@@ -1617,23 +1617,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PK-25 · API loopback e read model</t>
+          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="B47">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-25")+COUNTIF('Post-GO'!D5:D53,"PK-25")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D58,"PK-22")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-25",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-25",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-25",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-25",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-25",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-25",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F47" s="5">
@@ -1644,23 +1644,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="B48">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-26")+COUNTIF('Post-GO'!D5:D53,"PK-26")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D58,"PK-23")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-26",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-26",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-26",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-26",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-26",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-26",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F48" s="5">
@@ -1671,23 +1671,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PK-27 · Scenari E2E V1–V24</t>
+          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="B49">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-27")+COUNTIF('Post-GO'!D5:D53,"PK-27")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D58,"PK-24")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-27",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-27",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-27",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-27",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-27",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-27",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F49" s="5">
@@ -1698,23 +1698,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PK-28 · README plugin e manuali</t>
+          <t>PK-25 · API loopback e read model</t>
         </is>
       </c>
       <c r="B50">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-28")+COUNTIF('Post-GO'!D5:D53,"PK-28")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D58,"PK-25")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-28",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-28",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-28",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-28",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-28",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-28",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F50" s="5">
@@ -1725,23 +1725,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PK-29 · Hardening</t>
+          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-29")+COUNTIF('Post-GO'!D5:D53,"PK-29")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D58,"PK-26")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-29",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-29",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-29",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-29",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-29",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-29",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F51" s="5">
@@ -1752,23 +1752,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PK-30 · Rollout sul pilota</t>
+          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIF('Pre-GO'!D5:D25,"PK-30")+COUNTIF('Post-GO'!D5:D53,"PK-30")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D58,"PK-26b")</f>
         <v/>
       </c>
       <c r="C52">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-30",'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,"PK-30",'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D52">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-30",'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,"PK-30",'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E52">
-        <f>COUNTIFS('Pre-GO'!D5:D25,"PK-30",'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!D5:D53,"PK-30",'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F52" s="5">
@@ -1776,63 +1776,107 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PK-26c · Pannello di avvio del run non presidiato</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D58,"PK-26c")</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F53" s="5">
+        <f>IF(B53=0,0,C53/B53)</f>
+        <v/>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Avanzamento per fase</t>
-        </is>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PK-27 · Scenari E2E V1–V24</t>
+        </is>
+      </c>
+      <c r="B54">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D58,"PK-27")</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F54" s="5">
+        <f>IF(B54=0,0,C54/B54)</f>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Fase</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Fatti</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>In corso</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Da fare</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PK-28 · README plugin e manuali</t>
+        </is>
+      </c>
+      <c r="B55">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D58,"PK-28")</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F55" s="5">
+        <f>IF(B55=0,0,C55/B55)</f>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>1</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PK-29 · Hardening</t>
+        </is>
       </c>
       <c r="B56">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A56)+COUNTIFS('Post-GO'!A5:A53,$A56)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D58,"PK-29")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A56,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A56,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A56,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A56,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A56,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A56,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F56" s="5">
@@ -1841,23 +1885,25 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>2</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PK-30 · Rollout sul pilota</t>
+        </is>
       </c>
       <c r="B57">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A57)+COUNTIFS('Post-GO'!A5:A53,$A57)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D58,"PK-30")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A57,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A57,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A57,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A57,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A57,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A57,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F57" s="5">
@@ -1865,99 +1911,63 @@
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A58)+COUNTIFS('Post-GO'!A5:A53,$A58)</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A58,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A58,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A58,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A58,'Post-GO'!I5:I53,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A58,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A58,'Post-GO'!I5:I53,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F58" s="5">
-        <f>IF(B58=0,0,C58/B58)</f>
-        <v/>
-      </c>
-    </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A59)+COUNTIFS('Post-GO'!A5:A53,$A59)</f>
-        <v/>
-      </c>
-      <c r="C59">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A59,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A59,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D59">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A59,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A59,'Post-GO'!I5:I53,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E59">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A59,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A59,'Post-GO'!I5:I53,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F59" s="5">
-        <f>IF(B59=0,0,C59/B59)</f>
-        <v/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Avanzamento per fase</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A60)+COUNTIFS('Post-GO'!A5:A53,$A60)</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A60,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A60,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A60,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A60,'Post-GO'!I5:I53,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A60,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A60,'Post-GO'!I5:I53,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F60" s="5">
-        <f>IF(B60=0,0,C60/B60)</f>
-        <v/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Fatti</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>In corso</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B61">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A61)+COUNTIFS('Post-GO'!A5:A53,$A61)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A61)+COUNTIFS('Post-GO'!A5:A58,$A61)</f>
         <v/>
       </c>
       <c r="C61">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A61,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A61,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D61">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A61,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A61,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E61">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A61,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A61,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F61" s="5">
@@ -1967,22 +1977,22 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B62">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A62)+COUNTIFS('Post-GO'!A5:A53,$A62)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A62)+COUNTIFS('Post-GO'!A5:A58,$A62)</f>
         <v/>
       </c>
       <c r="C62">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A62,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A62,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D62">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A62,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A62,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E62">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A62,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A62,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F62" s="5">
@@ -1992,22 +2002,22 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B63">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A63)+COUNTIFS('Post-GO'!A5:A53,$A63)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63)+COUNTIFS('Post-GO'!A5:A58,$A63)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A63,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A63,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D63">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A63,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A63,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E63">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A63,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A63,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F63" s="5">
@@ -2016,25 +2026,23 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A64" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="B64">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A64)+COUNTIFS('Post-GO'!A5:A53,$A64)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A58,$A64)</f>
         <v/>
       </c>
       <c r="C64">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A64,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A64,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D64">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A64,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A64,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E64">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A64,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A64,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F64" s="5">
@@ -2044,22 +2052,22 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A65)+COUNTIFS('Post-GO'!A5:A53,$A65)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A58,$A65)</f>
         <v/>
       </c>
       <c r="C65">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A65,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A65,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D65">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A65,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A65,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E65">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A65,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A65,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F65" s="5">
@@ -2069,22 +2077,22 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B66">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A66)+COUNTIFS('Post-GO'!A5:A53,$A66)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A58,$A66)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A66,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A66,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D66">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A66,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A66,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E66">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A66,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A66,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F66" s="5">
@@ -2094,22 +2102,22 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B67">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A67)+COUNTIFS('Post-GO'!A5:A53,$A67)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A58,$A67)</f>
         <v/>
       </c>
       <c r="C67">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A67,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A67,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D67">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A67,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A67,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E67">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A67,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A67,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F67" s="5">
@@ -2119,26 +2127,153 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B68">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A68)+COUNTIFS('Post-GO'!A5:A53,$A68)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A58,$A68)</f>
         <v/>
       </c>
       <c r="C68">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A68,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!A5:A53,$A68,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="D68">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A68,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!A5:A53,$A68,'Post-GO'!I5:I53,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"In corso")</f>
         <v/>
       </c>
       <c r="E68">
-        <f>COUNTIFS('Pre-GO'!A5:A25,$A68,'Pre-GO'!I5:I25,"Da fare")+COUNTIFS('Post-GO'!A5:A53,$A68,'Post-GO'!I5:I53,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"Da fare")</f>
         <v/>
       </c>
       <c r="F68" s="5">
         <f>IF(B68=0,0,C68/B68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="B69">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A58,$A69)</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F69" s="5">
+        <f>IF(B69=0,0,C69/B69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A58,$A70)</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F70" s="5">
+        <f>IF(B70=0,0,C70/B70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A58,$A71)</f>
+        <v/>
+      </c>
+      <c r="C71">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D71">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E71">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F71" s="5">
+        <f>IF(B71=0,0,C71/B71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A58,$A72)</f>
+        <v/>
+      </c>
+      <c r="C72">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F72" s="5">
+        <f>IF(B72=0,0,C72/B72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A58,$A73)</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D73">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F73" s="5">
+        <f>IF(B73=0,0,C73/B73)</f>
         <v/>
       </c>
     </row>
@@ -2155,7 +2290,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F52">
+  <conditionalFormatting sqref="F21:F57">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2164,7 +2299,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F56:F68">
+  <conditionalFormatting sqref="F61:F73">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2184,7 +2319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2225,11 +2360,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(I5:I25,"Fatto")/COUNTA(C5:C25)</f>
+        <f>COUNTIF(I5:I26,"Fatto")/COUNTA(C5:C26)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(I5:I25,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C25)&amp;" task · "&amp;COUNTIF(I5:I25,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I25,"Bloccato")&amp;" bloccati"</f>
+        <f>COUNTIF(I5:I26,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C26)&amp;" task · "&amp;COUNTIF(I5:I26,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I26,"Bloccato")&amp;" bloccati"</f>
         <v/>
       </c>
     </row>
@@ -3549,39 +3684,39 @@
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-309</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>PK-08</t>
+          <t>PK-07b</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Runner con allowlist</t>
+          <t>Configurazione locale (`helios.local.json`)</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>`agents/runner/`</t>
+          <t>**Fase 3.** Modulo di bootstrap condiviso (non solo dashboard), catena `HELIOS_CONFIG` → repo → utente, esempio versionato, `.gitignore`, `helios doctor`</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Eseguire solo operazioni ammesse, senza rete, con log hashato, senza commit/push</t>
+          <t>Evitare che chi clona HELIOS erediti i percorsi e le configurazioni di un altro</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-103 [P]</t>
+          <t>H-301, H-303</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -3612,23 +3747,27 @@
       </c>
       <c r="P19" s="10" t="n"/>
       <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="inlineStr"/>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>Richiesta SUPERVISORE 2026-10-30; attua C20</t>
+        </is>
+      </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="10" t="inlineStr">
         <is>
-          <t>T-401, T-402</t>
+          <t>T-309</t>
         </is>
       </c>
       <c r="U19" s="10" t="inlineStr">
         <is>
-          <t>H-303</t>
+          <t>H-301, H-303</t>
         </is>
       </c>
       <c r="V19" s="10" t="inlineStr">
         <is>
-          <t>agents/runner/</t>
+          <t>.gitignore</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3780,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>H-404</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -3651,22 +3790,22 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Policy permessi con pavimento hard-deny</t>
+          <t>Runner con allowlist</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>`agents/policy/policy.json`, `floor.json`</t>
+          <t>`agents/runner/`</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Impedire che permessi pericolosi siano rimovibili</t>
+          <t>Eseguire solo operazioni ammesse, senza rete, con log hashato, senza commit/push</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>H-303, H-103 [P]</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -3703,17 +3842,17 @@
       </c>
       <c r="T20" s="10" t="inlineStr">
         <is>
-          <t>T-405</t>
+          <t>T-401, T-402</t>
         </is>
       </c>
       <c r="U20" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-303</t>
         </is>
       </c>
       <c r="V20" s="10" t="inlineStr">
         <is>
-          <t>agents/policy/policy.json, floor.json</t>
+          <t>agents/runner/</t>
         </is>
       </c>
     </row>
@@ -3726,32 +3865,32 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>H-402</t>
+          <t>H-404</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>PK-09</t>
+          <t>PK-08</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Ruoli PoC</t>
+          <t>Policy permessi con pavimento hard-deny</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>`agents/roles/*.md`</t>
+          <t>`agents/policy/policy.json`, `floor.json`</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>analyst, developer, reviewer con `tools:` senza Bash libero</t>
+          <t>Impedire che permessi pericolosi siano rimovibili</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-303 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -3788,17 +3927,17 @@
       </c>
       <c r="T21" s="10" t="inlineStr">
         <is>
-          <t>T-403</t>
+          <t>T-405</t>
         </is>
       </c>
       <c r="U21" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-404</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V21" s="10" t="inlineStr">
         <is>
-          <t>agents/roles/*.md</t>
+          <t>agents/policy/policy.json, floor.json</t>
         </is>
       </c>
     </row>
@@ -3811,32 +3950,32 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>H-403</t>
+          <t>H-402</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>PK-10</t>
+          <t>PK-09</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Gate umano meccanico sul PLAN</t>
+          <t>Ruoli PoC</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>`agents/workflow/gate.py`</t>
+          <t>`agents/roles/*.md`</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Nessun avanzamento senza approvazione umana</t>
+          <t>analyst, developer, reviewer con `tools:` senza Bash libero</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>H-303 [P]</t>
+          <t>H-404, H-303 [P]</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -3850,7 +3989,7 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr"/>
@@ -3873,17 +4012,17 @@
       </c>
       <c r="T22" s="10" t="inlineStr">
         <is>
-          <t>T-404</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="U22" s="10" t="inlineStr">
         <is>
-          <t>H-303</t>
+          <t>H-303, H-404</t>
         </is>
       </c>
       <c r="V22" s="10" t="inlineStr">
         <is>
-          <t>agents/workflow/gate.py</t>
+          <t>agents/roles/*.md</t>
         </is>
       </c>
     </row>
@@ -3896,32 +4035,32 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-403</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>PK-11</t>
+          <t>PK-10</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Prova del plugin Claude Code</t>
+          <t>Gate umano meccanico sul PLAN</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>`agents/plugin/`</t>
+          <t>`agents/workflow/gate.py`</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Dimostrare registrazione e invocazione reale del workflow in sessione Claude Code (V13/V14)</t>
+          <t>Nessun avanzamento senza approvazione umana</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>H-103, H-303 [P]</t>
+          <t>H-303 [P]</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -3958,7 +4097,7 @@
       </c>
       <c r="T23" s="10" t="inlineStr">
         <is>
-          <t>T-407</t>
+          <t>T-404</t>
         </is>
       </c>
       <c r="U23" s="10" t="inlineStr">
@@ -3968,7 +4107,7 @@
       </c>
       <c r="V23" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/, poc-report.md</t>
+          <t>agents/workflow/gate.py</t>
         </is>
       </c>
     </row>
@@ -3981,32 +4120,32 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>H-405</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>PK-12</t>
+          <t>PK-11</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Asset ECC portato + A/B</t>
+          <t>Prova del plugin Claude Code</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>T-406. Asset = `code-reviewer` ECC (Q-4 chiusa, 2026-10-29). **[N]** Metrica e baseline da definire (Q-6)</t>
+          <t>`agents/plugin/`</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Portare un asset `ecc-*` e confrontarlo con la baseline</t>
+          <t>Dimostrare registrazione e invocazione reale del workflow in sessione Claude Code (V13/V14)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>H-402, H-401</t>
+          <t>H-103, H-303 [P]</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -4020,7 +4159,7 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr"/>
@@ -4043,17 +4182,17 @@
       </c>
       <c r="T24" s="10" t="inlineStr">
         <is>
-          <t>T-406</t>
+          <t>T-407</t>
         </is>
       </c>
       <c r="U24" s="10" t="inlineStr">
         <is>
-          <t>H-401, H-402</t>
+          <t>H-303</t>
         </is>
       </c>
       <c r="V24" s="10" t="inlineStr">
         <is>
-          <t>tests/test_ab_metrics.py, [N] cartella dell'asset ecc-code-reviewer</t>
+          <t>agents/plugin/, poc-report.md</t>
         </is>
       </c>
     </row>
@@ -4066,32 +4205,32 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>H-406</t>
+          <t>H-405</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>PK-13</t>
+          <t>PK-12</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Rapporto go/no-go</t>
+          <t>Asset ECC portato + A/B</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>`docs/poc-report.md`. **PUNTO DI DECISIONE del SUPERVISORE (GO / NO-GO / piano B), non fine del piano**: Fasi 5–12 dipendono da questo esito</t>
+          <t>T-406. Asset = `code-reviewer` ECC (Q-4 chiusa, 2026-10-29). **[N]** Metrica e baseline da definire (Q-6)</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Giudicare i 10 criteri di R05 §5</t>
+          <t>Portare un asset `ecc-*` e confrontarlo con la baseline</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>H-401…H-405, H-407</t>
+          <t>H-402, H-401</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -4105,7 +4244,7 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr"/>
@@ -4128,26 +4267,111 @@
       </c>
       <c r="T25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-406</t>
         </is>
       </c>
       <c r="U25" s="10" t="inlineStr">
         <is>
+          <t>H-401, H-402</t>
+        </is>
+      </c>
+      <c r="V25" s="10" t="inlineStr">
+        <is>
+          <t>tests/test_ab_metrics.py, [N] cartella dell'asset ecc-code-reviewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>H-406</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>PK-13</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Rapporto go/no-go</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>`docs/poc-report.md`. **PUNTO DI DECISIONE del SUPERVISORE (GO / NO-GO / piano B), non fine del piano**: Fasi 5–12 dipendono da questo esito</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Giudicare i 10 criteri di R05 §5</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>H-401…H-405, H-407</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J26" s="9">
+        <f>IF(I26="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="inlineStr"/>
+      <c r="S26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="10" t="inlineStr">
+        <is>
           <t>H-401, H-402, H-403, H-404, H-405, H-407</t>
         </is>
       </c>
-      <c r="V25" s="10" t="inlineStr">
+      <c r="V26" s="10" t="inlineStr">
         <is>
           <t>docs/poc-report.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V25"/>
+  <autoFilter ref="A4:V26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:S25">
+  <conditionalFormatting sqref="A5:S26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($S5=1,$I5&lt;&gt;"Fatto")</formula>
     </cfRule>
@@ -4155,7 +4379,7 @@
       <formula>$I5="Fatto"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I25">
+  <conditionalFormatting sqref="I5:I26">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -4172,7 +4396,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K25">
+  <conditionalFormatting sqref="K5:K26">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
@@ -4183,7 +4407,7 @@
       <formula>"SUPERVISORE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S25">
+  <conditionalFormatting sqref="S5:S26">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4193,19 +4417,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="I5:I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Da fare,In corso,In review,Fatto,Bloccato"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NARO,SCIBETTA,SUPERVISORE,Da assegnare"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,M,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="S5:S26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -4221,7 +4445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4262,11 +4486,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(I5:I53,"Fatto")/COUNTA(C5:C53)</f>
+        <f>COUNTIF(I5:I58,"Fatto")/COUNTA(C5:C58)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(I5:I53,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C53)&amp;" task · "&amp;COUNTIF(I5:I53,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I53,"Bloccato")&amp;" bloccati"</f>
+        <f>COUNTIF(I5:I58,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C58)&amp;" task · "&amp;COUNTIF(I5:I58,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I58,"Bloccato")&amp;" bloccati"</f>
         <v/>
       </c>
     </row>
@@ -4387,7 +4611,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
@@ -4476,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
@@ -4565,7 +4789,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
@@ -4654,7 +4878,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -4743,7 +4967,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
@@ -4832,7 +5056,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -4921,7 +5145,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
@@ -5010,7 +5234,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -5099,7 +5323,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
@@ -5188,7 +5412,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
@@ -5277,7 +5501,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
@@ -5366,7 +5590,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
@@ -5455,7 +5679,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
@@ -5544,7 +5768,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
@@ -5633,7 +5857,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
@@ -5722,7 +5946,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
@@ -5811,7 +6035,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
@@ -5900,7 +6124,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
@@ -5989,7 +6213,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
@@ -6078,7 +6302,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
@@ -6167,7 +6391,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
@@ -6256,7 +6480,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
@@ -6345,7 +6569,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
@@ -6434,7 +6658,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
@@ -6523,7 +6747,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6612,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
@@ -6701,7 +6925,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6787,39 +7011,39 @@
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi post-task (prodotto)</t>
+          <t>Modalità non presidiata (UNATTENDED)</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6, gruppo E.** T-611</t>
+          <t>**Fase 7.** Estende H-707/H-708. Default decisi (Q-14): `stopOnQuestions` = `false`, `maxDurationMin` = 480, nessun reperibile. T-713, E2E-AUT-1, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
+          <t>Sezione `night` in `limits.json`, macchina a stati del run, parcheggio dei dipendenti, kill switch, dead-man switch</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-706, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -6833,7 +7057,7 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
@@ -6852,7 +7076,7 @@
       <c r="Q32" s="10" t="n"/>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003; richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S32" s="12" t="n">
@@ -6860,17 +7084,17 @@
       </c>
       <c r="T32" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-713, T-1, T-2</t>
         </is>
       </c>
       <c r="U32" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-706, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="V32" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
     </row>
@@ -6879,36 +7103,36 @@
         <v>7</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>H-702</t>
+          <t>H-715</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Installer `limet-agents.ps1/.sh`</t>
+          <t>Allow-list dei ruoli non presidiati</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-702</t>
+          <t>**Fase 7.** Applicata dal codice, non convenzione (Q-16). T-715, E2E-AUT-1</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>`init|update` idempotente, plugin facoltativo</t>
+          <t>Solo `developer`, `tester`, `runner`, `test-reader`, `reviewer`, `metrics-observer`; al turno di un ruolo escluso il task si parcheggia con motivazione</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -6922,7 +7146,7 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -6941,7 +7165,7 @@
       <c r="Q33" s="10" t="n"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §5</t>
         </is>
       </c>
       <c r="S33" s="12" t="n">
@@ -6949,17 +7173,17 @@
       </c>
       <c r="T33" s="10" t="inlineStr">
         <is>
-          <t>T-702</t>
+          <t>T-715, T-1</t>
         </is>
       </c>
       <c r="U33" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="V33" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
     </row>
@@ -6968,36 +7192,36 @@
         <v>7</v>
       </c>
       <c r="B34" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>H-712</t>
+          <t>H-714</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Modifiche documentali a LIMET M.1–M.9</t>
+          <t>Registro delle decisioni autonome</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7, gruppo F.** T-712</t>
+          <t>**Fase 7.** Estende H-709 (ALA R18). T-714, E2E-AUT-1</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
+          <t>Ogni decisione presa in autonomia registrata con evidenza e reversibilità; sezione «decisioni autonome» in `REPORT_NOTTURNO.md`</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
+          <t>H-709, H-713</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -7030,7 +7254,7 @@
       <c r="Q34" s="10" t="n"/>
       <c r="R34" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §8</t>
         </is>
       </c>
       <c r="S34" s="12" t="n">
@@ -7038,55 +7262,55 @@
       </c>
       <c r="T34" s="10" t="inlineStr">
         <is>
-          <t>T-712</t>
+          <t>T-714, T-1</t>
         </is>
       </c>
       <c r="U34" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-709, H-713</t>
         </is>
       </c>
       <c r="V34" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Analisi degli hook ECC</t>
+          <t>Valutazione rischi post-task (prodotto)</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
+          <t>**Fase 6, gruppo E.** T-611</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Decisione motivata per ognuno dei 27 hook</t>
+          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -7100,7 +7324,7 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr"/>
@@ -7119,7 +7343,7 @@
       <c r="Q35" s="10" t="n"/>
       <c r="R35" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO (o anticipo)</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S35" s="12" t="n">
@@ -7127,55 +7351,55 @@
       </c>
       <c r="T35" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="U35" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="V35" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B36" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>H-800b</t>
+          <t>H-702</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Replica sicura hook utili</t>
+          <t>Installer `limet-agents.ps1/.sh`</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** Test: da definire per hook replicato **[N]** (nessun T-xxx in IN §6)</t>
+          <t>**Fase 7.** T-702</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
+          <t>`init|update` idempotente, plugin facoltativo</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -7189,7 +7413,7 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr"/>
@@ -7216,55 +7440,55 @@
       </c>
       <c r="T36" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-702</t>
         </is>
       </c>
       <c r="U36" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V36" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B37" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>H-801</t>
+          <t>H-712</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Registro chiamate LLM (C05)</t>
+          <t>Modifiche documentali a LIMET M.1–M.9</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
+          <t>**Fase 7, gruppo F.** T-712</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Ogni chiamata LLM extra registrata</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -7278,7 +7502,7 @@
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr"/>
@@ -7305,17 +7529,17 @@
       </c>
       <c r="T37" s="10" t="inlineStr">
         <is>
-          <t>T-801</t>
+          <t>T-712</t>
         </is>
       </c>
       <c r="U37" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V37" s="10" t="inlineStr">
         <is>
-          <t>agents/policy/llm-registry.json</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
@@ -7324,11 +7548,11 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>H-802</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -7338,22 +7562,22 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Wrapper AgentShield</t>
+          <t>Analisi degli hook ECC</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
+          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
+          <t>Decisione motivata per ognuno dei 27 hook</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -7386,7 +7610,7 @@
       <c r="Q38" s="10" t="n"/>
       <c r="R38" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO (o anticipo)</t>
         </is>
       </c>
       <c r="S38" s="12" t="n">
@@ -7394,7 +7618,7 @@
       </c>
       <c r="T38" s="10" t="inlineStr">
         <is>
-          <t>T-802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U38" s="10" t="inlineStr">
@@ -7404,7 +7628,7 @@
       </c>
       <c r="V38" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>docs/ecc-hooks-analysis.md</t>
         </is>
       </c>
     </row>
@@ -7413,36 +7637,36 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>H-803</t>
+          <t>H-800b</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Setup KB `HLS_*`</t>
+          <t>Replica sicura hook utili</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
+          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
+          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204 [P]</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -7483,17 +7707,17 @@
       </c>
       <c r="T39" s="10" t="inlineStr">
         <is>
-          <t>T-803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U39" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="V39" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -7502,36 +7726,36 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>H-804</t>
+          <t>H-801</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Accesso agenti alla KB</t>
+          <t>Registro chiamate LLM (C05)</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-804</t>
+          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
+          <t>Ogni chiamata LLM extra registrata</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-611 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -7572,57 +7796,55 @@
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
-          <t>T-804</t>
+          <t>T-801</t>
         </is>
       </c>
       <c r="U40" s="10" t="inlineStr">
         <is>
-          <t>H-611, H-803</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V40" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>agents/policy/llm-registry.json</t>
         </is>
       </c>
     </row>
     <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A41" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B41" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-802</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>`api/` loopback e hardening</t>
+          <t>Wrapper AgentShield</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b01…T-8b04</t>
+          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
+          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -7663,57 +7885,55 @@
       </c>
       <c r="T41" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04</t>
+          <t>T-802</t>
         </is>
       </c>
       <c r="U41" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V41" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A42" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B42" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-803</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Read model derivato</t>
+          <t>Setup KB `HLS_*`</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b05</t>
+          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Cache rigenerabile, fonte unica (C27)</t>
+          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-202, H-204 [P]</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -7754,57 +7974,55 @@
       </c>
       <c r="T42" s="10" t="inlineStr">
         <is>
-          <t>T-8b05</t>
+          <t>T-803</t>
         </is>
       </c>
       <c r="U42" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-202, H-204</t>
         </is>
       </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A43" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B43" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>H-8b05</t>
+          <t>H-804</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Gate solo da sessione umana</t>
+          <t>Accesso agenti alla KB</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
+          <t>**Fase 8.** T-804</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git</t>
+          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-403</t>
+          <t>H-803, H-611 [P]</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -7845,17 +8063,17 @@
       </c>
       <c r="T43" s="10" t="inlineStr">
         <is>
-          <t>T-8b08</t>
+          <t>T-804</t>
         </is>
       </c>
       <c r="U43" s="10" t="inlineStr">
         <is>
-          <t>H-403, H-8b01</t>
+          <t>H-611, H-803</t>
         </is>
       </c>
       <c r="V43" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
@@ -7866,36 +8084,36 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>`ui/` viste</t>
+          <t>`api/` loopback e hardening</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b06</t>
+          <t>**Fase 8b.** T-8b01…T-8b04</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
+          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-303, H-401 [P]</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -7909,7 +8127,7 @@
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr"/>
@@ -7936,17 +8154,17 @@
       </c>
       <c r="T44" s="10" t="inlineStr">
         <is>
-          <t>T-8b06</t>
+          <t>T-8b01, T-8b04</t>
         </is>
       </c>
       <c r="U44" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-303, H-401</t>
         </is>
       </c>
       <c r="V44" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -7957,36 +8175,36 @@
         </is>
       </c>
       <c r="B45" s="9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>H-8b04</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Vista Permessi agenti</t>
+          <t>Read model derivato</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-405, T-8b07</t>
+          <t>**Fase 8b.** T-8b05</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Conferma, motivazione, audit, rollback</t>
+          <t>Cache rigenerabile, fonte unica (C27)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
@@ -8000,7 +8218,7 @@
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr"/>
@@ -8027,17 +8245,17 @@
       </c>
       <c r="T45" s="10" t="inlineStr">
         <is>
-          <t>T-405, T-8b07</t>
+          <t>T-8b05</t>
         </is>
       </c>
       <c r="U45" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="V45" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8048,36 +8266,36 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>H-8b06</t>
+          <t>H-8b05</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Grafica e accessibilità</t>
+          <t>Gate solo da sessione umana</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b09</t>
+          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
+          <t>La UI non esegue build/test/git</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b01, H-403</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -8091,7 +8309,7 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr"/>
@@ -8118,17 +8336,17 @@
       </c>
       <c r="T46" s="10" t="inlineStr">
         <is>
-          <t>T-8b09</t>
+          <t>T-8b08</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-403, H-8b01</t>
         </is>
       </c>
       <c r="V46" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8139,11 +8357,11 @@
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>H-8b07</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -8153,22 +8371,22 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Governance dipendenze npm</t>
+          <t>`ui/` viste</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b10</t>
+          <t>**Fase 8b.** T-8b06</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Lockfile, licenze, audit, SBOM (C25)</t>
+          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
@@ -8209,12 +8427,12 @@
       </c>
       <c r="T47" s="10" t="inlineStr">
         <is>
-          <t>T-8b10</t>
+          <t>T-8b06</t>
         </is>
       </c>
       <c r="U47" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="V47" s="10" t="inlineStr">
@@ -8230,11 +8448,11 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>H-8b08</t>
+          <t>H-8b04</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -8244,22 +8462,22 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione launcher :8799</t>
+          <t>Vista Permessi agenti</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-304</t>
+          <t>**Fase 8b.** T-405, T-8b07</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Tramite shim</t>
+          <t>Conferma, motivazione, audit, rollback</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -8300,12 +8518,12 @@
       </c>
       <c r="T48" s="10" t="inlineStr">
         <is>
-          <t>T-304</t>
+          <t>T-405, T-8b07</t>
         </is>
       </c>
       <c r="U48" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="V48" s="10" t="inlineStr">
@@ -8315,40 +8533,42 @@
       </c>
     </row>
     <row r="49" ht="58" customHeight="1">
-      <c r="A49" s="9" t="n">
-        <v>9</v>
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b06</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E ALA V1–V24</t>
+          <t>Grafica e accessibilità</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
+          <t>**Fase 8b.** T-8b09</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Catena completa su 3 OS, progetto pilota</t>
+          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -8362,7 +8582,7 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr"/>
@@ -8389,55 +8609,57 @@
       </c>
       <c r="T49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b09</t>
         </is>
       </c>
       <c r="U49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V49" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
-      <c r="A50" s="9" t="n">
-        <v>9</v>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B50" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>H-902</t>
+          <t>H-8b07</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>README e troubleshooting plugin</t>
+          <t>Governance dipendenze npm</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `agents/plugin/README.md`</t>
+          <t>**Fase 8b.** T-8b10</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Installazione, configurazione, errori</t>
+          <t>Lockfile, licenze, audit, SBOM (C25)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>H-901 [P]</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -8478,55 +8700,57 @@
       </c>
       <c r="T50" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b10</t>
         </is>
       </c>
       <c r="U50" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V50" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
-      <c r="A51" s="9" t="n">
-        <v>11</v>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B51" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>H-1101</t>
+          <t>H-8b08</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Manuali, NOTICE, runbook</t>
+          <t>Sostituzione launcher :8799</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>**Fase 11.** Revisione approvata</t>
+          <t>**Fase 8b.** T-304</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Documentazione finale</t>
+          <t>Tramite shim</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -8567,55 +8791,57 @@
       </c>
       <c r="T51" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="U51" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="V51" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
-      <c r="A52" s="9" t="n">
-        <v>10</v>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit</t>
+          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Log immutabili, sandbox, SBOM, audit</t>
+          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -8629,7 +8855,7 @@
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr"/>
@@ -8648,7 +8874,7 @@
       <c r="Q52" s="10" t="n"/>
       <c r="R52" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S52" s="12" t="n">
@@ -8656,55 +8882,57 @@
       </c>
       <c r="T52" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="U52" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="V52" s="10" t="inlineStr">
         <is>
-          <t>[N] log immutabili, sandbox, SBOM</t>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
-      <c r="A53" s="9" t="n">
-        <v>12</v>
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>H-1201</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>PK-30</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Rollout sul pilota</t>
+          <t>Avvio del run non presidiato dalla dashboard</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>**Fase 12.** Parere legale **[N]**</t>
+          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Metriche, rollback, parere legale</t>
+          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>H-1001, H-1101</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
@@ -8737,7 +8965,7 @@
       <c r="Q53" s="10" t="n"/>
       <c r="R53" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §9</t>
         </is>
       </c>
       <c r="S53" s="12" t="n">
@@ -8745,26 +8973,471 @@
       </c>
       <c r="T53" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="U53" s="10" t="inlineStr">
         <is>
+          <t>H-713, H-714, H-715, H-8b05</t>
+        </is>
+      </c>
+      <c r="V53" s="10" t="inlineStr">
+        <is>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Scenari E2E ALA V1–V24</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Catena completa su 3 OS, progetto pilota</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Fasi 5–8</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J54" s="9">
+        <f>IF(I54="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U54" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V54" s="10" t="inlineStr">
+        <is>
+          <t>E2E_VERIFICATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="58" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>H-902</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>README e troubleshooting plugin</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 9.** `agents/plugin/README.md`</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Installazione, configurazione, errori</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>H-901 [P]</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J55" s="9">
+        <f>IF(I55="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr"/>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V55" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58" customHeight="1">
+      <c r="A56" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>H-1101</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Manuali, NOTICE, runbook</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 11.** Revisione approvata</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Documentazione finale</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J56" s="9">
+        <f>IF(I56="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr"/>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U56" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V56" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="58" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Log immutabili, sandbox, SBOM, audit</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J57" s="9">
+        <f>IF(I57="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O57" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U57" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V57" s="10" t="inlineStr">
+        <is>
+          <t>docs/audit-hardening.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="58" customHeight="1">
+      <c r="A58" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>H-1201</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>PK-30</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 12.** Parere legale **[N]**</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Metriche, rollback, parere legale</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
           <t>H-1001, H-1101</t>
         </is>
       </c>
-      <c r="V53" s="10" t="inlineStr">
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J58" s="9">
+        <f>IF(I58="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr"/>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>H-1001, H-1101</t>
+        </is>
+      </c>
+      <c r="V58" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V53"/>
+  <autoFilter ref="A4:V58"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:S53">
+  <conditionalFormatting sqref="A5:S58">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($S5=1,$I5&lt;&gt;"Fatto")</formula>
     </cfRule>
@@ -8772,7 +9445,7 @@
       <formula>$I5="Fatto"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I53">
+  <conditionalFormatting sqref="I5:I58">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -8789,7 +9462,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K53">
+  <conditionalFormatting sqref="K5:K58">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
@@ -8800,7 +9473,7 @@
       <formula>"SUPERVISORE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S53">
+  <conditionalFormatting sqref="S5:S58">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -8810,19 +9483,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="I5:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Da fare,In corso,In review,Fatto,Bloccato"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NARO,SCIBETTA,SUPERVISORE,Da assegnare"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,M,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="S5:S58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -8838,7 +9511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8965,15 +9638,15 @@
         </is>
       </c>
       <c r="E5" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A5)+COUNTIF('Post-GO'!D5:D53,A5)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D58,A5)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A5,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A5,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A5,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A5,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A5,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A5,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A5,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A5,'Post-GO'!I5:I53,"In review")+F5&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"In review")+F5&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -9034,15 +9707,15 @@
         </is>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A6)+COUNTIF('Post-GO'!D5:D53,A6)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D58,A6)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A6,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A6,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A6,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A6,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A6,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A6,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A6,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A6,'Post-GO'!I5:I53,"In review")+F6&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"In review")+F6&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -9103,15 +9776,15 @@
         </is>
       </c>
       <c r="E7" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A7)+COUNTIF('Post-GO'!D5:D53,A7)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D58,A7)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A7,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A7,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A7,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A7,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A7,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A7,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A7,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A7,'Post-GO'!I5:I53,"In review")+F7&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"In review")+F7&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -9172,15 +9845,15 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A8)+COUNTIF('Post-GO'!D5:D53,A8)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D58,A8)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A8,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A8,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A8,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A8,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A8,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A8,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A8,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A8,'Post-GO'!I5:I53,"In review")+F8&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"In review")+F8&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -9241,15 +9914,15 @@
         </is>
       </c>
       <c r="E9" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A9)+COUNTIF('Post-GO'!D5:D53,A9)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D58,A9)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A9,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A9,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A9,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A9,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A9,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A9,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A9,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A9,'Post-GO'!I5:I53,"In review")+F9&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"In review")+F9&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -9310,15 +9983,15 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A10)+COUNTIF('Post-GO'!D5:D53,A10)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D58,A10)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A10,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A10,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A10,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A10,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A10,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A10,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A10,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A10,'Post-GO'!I5:I53,"In review")+F10&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"In review")+F10&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -9379,15 +10052,15 @@
         </is>
       </c>
       <c r="E11" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A11)+COUNTIF('Post-GO'!D5:D53,A11)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D58,A11)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A11,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A11,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A11,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A11,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A11,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A11,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A11,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A11,'Post-GO'!I5:I53,"In review")+F11&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"In review")+F11&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -9448,15 +10121,15 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A12)+COUNTIF('Post-GO'!D5:D53,A12)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D58,A12)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A12,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A12,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A12,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A12,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A12,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A12,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A12,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A12,'Post-GO'!I5:I53,"In review")+F12&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"In review")+F12&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -9517,15 +10190,15 @@
         </is>
       </c>
       <c r="E13" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A13)+COUNTIF('Post-GO'!D5:D53,A13)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D58,A13)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A13,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A13,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A13,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A13,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A13,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A13,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A13,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A13,'Post-GO'!I5:I53,"In review")+F13&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"In review")+F13&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -9567,34 +10240,34 @@
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PK-08</t>
+          <t>PK-07b</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Onda 2</t>
+          <t>Onda 1 (dopo H-301)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Runner con allowlist e policy permessi</t>
+          <t>Configurazione locale non versionata</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>H-401, H-404</t>
+          <t>H-309</t>
         </is>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A14)+COUNTIF('Post-GO'!D5:D53,A14)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D58,A14)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A14,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A14,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A14,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A14,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A14,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A14,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A14,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A14,'Post-GO'!I5:I53,"In review")+F14&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"In review")+F14&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -9604,39 +10277,39 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3b</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>T-401, T-402, T-405</t>
+          <t>T-309</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>agents/runner/, agents/policy/policy.json, agents/policy/floor.json</t>
+          <t>config/helios.local.example.json, config/helios.config.schema.json, modulo di bootstrap helios.config, .gitignore</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>PK-01, PK-05, PK-05b, PK-06, PK-07 (Fase 3 chiusa)</t>
+          <t>PK-04 (H-301), PK-05b (.gitignore), PK-01 (contratti)</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>PK-10, PK-11</t>
+          <t>PK-07</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>Output del runner = contratto di PK-01 (sola lettura per NARO).</t>
+          <t>Modulo condiviso da dashboard, runner, CLI, installer e CI: non duplicare la logica nella UI. Tocca .gitignore dopo PK-05b (stessa persona). Attua C20; abilita PK-26b.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PK-09</t>
+          <t>PK-08</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -9646,24 +10319,24 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Ruoli PoC (analyst, developer, reviewer)</t>
+          <t>Runner con allowlist e policy permessi</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>H-402</t>
+          <t>H-401, H-404</t>
         </is>
       </c>
       <c r="E15" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A15)+COUNTIF('Post-GO'!D5:D53,A15)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D58,A15)</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A15,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A15,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A15,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A15,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A15,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A15,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A15,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A15,'Post-GO'!I5:I53,"In review")+F15&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"In review")+F15&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -9673,22 +10346,22 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>T-403</t>
+          <t>T-401, T-402, T-405</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>agents/roles/*.md</t>
+          <t>agents/runner/, agents/policy/policy.json, agents/policy/floor.json</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>PK-08 (H-404), PK-01</t>
+          <t>PK-01, PK-05, PK-05b, PK-06, PK-07 (Fase 3 chiusa)</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -9698,14 +10371,14 @@
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>Nessun Bash libero nei tools.</t>
+          <t>Output del runner = contratto di PK-01 (sola lettura per NARO).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PK-10</t>
+          <t>PK-09</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -9715,66 +10388,66 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Gate umano meccanico sul PLAN</t>
+          <t>Ruoli PoC (analyst, developer, reviewer)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>H-403</t>
+          <t>H-402</t>
         </is>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A16)+COUNTIF('Post-GO'!D5:D53,A16)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D58,A16)</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A16,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A16,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A16,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A16,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A16,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A16,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A16,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A16,'Post-GO'!I5:I53,"In review")+F16&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"In review")+F16&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>T-404</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>agents/workflow/gate.py</t>
+          <t>agents/roles/*.md</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>PK-01</t>
+          <t>PK-08 (H-404), PK-01</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>PK-08, PK-09, PK-11</t>
+          <t>PK-10, PK-11</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>Approvazione solo da sessione umana (C24).</t>
+          <t>Nessun Bash libero nei tools.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>PK-11</t>
+          <t>PK-10</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -9784,24 +10457,24 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Prova del plugin Claude Code (V13/V14)</t>
+          <t>Gate umano meccanico sul PLAN</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-403</t>
         </is>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A17)+COUNTIF('Post-GO'!D5:D53,A17)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D58,A17)</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A17,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A17,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A17,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A17,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A17,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A17,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A17,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A17,'Post-GO'!I5:I53,"In review")+F17&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"In review")+F17&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -9811,17 +10484,17 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>T-407</t>
+          <t>T-404</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/</t>
+          <t>agents/workflow/gate.py</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
@@ -9831,19 +10504,19 @@
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>PK-08, PK-09, PK-10</t>
+          <t>PK-08, PK-09, PK-11</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>[N] sintassi Dynamic Workflow in Claude Code 2.1.311; se non riconosciuto: piano B in poc-report.md.</t>
+          <t>Approvazione solo da sessione umana (C24).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>PK-12</t>
+          <t>PK-11</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -9853,66 +10526,66 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Asset ECC portato + A/B</t>
+          <t>Prova del plugin Claude Code (V13/V14)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>H-405</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A18)+COUNTIF('Post-GO'!D5:D53,A18)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D58,A18)</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A18,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A18,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A18,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A18,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A18,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A18,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A18,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A18,'Post-GO'!I5:I53,"In review")+F18&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"In review")+F18&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>T-406</t>
+          <t>T-407</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>tests/test_ab_metrics.py, [N] cartella dell'asset ecc-code-reviewer</t>
+          <t>agents/plugin/</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>PK-08, PK-09</t>
+          <t>PK-01</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>PK-11</t>
+          <t>PK-08, PK-09, PK-10</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>D1–D10 approvati (Q-6); pilota in test\ (Q-5).</t>
+          <t>[N] sintassi Dynamic Workflow in Claude Code 2.1.311; se non riconosciuto: piano B in poc-report.md.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="62" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PK-13</t>
+          <t>PK-12</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -9922,231 +10595,231 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Rapporto go/no-go (compila NARO, decide il SUPERVISORE)</t>
+          <t>Asset ECC portato + A/B</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>H-406</t>
+          <t>H-405</t>
         </is>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A19)+COUNTIF('Post-GO'!D5:D53,A19)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D58,A19)</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A19,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A19,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A19,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A19,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A19,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A19,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A19,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A19,'Post-GO'!I5:I53,"In review")+F19&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"In review")+F19&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-406</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>docs/poc-report.md</t>
+          <t>tests/test_ab_metrics.py, [N] cartella dell'asset ecc-code-reviewer</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>PK-08…PK-12</t>
+          <t>PK-08, PK-09</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PK-11</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>PUNTO DI DECISIONE: GO / NO-GO / piano B. Le Onde 3+ partono solo dopo GO.</t>
+          <t>D1–D10 approvati (Q-6); pilota in test\ (Q-5).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="62" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PK-14</t>
+          <t>PK-13</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Onda 3 (dopo GO)</t>
+          <t>Onda 2</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Contratti della catena e skill runner</t>
+          <t>Rapporto go/no-go (compila NARO, decide il SUPERVISORE)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-409</t>
+          <t>H-406</t>
         </is>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A20)+COUNTIF('Post-GO'!D5:D53,A20)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D58,A20)</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A20,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A20,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A20,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A20,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A20,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A20,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A20,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A20,'Post-GO'!I5:I53,"In review")+F20&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"In review")+F20&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>T-308, T-409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>agents/contracts/ (nuovi schemi), agents/plugin/skills/limet-runner/</t>
+          <t>docs/poc-report.md</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-08</t>
+          <t>PK-08…PK-12</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>PK-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>Sblocca PK-16 e i ruoli (sync point).</t>
+          <t>PUNTO DI DECISIONE: GO / NO-GO / piano B. Le Onde 3+ partono solo dopo GO.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="62" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>PK-14</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Onda 3 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Contratti della catena e skill runner</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>H-308, H-409</t>
+        </is>
+      </c>
+      <c r="E21" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D58,A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G21" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"In review")+F21&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>T-308, T-409</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>agents/contracts/ (nuovi schemi), agents/plugin/skills/limet-runner/</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>GO; PK-08</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
           <t>PK-15</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Onda 3 (dopo GO)</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Scheduler e regole comuni dei ruoli</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>H-408, H-611</t>
-        </is>
-      </c>
-      <c r="E21" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A21)+COUNTIF('Post-GO'!D5:D53,A21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A21,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A21,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G21" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A21,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A21,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A21,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A21,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A21,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A21,'Post-GO'!I5:I53,"In review")+F21&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>NARO</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>T-408, T-610</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>agents/plugin/scheduler/, agents/plugin/agents/_common.md</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>GO; PK-08</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>PK-14</t>
-        </is>
-      </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>_common.md: owner NARO, sola lettura per SCIBETTA.</t>
+          <t>Sblocca PK-16 e i ruoli (sync point).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="62" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>PK-16</t>
+          <t>PK-15</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Onda 4 (dopo GO)</t>
+          <t>Onda 3 (dopo GO)</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Porting asset ECC</t>
+          <t>Scheduler e regole comuni dei ruoli</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>H-501, H-502, H-503</t>
+          <t>H-408, H-611</t>
         </is>
       </c>
       <c r="E22" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A22)+COUNTIF('Post-GO'!D5:D53,A22)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D58,A22)</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A22,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A22,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G22" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A22,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A22,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A22,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A22,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A22,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A22,'Post-GO'!I5:I53,"In review")+F22&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"In review")+F22&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -10156,108 +10829,108 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>N8</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>T-501, T-502, T-503</t>
+          <t>T-408, T-610</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>agents/assets/ (ecc-*), test di agnosticità</t>
+          <t>agents/plugin/scheduler/, agents/plugin/agents/_common.md</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>PK-03, PK-14</t>
+          <t>GO; PK-08</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-14</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>Aspetta H-308 (PK-14).</t>
+          <t>_common.md: owner NARO, sola lettura per SCIBETTA.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="62" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>PK-16</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Onda 4 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Porting asset ECC</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>H-501, H-502, H-503</t>
+        </is>
+      </c>
+      <c r="E23" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D58,A23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"In review")+F23&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>T-501, T-502, T-503</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>agents/assets/ (ecc-*), test di agnosticità</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>PK-03, PK-14</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
           <t>PK-17</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Onda 4 (dopo GO)</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Ruoli di sviluppo</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>H-602, H-603, H-604, H-605</t>
-        </is>
-      </c>
-      <c r="E23" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A23)+COUNTIF('Post-GO'!D5:D53,A23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A23,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A23,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A23,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A23,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A23,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A23,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A23,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A23,'Post-GO'!I5:I53,"In review")+F23&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>SCIBETTA</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>T-601, T-602, T-603, T-604</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>agents/plugin/agents/{analyst,developer,tester,integrator}.md</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>PK-14, PK-15, PK-09</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>PK-16, PK-18</t>
-        </is>
-      </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>Stessa cartella di PK-18 ma file distinti.</t>
+          <t>Aspetta H-308 (PK-14).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PK-18</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -10267,44 +10940,44 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Ruoli di controllo</t>
+          <t>Ruoli di sviluppo</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>H-606, H-607, H-608, H-609, H-610, H-601</t>
+          <t>H-602, H-603, H-604, H-605</t>
         </is>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A24)+COUNTIF('Post-GO'!D5:D53,A24)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D58,A24)</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A24,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A24,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A24,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A24,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A24,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A24,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A24,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A24,'Post-GO'!I5:I53,"In review")+F24&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"In review")+F24&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>N9</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>T-605, T-606, T-607, T-608, T-609, T-403</t>
+          <t>T-601, T-602, T-603, T-604</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
+          <t>agents/plugin/agents/{analyst,developer,tester,integrator}.md</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
@@ -10314,88 +10987,88 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16, PK-18</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>Stessa cartella di PK-17 ma file distinti.</t>
+          <t>Stessa cartella di PK-18 ma file distinti.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="62" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-18</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 4 (dopo GO)</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Workflow core e permessi tool</t>
+          <t>Ruoli di controllo</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>H-701, H-703, H-704, H-705, H-707, H-708, H-710</t>
+          <t>H-606, H-607, H-608, H-609, H-610, H-601</t>
         </is>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A25)+COUNTIF('Post-GO'!D5:D53,A25)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D58,A25)</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A25,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A25,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A25,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A25,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A25,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A25,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A25,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A25,'Post-GO'!I5:I53,"In review")+F25&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"In review")+F25&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>N9</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>T-701, T-703, T-704, T-705, T-707, T-708, T-710</t>
+          <t>T-605, T-606, T-607, T-608, T-609, T-403</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
+          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-18, H-407</t>
+          <t>PK-14, PK-15, PK-09</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>PK-20, PK-22</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>[N] se limet-change.js è un file unico va scritto da una sola persona (SCIBETTA).</t>
+          <t>Stessa cartella di PK-17 ma file distinti.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>PK-20</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -10405,44 +11078,44 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Stato/eventi, report e gate di merge</t>
+          <t>Workflow core e permessi tool</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>H-706, H-709, H-711</t>
+          <t>H-701, H-703, H-704, H-705, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="E26" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A26)+COUNTIF('Post-GO'!D5:D53,A26)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D58,A26)</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A26,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A26,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A26,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A26,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A26,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A26,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A26,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A26,'Post-GO'!I5:I53,"In review")+F26&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"In review")+F26&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>T-706, T-709, T-711</t>
+          <t>T-701, T-703, T-704, T-705, T-707, T-708, T-710</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
+          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
@@ -10452,46 +11125,46 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-20, PK-22</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto state.json / events.jsonl di H-308. NARO non modifica limet-change.js.</t>
+          <t>[N] se limet-change.js è un file unico va scritto da una sola persona (SCIBETTA).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi di prodotto (C28)</t>
+          <t>Stato/eventi, report e gate di merge</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-706, H-709, H-711</t>
         </is>
       </c>
       <c r="E27" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A27)+COUNTIF('Post-GO'!D5:D53,A27)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D58,A27)</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A27,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A27,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A27,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A27,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A27,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A27,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A27,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A27,'Post-GO'!I5:I53,"In review")+F27&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"In review")+F27&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -10501,177 +11174,177 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-706, T-709, T-711</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
+          <t>PK-14…PK-18, H-407</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>PK-23, PK-24, PK-25</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>risk-assessor ≠ developer, sola lettura.</t>
+          <t>Contatto: contratto state.json / events.jsonl di H-308. NARO non modifica limet-change.js.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="62" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Installer e modifiche documentali a LIMET</t>
+          <t>Modalità non presidiata: motore e allow-list dei ruoli</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>H-702, H-712</t>
+          <t>H-713, H-715</t>
         </is>
       </c>
       <c r="E28" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A28)+COUNTIF('Post-GO'!D5:D53,A28)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D58,A28)</f>
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A28,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A28,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G28" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A28,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A28,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A28,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A28,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A28,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A28,'Post-GO'!I5:I53,"In review")+F28&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"In review")+F28&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>S9b</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>T-702, T-712</t>
+          <t>T-713, T-1, T-2, T-715</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
+          <t>PK-19 (H-707, H-708), PK-20 (H-706), PK-21 (H-612)</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
+          <t>ADR 0003. **Neutralità dei permessi**: la modalità non amplia MAI i permessi (C02, C24, pavimento H-404). Stessi file di PK-19: stessa persona. Verifica: T-713, T-715, E2E-AUT-1, E2E-AUT-2.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Hook ECC e registro chiamate LLM</t>
+          <t>Registro delle decisioni autonome e report notturno</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>H-800, H-800b, H-801, H-802</t>
+          <t>H-714</t>
         </is>
       </c>
       <c r="E29" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A29)+COUNTIF('Post-GO'!D5:D53,A29)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D58,A29)</f>
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A29,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A29,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G29" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A29,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A29,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A29,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A29,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A29,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A29,'Post-GO'!I5:I53,"In review")+F29&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"In review")+F29&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>N10b</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>T-801, T-802</t>
+          <t>T-714, T-1</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-08</t>
+          <t>PK-19b (H-713), PK-20 (H-709)</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-22</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
+          <t>ADR 0003 §8 (prova a posteriori, R18). Contatto: formato del registro definito in H-713. Verifica: T-714, E2E-AUT-1.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="62" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -10681,231 +11354,231 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Knowledge base HLS_* e accesso agenti</t>
+          <t>Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-804</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="E30" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A30)+COUNTIF('Post-GO'!D5:D53,A30)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D58,A30)</f>
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A30,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A30,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G30" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A30,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A30,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A30,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A30,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A30,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A30,'Post-GO'!I5:I53,"In review")+F30&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"In review")+F30&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>T-803, T-804</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>PK-03, PK-15</t>
+          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-23, PK-24, PK-25</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
+          <t>risk-assessor ≠ developer, sola lettura.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>API loopback e read model</t>
+          <t>Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-8b02, H-8b05</t>
+          <t>H-702, H-712</t>
         </is>
       </c>
       <c r="E31" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A31)+COUNTIF('Post-GO'!D5:D53,A31)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D58,A31)</f>
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A31,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A31,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G31" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A31,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A31,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A31,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A31,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A31,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A31,'Post-GO'!I5:I53,"In review")+F31&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"In review")+F31&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
+          <t>T-702, T-712</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-06, PK-08</t>
+          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>PK-26 (dopo contratto API)</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="62" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Onda 4+ (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
+          <t>H-800, H-800b, H-801, H-802</t>
         </is>
       </c>
       <c r="E32" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A32)+COUNTIF('Post-GO'!D5:D53,A32)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D58,A32)</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A32,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A32,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G32" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A32,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A32,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A32,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A32,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A32,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A32,'Post-GO'!I5:I53,"In review")+F32&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"In review")+F32&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>N13</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
+          <t>T-801, T-802</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>PK-25, PK-08, PK-06</t>
+          <t>GO; PK-08</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>PK-25 (dopo contratto API)</t>
+          <t>PK-14…PK-22</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git (C23–C24).</t>
+          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="62" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E V1–V24</t>
+          <t>Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-803, H-804</t>
         </is>
       </c>
       <c r="E33" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A33)+COUNTIF('Post-GO'!D5:D53,A33)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D58,A33)</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A33,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A33,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G33" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A33,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A33,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A33,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A33,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A33,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A33,'Post-GO'!I5:I53,"In review")+F33&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"In review")+F33&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -10915,249 +11588,594 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-803, T-804</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>PK-03, PK-15</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
+          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>README plugin e manuali</t>
+          <t>API loopback e read model</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>H-902, H-1101</t>
+          <t>H-8b01, H-8b02, H-8b05</t>
         </is>
       </c>
       <c r="E34" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A34)+COUNTIF('Post-GO'!D5:D53,A34)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D58,A34)</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A34,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A34,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G34" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A34,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A34,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A34,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A34,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A34,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A34,'Post-GO'!I5:I53,"In review")+F34&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"In review")+F34&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>N14</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>api/</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>GO; PK-06, PK-08</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-26 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>Revisione approvata dal SUPERVISORE.</t>
+          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="62" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Onda 8 (dopo GO)</t>
+          <t>Onda 4+ (dopo GO)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
         </is>
       </c>
       <c r="E35" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A35)+COUNTIF('Post-GO'!D5:D53,A35)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D58,A35)</f>
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A35,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A35,'Post-GO'!I5:I53,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"Fatto")</f>
         <v/>
       </c>
       <c r="G35" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A35,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A35,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A35,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A35,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A35,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A35,'Post-GO'!I5:I53,"In review")+F35&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"In review")+F35&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>[N] log immutabili, sandbox, SBOM</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-25, PK-08, PK-06</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-25 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+          <t>La UI non esegue build/test/git (C23–C24).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
+          <t>PK-26b</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Onda 4+ (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Gate di configurazione all'avvio della dashboard</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>H-8b09</t>
+        </is>
+      </c>
+      <c r="E36" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D58,A36)</f>
+        <v/>
+      </c>
+      <c r="F36" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G36" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"In review")+F36&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>N13b</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>T-8b11</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="62" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>PK-26c</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Onda 5+ (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Pannello di avvio del run non presidiato</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>H-8b10</t>
+        </is>
+      </c>
+      <c r="E37" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D58,A37)</f>
+        <v/>
+      </c>
+      <c r="F37" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G37" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"In review")+F37&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>N13c</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>T-8b13, T-2</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="62" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Scenari E2E V1–V24</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="E38" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D58,A38)</f>
+        <v/>
+      </c>
+      <c r="F38" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G38" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"In review")+F38&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>Fasi 5–8</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="62" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>README plugin e manuali</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>H-902, H-1101</t>
+        </is>
+      </c>
+      <c r="E39" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D58,A39)</f>
+        <v/>
+      </c>
+      <c r="F39" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G39" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"In review")+F39&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>Revisione approvata dal SUPERVISORE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="62" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Onda 8 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="E40" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D58,A40)</f>
+        <v/>
+      </c>
+      <c r="F40" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G40" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"In review")+F40&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>[N] log immutabili, sandbox, SBOM</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="62" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
           <t>PK-30</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Onda 9 (dopo GO)</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Rollout sul pilota</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>H-1201</t>
         </is>
       </c>
-      <c r="E36" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D25,A36)+COUNTIF('Post-GO'!D5:D53,A36)</f>
-        <v/>
-      </c>
-      <c r="F36" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D25,A36,'Pre-GO'!I5:I25,"Fatto")+COUNTIFS('Post-GO'!D5:D53,A36,'Post-GO'!I5:I53,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G36" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D25,A36,'Pre-GO'!I5:I25,"Bloccato")+COUNTIFS('Post-GO'!D5:D53,A36,'Post-GO'!I5:I53,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D25,A36,'Pre-GO'!I5:I25,"In corso")+COUNTIFS('Post-GO'!D5:D53,A36,'Post-GO'!I5:I53,"In corso")+COUNTIFS('Pre-GO'!D5:D25,A36,'Pre-GO'!I5:I25,"In review")+COUNTIFS('Post-GO'!D5:D53,A36,'Post-GO'!I5:I53,"In review")+F36&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="E41" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D58,A41)</f>
+        <v/>
+      </c>
+      <c r="F41" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G41" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"In review")+F41&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>NARO</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>N15</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>PK-28, PK-29</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>[N] parere legale; pilota da scegliere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N36"/>
+  <autoFilter ref="A4:N41"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G36">
+  <conditionalFormatting sqref="G5:G41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -11171,7 +12189,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H36">
+  <conditionalFormatting sqref="H5:H41">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>

--- a/log/HELIOS_Distribuzione_task.xlsx
+++ b/log/HELIOS_Distribuzione_task.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-GO'!$A$4:$V$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIF('Post-GO'!I5:I58,A4)</f>
+        <f>COUNTIF('Post-GO'!I5:I61,A4)</f>
         <v/>
       </c>
       <c r="D4">
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIF('Post-GO'!I5:I58,A5)</f>
+        <f>COUNTIF('Post-GO'!I5:I61,A5)</f>
         <v/>
       </c>
       <c r="D5">
@@ -677,7 +677,7 @@
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIF('Post-GO'!I5:I58,A6)</f>
+        <f>COUNTIF('Post-GO'!I5:I61,A6)</f>
         <v/>
       </c>
       <c r="D6">
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIF('Post-GO'!I5:I58,A7)</f>
+        <f>COUNTIF('Post-GO'!I5:I61,A7)</f>
         <v/>
       </c>
       <c r="D7">
@@ -715,7 +715,7 @@
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIF('Post-GO'!I5:I58,A8)</f>
+        <f>COUNTIF('Post-GO'!I5:I61,A8)</f>
         <v/>
       </c>
       <c r="D8">
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIF('Post-GO'!K5:K58,A14)</f>
+        <f>COUNTIF('Post-GO'!K5:K61,A14)</f>
         <v/>
       </c>
       <c r="D14">
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A14,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A14,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIF('Post-GO'!K5:K58,A15)</f>
+        <f>COUNTIF('Post-GO'!K5:K61,A15)</f>
         <v/>
       </c>
       <c r="D15">
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A15,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A15,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIF('Post-GO'!K5:K58,A16)</f>
+        <f>COUNTIF('Post-GO'!K5:K61,A16)</f>
         <v/>
       </c>
       <c r="D16">
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A16,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A16,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIF('Post-GO'!K5:K58,A17)</f>
+        <f>COUNTIF('Post-GO'!K5:K61,A17)</f>
         <v/>
       </c>
       <c r="D17">
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K58,A17,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A17,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D58,"PK-00")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D61,"PK-00")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-00",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="B22">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D58,"PK-01")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D61,"PK-01")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-01",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B23">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D58,"PK-02")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D61,"PK-02")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-02",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B24">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D58,"PK-03")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D61,"PK-03")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-03",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B25">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D58,"PK-04")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D61,"PK-04")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-04",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B26">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D58,"PK-05")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D61,"PK-05")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-05",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="B27">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D58,"PK-05b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D61,"PK-05b")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-05b",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="B28">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D58,"PK-06")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D61,"PK-06")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-06",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B29">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D58,"PK-07")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D61,"PK-07")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-07",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="B30">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D58,"PK-07b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D61,"PK-07b")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-07b",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -1189,19 +1189,19 @@
         </is>
       </c>
       <c r="B31">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D58,"PK-08")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D61,"PK-08")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-08",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B32">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D58,"PK-09")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D61,"PK-09")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-09",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D58,"PK-10")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D61,"PK-10")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-10",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D58,"PK-11")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D61,"PK-11")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-11",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D58,"PK-12")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D61,"PK-12")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-12",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D58,"PK-13")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D61,"PK-13")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-13",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D58,"PK-14")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D61,"PK-14")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-14",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="B38">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D58,"PK-15")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D61,"PK-15")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-15",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F38" s="5">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="B39">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D58,"PK-16")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D61,"PK-16")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-16",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F39" s="5">
@@ -1428,23 +1428,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PK-17 · Ruoli di sviluppo</t>
+          <t>PK-16b · Architettura viva (documenti + test di integrita)</t>
         </is>
       </c>
       <c r="B40">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D58,"PK-17")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16b")+COUNTIF('Post-GO'!D5:D61,"PK-16b")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-17",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F40" s="5">
@@ -1455,23 +1455,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PK-18 · Ruoli di controllo</t>
+          <t>PK-16c · Guida d'uso e documenti di contesto per gli agenti</t>
         </is>
       </c>
       <c r="B41">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D58,"PK-18")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16c")+COUNTIF('Post-GO'!D5:D61,"PK-16c")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-18",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F41" s="5">
@@ -1482,23 +1482,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PK-19 · Workflow core e permessi tool</t>
+          <t>PK-17 · Ruoli di sviluppo</t>
         </is>
       </c>
       <c r="B42">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D58,"PK-19")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D61,"PK-17")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-19",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F42" s="5">
@@ -1509,23 +1509,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PK-20 · Stato/eventi, report e gate di merge</t>
+          <t>PK-18 · Ruoli di controllo</t>
         </is>
       </c>
       <c r="B43">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D58,"PK-20")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D61,"PK-18")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-20",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F43" s="5">
@@ -1536,23 +1536,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PK-19b · Modalità non presidiata: motore e allow-list dei ruoli</t>
+          <t>PK-19 · Workflow core e permessi tool</t>
         </is>
       </c>
       <c r="B44">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D58,"PK-19b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D61,"PK-19")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-19b",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F44" s="5">
@@ -1563,23 +1563,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PK-20b · Registro delle decisioni autonome e report notturno</t>
+          <t>PK-20 · Stato/eventi, report e gate di merge</t>
         </is>
       </c>
       <c r="B45">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D58,"PK-20b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D61,"PK-20")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-20b",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F45" s="5">
@@ -1590,23 +1590,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
+          <t>PK-19b · Modalità non presidiata: motore e allow-list dei ruoli</t>
         </is>
       </c>
       <c r="B46">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D58,"PK-21")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D61,"PK-19b")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-21",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F46" s="5">
@@ -1617,23 +1617,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
+          <t>PK-20b · Registro delle decisioni autonome e report notturno</t>
         </is>
       </c>
       <c r="B47">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D58,"PK-22")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D61,"PK-20b")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-22",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F47" s="5">
@@ -1644,23 +1644,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
+          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="B48">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D58,"PK-23")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D61,"PK-21")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-23",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F48" s="5">
@@ -1671,23 +1671,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
+          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="B49">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D58,"PK-24")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D61,"PK-22")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-24",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F49" s="5">
@@ -1698,23 +1698,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PK-25 · API loopback e read model</t>
+          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="B50">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D58,"PK-25")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D61,"PK-23")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-25",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F50" s="5">
@@ -1725,23 +1725,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D58,"PK-26")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D61,"PK-24")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F51" s="5">
@@ -1752,23 +1752,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
+          <t>PK-25 · API loopback e read model</t>
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D58,"PK-26b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D61,"PK-25")</f>
         <v/>
       </c>
       <c r="C52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26b",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F52" s="5">
@@ -1779,23 +1779,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PK-26c · Pannello di avvio del run non presidiato</t>
+          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="B53">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D58,"PK-26c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D61,"PK-26")</f>
         <v/>
       </c>
       <c r="C53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-26c",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F53" s="5">
@@ -1806,23 +1806,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PK-27 · Scenari E2E V1–V24</t>
+          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="B54">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D58,"PK-27")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D61,"PK-26b")</f>
         <v/>
       </c>
       <c r="C54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-27",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F54" s="5">
@@ -1833,23 +1833,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PK-28 · README plugin e manuali</t>
+          <t>PK-26c · Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="B55">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D58,"PK-28")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D61,"PK-26c")</f>
         <v/>
       </c>
       <c r="C55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-28",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F55" s="5">
@@ -1860,23 +1860,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PK-29 · Hardening</t>
+          <t>PK-27 · Scenari E2E V1–V24</t>
         </is>
       </c>
       <c r="B56">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D58,"PK-29")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D61,"PK-27")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-29",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F56" s="5">
@@ -1887,23 +1887,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PK-30 · Rollout sul pilota</t>
+          <t>PK-28 · README plugin e manuali</t>
         </is>
       </c>
       <c r="B57">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D58,"PK-30")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D61,"PK-28")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D58,"PK-30",'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F57" s="5">
@@ -1911,113 +1911,117 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PK-29 · Hardening</t>
+        </is>
+      </c>
+      <c r="B58">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D61,"PK-29")</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F58" s="5">
+        <f>IF(B58=0,0,C58/B58)</f>
+        <v/>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PK-30 · Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="B59">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D61,"PK-30")</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F59" s="5">
+        <f>IF(B59=0,0,C59/B59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Avanzamento per fase</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Fatti</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>In corso</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A61)+COUNTIFS('Post-GO'!A5:A58,$A61)</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A61,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A61,'Post-GO'!I5:I58,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F61" s="5">
-        <f>IF(B61=0,0,C61/B61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B62">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A62)+COUNTIFS('Post-GO'!A5:A58,$A62)</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A62,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A62,'Post-GO'!I5:I58,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F62" s="5">
-        <f>IF(B62=0,0,C62/B62)</f>
-        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63)+COUNTIFS('Post-GO'!A5:A58,$A63)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63)+COUNTIFS('Post-GO'!A5:A61,$A63)</f>
         <v/>
       </c>
       <c r="C63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A63,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F63" s="5">
@@ -2027,22 +2031,22 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A58,$A64)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A61,$A64)</f>
         <v/>
       </c>
       <c r="C64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A64,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F64" s="5">
@@ -2052,22 +2056,22 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A58,$A65)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A61,$A65)</f>
         <v/>
       </c>
       <c r="C65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A65,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F65" s="5">
@@ -2077,22 +2081,22 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A58,$A66)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A61,$A66)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A66,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F66" s="5">
@@ -2102,22 +2106,22 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A58,$A67)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A61,$A67)</f>
         <v/>
       </c>
       <c r="C67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A67,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F67" s="5">
@@ -2127,22 +2131,22 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A58,$A68)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A61,$A68)</f>
         <v/>
       </c>
       <c r="C68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A68,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F68" s="5">
@@ -2151,25 +2155,23 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A69" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="B69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A58,$A69)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A61,$A69)</f>
         <v/>
       </c>
       <c r="C69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A69,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F69" s="5">
@@ -2179,22 +2181,22 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A58,$A70)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A61,$A70)</f>
         <v/>
       </c>
       <c r="C70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A70,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F70" s="5">
@@ -2203,23 +2205,25 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>10</v>
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A58,$A71)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A61,$A71)</f>
         <v/>
       </c>
       <c r="C71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A71,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F71" s="5">
@@ -2229,22 +2233,22 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A58,$A72)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A61,$A72)</f>
         <v/>
       </c>
       <c r="C72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A72,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F72" s="5">
@@ -2254,26 +2258,76 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A58,$A73)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A61,$A73)</f>
         <v/>
       </c>
       <c r="C73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="D73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"In corso")</f>
         <v/>
       </c>
       <c r="E73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A58,$A73,'Post-GO'!I5:I58,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"Da fare")</f>
         <v/>
       </c>
       <c r="F73" s="5">
         <f>IF(B73=0,0,C73/B73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74)+COUNTIFS('Post-GO'!A5:A61,$A74)</f>
+        <v/>
+      </c>
+      <c r="C74">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D74">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E74">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F74" s="5">
+        <f>IF(B74=0,0,C74/B74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B75">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75)+COUNTIFS('Post-GO'!A5:A61,$A75)</f>
+        <v/>
+      </c>
+      <c r="C75">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D75">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E75">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F75" s="5">
+        <f>IF(B75=0,0,C75/B75)</f>
         <v/>
       </c>
     </row>
@@ -2290,7 +2344,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F57">
+  <conditionalFormatting sqref="F21:F59">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2299,7 +2353,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F61:F73">
+  <conditionalFormatting sqref="F63:F75">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4445,7 +4499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4486,11 +4540,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(I5:I58,"Fatto")/COUNTA(C5:C58)</f>
+        <f>COUNTIF(I5:I61,"Fatto")/COUNTA(C5:C61)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(I5:I58,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C58)&amp;" task · "&amp;COUNTIF(I5:I58,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I58,"Bloccato")&amp;" bloccati"</f>
+        <f>COUNTIF(I5:I61,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C61)&amp;" task · "&amp;COUNTIF(I5:I61,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I61,"Bloccato")&amp;" bloccati"</f>
         <v/>
       </c>
     </row>
@@ -5231,39 +5285,39 @@
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>30</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>H-602</t>
+          <t>H-504</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16b</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `analyst` (opus)</t>
+          <t>Architettura viva</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6, gruppo C.** `agents/plugin/agents/analyst.md`</t>
+          <t>**Fase 5.** `docs-limet/architecture.md` + `docs-limet/module-map.md`, con citazioni `file:riga` e diagrammi Mermaid (convenzione `AGENTS.md`). Indicizzati in `CRB_helios`, quindi interrogabili via RA</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Produrre `plan.json`; non inventa requisiti</t>
+          <t>Descrivere l'architettura **com'è realmente**, aggiornata a ogni fase e non ricostruita a memoria alla fine</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>gruppo A, H-402</t>
+          <t>H-406 (GO)</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -5296,7 +5350,7 @@
       <c r="Q12" s="10" t="n"/>
       <c r="R12" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. Nasce dal rilievo **A13** dell'audit 2026-10-30</t>
         </is>
       </c>
       <c r="S12" s="12" t="n">
@@ -5304,55 +5358,55 @@
       </c>
       <c r="T12" s="10" t="inlineStr">
         <is>
-          <t>T-601</t>
+          <t>T-504</t>
         </is>
       </c>
       <c r="U12" s="10" t="inlineStr">
         <is>
-          <t>H-402 · gruppo A/C come da dipendenze</t>
+          <t>H-406</t>
         </is>
       </c>
       <c r="V12" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/analyst.md</t>
+          <t>docs-limet/architecture.md, docs-limet/module-map.md, AGENTS.md</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>31</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>H-603</t>
+          <t>H-505</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16c</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `developer` ×N (sonnet)</t>
+          <t>Guida d'uso per l'utente</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `developer.md`</t>
+          <t>**Fase 5.** `docs/USER_GUIDE.md`. Destinatario distinto da `guides/` (che è per chi lavora al repository). Nessun unit test: verifica = **comandi della guida eseguiti davvero** (stesso criterio di H-9</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Un task per worktree/ramo, mai build/test/push</t>
+          <t>Dare a chi *usa* HELIOS un documento unico, accresciuto man mano, invece di una guida scritta a fine progetto</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>gruppo A, H-402</t>
+          <t>H-407 (prima funzionalità usabile)</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -5366,7 +5420,7 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr"/>
@@ -5385,7 +5439,7 @@
       <c r="Q13" s="10" t="n"/>
       <c r="R13" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. H-902 e H-1101 la completano, non la creano</t>
         </is>
       </c>
       <c r="S13" s="12" t="n">
@@ -5393,55 +5447,55 @@
       </c>
       <c r="T13" s="10" t="inlineStr">
         <is>
-          <t>T-602</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="10" t="inlineStr">
         <is>
-          <t>H-402 · gruppo A/C come da dipendenze</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V13" s="10" t="inlineStr">
         <is>
-          <t>developer.md</t>
+          <t>docs/USER_GUIDE.md, guides/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>32</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>H-604</t>
+          <t>H-506</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16c</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `tester` ×M (sonnet)</t>
+          <t>Documenti di contesto per gli agenti</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `tester.md`</t>
+          <t>**Fase 5.** `docs-limet/glossary.md` (71 agenti, 311 skill, ruoli ECC/LIMET/HELIOS con nomi sovrapposti), `docs-limet/conventions.md` (codice, commit, naming — letto dai ruoli H-6xx prima di scrivere)</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Test dal TEST_PLAN senza vedere il diff; mai Graphify</t>
+          <t>Fissare termini e convenzioni una volta sola, perché i ruoli non li interpretino ciascuno a modo suo</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>gruppo A, H-402</t>
+          <t>H-504</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -5455,7 +5509,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr"/>
@@ -5474,7 +5528,7 @@
       <c r="Q14" s="10" t="n"/>
       <c r="R14" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. Esclusi `decisions.md` (duplicherebbe `docs/adr/`) e `dependencies.md` (già nel ledger H-202 e nell'SBOM H-1001)</t>
         </is>
       </c>
       <c r="S14" s="12" t="n">
@@ -5482,17 +5536,17 @@
       </c>
       <c r="T14" s="10" t="inlineStr">
         <is>
-          <t>T-603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="10" t="inlineStr">
         <is>
-          <t>H-402 · gruppo A/C come da dipendenze</t>
+          <t>H-504</t>
         </is>
       </c>
       <c r="V14" s="10" t="inlineStr">
         <is>
-          <t>tester.md</t>
+          <t>docs-limet/glossary.md, docs-limet/conventions.md, docs-limet/NON_TECHNICAL_SUMMARY.md, 06_sintesi_non_tecnica.md</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5559,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>H-605</t>
+          <t>H-602</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -5515,17 +5569,17 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `integrator` (sonnet)</t>
+          <t>Ruolo `analyst` (opus)</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `integrator.md`</t>
+          <t>**Fase 6, gruppo C.** `agents/plugin/agents/analyst.md`</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Integra su `integration/NNNN`; mai merge su `main`</t>
+          <t>Produrre `plan.json`; non inventa requisiti</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -5571,7 +5625,7 @@
       </c>
       <c r="T15" s="10" t="inlineStr">
         <is>
-          <t>T-604</t>
+          <t>T-601</t>
         </is>
       </c>
       <c r="U15" s="10" t="inlineStr">
@@ -5581,7 +5635,7 @@
       </c>
       <c r="V15" s="10" t="inlineStr">
         <is>
-          <t>integrator.md</t>
+          <t>agents/plugin/agents/analyst.md</t>
         </is>
       </c>
     </row>
@@ -5594,27 +5648,27 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>H-606</t>
+          <t>H-603</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>PK-18</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `test-reader` (haiku)</t>
+          <t>Ruolo `developer` ×N (sonnet)</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `test-reader.md`</t>
+          <t>**Fase 6.** `developer.md`</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Classifica i fallimenti con estratti reali</t>
+          <t>Un task per worktree/ramo, mai build/test/push</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -5633,7 +5687,7 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr"/>
@@ -5660,7 +5714,7 @@
       </c>
       <c r="T16" s="10" t="inlineStr">
         <is>
-          <t>T-605</t>
+          <t>T-602</t>
         </is>
       </c>
       <c r="U16" s="10" t="inlineStr">
@@ -5670,7 +5724,7 @@
       </c>
       <c r="V16" s="10" t="inlineStr">
         <is>
-          <t>test-reader.md</t>
+          <t>developer.md</t>
         </is>
       </c>
     </row>
@@ -5683,27 +5737,27 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>H-607</t>
+          <t>H-604</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>PK-18</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `reviewer` (opus ≠ developer)</t>
+          <t>Ruolo `tester` ×M (sonnet)</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `reviewer.md`</t>
+          <t>**Fase 6.** `tester.md`</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Findings con severità/file/riga; non corregge</t>
+          <t>Test dal TEST_PLAN senza vedere il diff; mai Graphify</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -5722,7 +5776,7 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr"/>
@@ -5749,7 +5803,7 @@
       </c>
       <c r="T17" s="10" t="inlineStr">
         <is>
-          <t>T-606</t>
+          <t>T-603</t>
         </is>
       </c>
       <c r="U17" s="10" t="inlineStr">
@@ -5759,7 +5813,7 @@
       </c>
       <c r="V17" s="10" t="inlineStr">
         <is>
-          <t>reviewer.md</t>
+          <t>tester.md</t>
         </is>
       </c>
     </row>
@@ -5772,27 +5826,27 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>H-608</t>
+          <t>H-605</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>PK-18</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Ruolo `validator` (opus)</t>
+          <t>Ruolo `integrator` (sonnet)</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `validator.md`</t>
+          <t>**Fase 6.** `integrator.md`</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>conforme/non conforme/non determinabile con evidenze</t>
+          <t>Integra su `integration/NNNN`; mai merge su `main`</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -5811,7 +5865,7 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr"/>
@@ -5838,7 +5892,7 @@
       </c>
       <c r="T18" s="10" t="inlineStr">
         <is>
-          <t>T-607</t>
+          <t>T-604</t>
         </is>
       </c>
       <c r="U18" s="10" t="inlineStr">
@@ -5848,7 +5902,7 @@
       </c>
       <c r="V18" s="10" t="inlineStr">
         <is>
-          <t>validator.md</t>
+          <t>integrator.md</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5915,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>H-609</t>
+          <t>H-606</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -5871,17 +5925,17 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>`metrics-observer` + aggregatore</t>
+          <t>Ruolo `test-reader` (haiku)</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `metrics-observer.md`, `agents/metrics/`</t>
+          <t>**Fase 6.** `test-reader.md`</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Interpreta solo metriche già aggregate</t>
+          <t>Classifica i fallimenti con estratti reali</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -5927,7 +5981,7 @@
       </c>
       <c r="T19" s="10" t="inlineStr">
         <is>
-          <t>T-608</t>
+          <t>T-605</t>
         </is>
       </c>
       <c r="U19" s="10" t="inlineStr">
@@ -5937,7 +5991,7 @@
       </c>
       <c r="V19" s="10" t="inlineStr">
         <is>
-          <t>metrics-observer.md, agents/metrics/</t>
+          <t>test-reader.md</t>
         </is>
       </c>
     </row>
@@ -5950,7 +6004,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>H-610</t>
+          <t>H-607</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -5960,17 +6014,17 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Ruoli `e2e-designer`/`e2e-reader`</t>
+          <t>Ruolo `reviewer` (opus ≠ developer)</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** `e2e-*.md`</t>
+          <t>**Fase 6.** `reviewer.md`</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>E2E Playwright eseguiti dal runner</t>
+          <t>Findings con severità/file/riga; non corregge</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -6016,7 +6070,7 @@
       </c>
       <c r="T20" s="10" t="inlineStr">
         <is>
-          <t>T-609</t>
+          <t>T-606</t>
         </is>
       </c>
       <c r="U20" s="10" t="inlineStr">
@@ -6026,7 +6080,7 @@
       </c>
       <c r="V20" s="10" t="inlineStr">
         <is>
-          <t>e2e-*.md</t>
+          <t>reviewer.md</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6093,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>H-601</t>
+          <t>H-608</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -6049,22 +6103,22 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Reviewer specializzati ECC</t>
+          <t>Ruolo `validator` (opus)</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6.** T-403</t>
+          <t>**Fase 6.** `validator.md`</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Lenti `ecc-*` riusate con overlay minimo (estende H-607)</t>
+          <t>conforme/non conforme/non determinabile con evidenze</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>gruppo A, H-402, H-607 [P]</t>
+          <t>gruppo A, H-402</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -6105,55 +6159,55 @@
       </c>
       <c r="T21" s="10" t="inlineStr">
         <is>
-          <t>T-403</t>
+          <t>T-607</t>
         </is>
       </c>
       <c r="U21" s="10" t="inlineStr">
         <is>
-          <t>H-402, H-607 · gruppo A/C come da dipendenze</t>
+          <t>H-402 · gruppo A/C come da dipendenze</t>
         </is>
       </c>
       <c r="V21" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
+          <t>validator.md</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>40</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>H-701</t>
+          <t>H-609</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-18</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Workflow `limet-change.js`</t>
+          <t>`metrics-observer` + aggregatore</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7, gruppo D.** T-701</t>
+          <t>**Fase 6.** `metrics-observer.md`, `agents/metrics/`</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Struttura, validazione input, stati, retry, stop-e-chiedi</t>
+          <t>Interpreta solo metriche già aggregate</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>gruppo A, H-402</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -6167,7 +6221,7 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr"/>
@@ -6194,55 +6248,55 @@
       </c>
       <c r="T22" s="10" t="inlineStr">
         <is>
-          <t>T-701</t>
+          <t>T-608</t>
         </is>
       </c>
       <c r="U22" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-402 · gruppo A/C come da dipendenze</t>
         </is>
       </c>
       <c r="V22" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
+          <t>metrics-observer.md, agents/metrics/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>41</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>H-703</t>
+          <t>H-610</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-18</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Gate umano sul grafo</t>
+          <t>Ruoli `e2e-designer`/`e2e-reader`</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-703</t>
+          <t>**Fase 6.** `e2e-*.md`</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Conferma di task/onde/stima prima del lancio</t>
+          <t>E2E Playwright eseguiti dal runner</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>gruppo A, H-402</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -6256,7 +6310,7 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr"/>
@@ -6283,55 +6337,55 @@
       </c>
       <c r="T23" s="10" t="inlineStr">
         <is>
-          <t>T-703</t>
+          <t>T-609</t>
         </is>
       </c>
       <c r="U23" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-402 · gruppo A/C come da dipendenze</t>
         </is>
       </c>
       <c r="V23" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
+          <t>e2e-*.md</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>42</v>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>H-704</t>
+          <t>H-601</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-18</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Orchestrazione per onde</t>
+          <t>Reviewer specializzati ECC</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-704</t>
+          <t>**Fase 6.** T-403</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Worktree e rami dedicati, parallelismo entro limiti</t>
+          <t>Lenti `ecc-*` riusate con overlay minimo (estende H-607)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>gruppo A, H-402, H-607 [P]</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -6345,7 +6399,7 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr"/>
@@ -6372,17 +6426,17 @@
       </c>
       <c r="T24" s="10" t="inlineStr">
         <is>
-          <t>T-704</t>
+          <t>T-403</t>
         </is>
       </c>
       <c r="U24" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-402, H-607 · gruppo A/C come da dipendenze</t>
         </is>
       </c>
       <c r="V24" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
+          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6449,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>H-705</t>
+          <t>H-701</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -6405,17 +6459,17 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Integrazione su SHA verde</t>
+          <t>Workflow `limet-change.js`</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-705</t>
+          <t>**Fase 7, gruppo D.** T-701</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Avanza solo con run runner sullo stesso SHA</t>
+          <t>Struttura, validazione input, stati, retry, stop-e-chiedi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -6461,7 +6515,7 @@
       </c>
       <c r="T25" s="10" t="inlineStr">
         <is>
-          <t>T-705</t>
+          <t>T-701</t>
         </is>
       </c>
       <c r="U25" s="10" t="inlineStr">
@@ -6484,7 +6538,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>H-707</t>
+          <t>H-703</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -6494,17 +6548,17 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>«Fermati e chiedi» non globale</t>
+          <t>Gate umano sul grafo</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-707</t>
+          <t>**Fase 7.** T-703</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Blocca solo i dipendenti; `QUESTIONS.md`; maxAttempts 3</t>
+          <t>Conferma di task/onde/stima prima del lancio</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -6550,7 +6604,7 @@
       </c>
       <c r="T26" s="10" t="inlineStr">
         <is>
-          <t>T-707</t>
+          <t>T-703</t>
         </is>
       </c>
       <c r="U26" s="10" t="inlineStr">
@@ -6573,7 +6627,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>H-708</t>
+          <t>H-704</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -6583,17 +6637,17 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Budget, checkpoint, ripresa</t>
+          <t>Orchestrazione per onde</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-708</t>
+          <t>**Fase 7.** T-704</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Stop controllato e `resumeFromRunId`</t>
+          <t>Worktree e rami dedicati, parallelismo entro limiti</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -6639,7 +6693,7 @@
       </c>
       <c r="T27" s="10" t="inlineStr">
         <is>
-          <t>T-708</t>
+          <t>T-704</t>
         </is>
       </c>
       <c r="U27" s="10" t="inlineStr">
@@ -6662,7 +6716,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>H-710</t>
+          <t>H-705</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -6672,17 +6726,17 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Permessi a livello di tool</t>
+          <t>Integrazione su SHA verde</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-710</t>
+          <t>**Fase 7.** T-705</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>`deny` su mvnw/push/merge, hook di log propri (estende H-404)</t>
+          <t>Avanza solo con run runner sullo stesso SHA</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -6728,7 +6782,7 @@
       </c>
       <c r="T28" s="10" t="inlineStr">
         <is>
-          <t>T-710</t>
+          <t>T-705</t>
         </is>
       </c>
       <c r="U28" s="10" t="inlineStr">
@@ -6751,27 +6805,27 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>H-706</t>
+          <t>H-707</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>PK-20</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Stato ed eventi</t>
+          <t>«Fermati e chiedi» non globale</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-706</t>
+          <t>**Fase 7.** T-707</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>`state.json`/`events.jsonl`, `STALE` dopo merge</t>
+          <t>Blocca solo i dipendenti; `QUESTIONS.md`; maxAttempts 3</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -6790,7 +6844,7 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr"/>
@@ -6817,7 +6871,7 @@
       </c>
       <c r="T29" s="10" t="inlineStr">
         <is>
-          <t>T-706</t>
+          <t>T-707</t>
         </is>
       </c>
       <c r="U29" s="10" t="inlineStr">
@@ -6827,7 +6881,7 @@
       </c>
       <c r="V29" s="10" t="inlineStr">
         <is>
-          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
+          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
         </is>
       </c>
     </row>
@@ -6840,27 +6894,27 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>H-709</t>
+          <t>H-708</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>PK-20</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Report notturno/conformità/finale</t>
+          <t>Budget, checkpoint, ripresa</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-709</t>
+          <t>**Fase 7.** T-708</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Mai «completato» se incompleto; sezione rischi H-612</t>
+          <t>Stop controllato e `resumeFromRunId`</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -6879,7 +6933,7 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr"/>
@@ -6906,7 +6960,7 @@
       </c>
       <c r="T30" s="10" t="inlineStr">
         <is>
-          <t>T-709</t>
+          <t>T-708</t>
         </is>
       </c>
       <c r="U30" s="10" t="inlineStr">
@@ -6916,7 +6970,7 @@
       </c>
       <c r="V30" s="10" t="inlineStr">
         <is>
-          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
+          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
         </is>
       </c>
     </row>
@@ -6929,27 +6983,27 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>H-711</t>
+          <t>H-710</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>PK-20</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Gate di merge R13 + bug-fix R15</t>
+          <t>Permessi a livello di tool</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-711</t>
+          <t>**Fase 7.** T-710</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Merge solo con tutti i gate; regressione fallisce prima del fix</t>
+          <t>`deny` su mvnw/push/merge, hook di log propri (estende H-404)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -6968,7 +7022,7 @@
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr"/>
@@ -6995,7 +7049,7 @@
       </c>
       <c r="T31" s="10" t="inlineStr">
         <is>
-          <t>T-711</t>
+          <t>T-710</t>
         </is>
       </c>
       <c r="U31" s="10" t="inlineStr">
@@ -7005,7 +7059,7 @@
       </c>
       <c r="V31" s="10" t="inlineStr">
         <is>
-          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
+          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7072,32 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>H-713</t>
+          <t>H-706</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>PK-19b</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Modalità non presidiata (UNATTENDED)</t>
+          <t>Stato ed eventi</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** Estende H-707/H-708. Default decisi (Q-14): `stopOnQuestions` = `false`, `maxDurationMin` = 480, nessun reperibile. T-713, E2E-AUT-1, E2E-AUT-2</t>
+          <t>**Fase 7.** T-706</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Sezione `night` in `limits.json`, macchina a stati del run, parcheggio dei dipendenti, kill switch, dead-man switch</t>
+          <t>`state.json`/`events.jsonl`, `STALE` dopo merge</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>H-706, H-707, H-708, H-710</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -7057,7 +7111,7 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr"/>
@@ -7076,7 +7130,7 @@
       <c r="Q32" s="10" t="n"/>
       <c r="R32" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003; richiesta SUPERVISORE 2026-10-30</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S32" s="12" t="n">
@@ -7084,17 +7138,17 @@
       </c>
       <c r="T32" s="10" t="inlineStr">
         <is>
-          <t>T-713, T-1, T-2</t>
+          <t>T-706</t>
         </is>
       </c>
       <c r="U32" s="10" t="inlineStr">
         <is>
-          <t>H-706, H-707, H-708, H-710</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V32" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
+          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
         </is>
       </c>
     </row>
@@ -7107,32 +7161,32 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>H-715</t>
+          <t>H-709</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>PK-19b</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Allow-list dei ruoli non presidiati</t>
+          <t>Report notturno/conformità/finale</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** Applicata dal codice, non convenzione (Q-16). T-715, E2E-AUT-1</t>
+          <t>**Fase 7.** T-709</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Solo `developer`, `tester`, `runner`, `test-reader`, `reviewer`, `metrics-observer`; al turno di un ruolo escluso il task si parcheggia con motivazione</t>
+          <t>Mai «completato» se incompleto; sezione rischi H-612</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>H-713</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -7146,7 +7200,7 @@
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr"/>
@@ -7165,7 +7219,7 @@
       <c r="Q33" s="10" t="n"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003 §5</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S33" s="12" t="n">
@@ -7173,17 +7227,17 @@
       </c>
       <c r="T33" s="10" t="inlineStr">
         <is>
-          <t>T-715, T-1</t>
+          <t>T-709</t>
         </is>
       </c>
       <c r="U33" s="10" t="inlineStr">
         <is>
-          <t>H-713</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V33" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
+          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
         </is>
       </c>
     </row>
@@ -7196,32 +7250,32 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>H-714</t>
+          <t>H-711</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>PK-20b</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Registro delle decisioni autonome</t>
+          <t>Gate di merge R13 + bug-fix R15</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** Estende H-709 (ALA R18). T-714, E2E-AUT-1</t>
+          <t>**Fase 7.** T-711</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Ogni decisione presa in autonomia registrata con evidenza e reversibilità; sezione «decisioni autonome» in `REPORT_NOTTURNO.md`</t>
+          <t>Merge solo con tutti i gate; regressione fallisce prima del fix</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>H-709, H-713</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -7254,7 +7308,7 @@
       <c r="Q34" s="10" t="n"/>
       <c r="R34" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003 §8</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S34" s="12" t="n">
@@ -7262,55 +7316,55 @@
       </c>
       <c r="T34" s="10" t="inlineStr">
         <is>
-          <t>T-714, T-1</t>
+          <t>T-711</t>
         </is>
       </c>
       <c r="U34" s="10" t="inlineStr">
         <is>
-          <t>H-709, H-713</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V34" s="10" t="inlineStr">
         <is>
-          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
+          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" s="9" t="n">
         <v>53</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi post-task (prodotto)</t>
+          <t>Modalità non presidiata (UNATTENDED)</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6, gruppo E.** T-611</t>
+          <t>**Fase 7.** Estende H-707/H-708. Default decisi (Q-14): `stopOnQuestions` = `false`, `maxDurationMin` = 480, nessun reperibile. T-713, E2E-AUT-1, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
+          <t>Sezione `night` in `limits.json`, macchina a stati del run, parcheggio dei dipendenti, kill switch, dead-man switch</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-706, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -7324,7 +7378,7 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr"/>
@@ -7343,7 +7397,7 @@
       <c r="Q35" s="10" t="n"/>
       <c r="R35" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003; richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S35" s="12" t="n">
@@ -7351,17 +7405,17 @@
       </c>
       <c r="T35" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-713, T-1, T-2</t>
         </is>
       </c>
       <c r="U35" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-706, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="V35" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
     </row>
@@ -7374,32 +7428,32 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>H-702</t>
+          <t>H-715</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Installer `limet-agents.ps1/.sh`</t>
+          <t>Allow-list dei ruoli non presidiati</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-702</t>
+          <t>**Fase 7.** Applicata dal codice, non convenzione (Q-16). T-715, E2E-AUT-1</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>`init|update` idempotente, plugin facoltativo</t>
+          <t>Solo `developer`, `tester`, `runner`, `test-reader`, `reviewer`, `metrics-observer`; al turno di un ruolo escluso il task si parcheggia con motivazione</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -7413,7 +7467,7 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr"/>
@@ -7432,7 +7486,7 @@
       <c r="Q36" s="10" t="n"/>
       <c r="R36" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §5</t>
         </is>
       </c>
       <c r="S36" s="12" t="n">
@@ -7440,17 +7494,17 @@
       </c>
       <c r="T36" s="10" t="inlineStr">
         <is>
-          <t>T-702</t>
+          <t>T-715, T-1</t>
         </is>
       </c>
       <c r="U36" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-713</t>
         </is>
       </c>
       <c r="V36" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
     </row>
@@ -7463,32 +7517,32 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>H-712</t>
+          <t>H-714</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Modifiche documentali a LIMET M.1–M.9</t>
+          <t>Registro delle decisioni autonome</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7, gruppo F.** T-712</t>
+          <t>**Fase 7.** Estende H-709 (ALA R18). T-714, E2E-AUT-1</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
+          <t>Ogni decisione presa in autonomia registrata con evidenza e reversibilità; sezione «decisioni autonome» in `REPORT_NOTTURNO.md`</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
+          <t>H-709, H-713</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -7521,7 +7575,7 @@
       <c r="Q37" s="10" t="n"/>
       <c r="R37" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §8</t>
         </is>
       </c>
       <c r="S37" s="12" t="n">
@@ -7529,55 +7583,55 @@
       </c>
       <c r="T37" s="10" t="inlineStr">
         <is>
-          <t>T-712</t>
+          <t>T-714, T-1</t>
         </is>
       </c>
       <c r="U37" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-709, H-713</t>
         </is>
       </c>
       <c r="V37" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B38" s="9" t="n">
         <v>56</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Analisi degli hook ECC</t>
+          <t>Valutazione rischi post-task (prodotto)</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
+          <t>**Fase 6, gruppo E.** T-611</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Decisione motivata per ognuno dei 27 hook</t>
+          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -7591,7 +7645,7 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr"/>
@@ -7610,7 +7664,7 @@
       <c r="Q38" s="10" t="n"/>
       <c r="R38" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO (o anticipo)</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S38" s="12" t="n">
@@ -7618,55 +7672,55 @@
       </c>
       <c r="T38" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="U38" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="V38" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>57</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>H-800b</t>
+          <t>H-702</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Replica sicura hook utili</t>
+          <t>Installer `limet-agents.ps1/.sh`</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
+          <t>**Fase 7.** T-702</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
+          <t>`init|update` idempotente, plugin facoltativo</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -7680,7 +7734,7 @@
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr"/>
@@ -7707,55 +7761,55 @@
       </c>
       <c r="T39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-702</t>
         </is>
       </c>
       <c r="U39" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V39" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>58</v>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>H-801</t>
+          <t>H-712</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Registro chiamate LLM (C05)</t>
+          <t>Modifiche documentali a LIMET M.1–M.9</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
+          <t>**Fase 7, gruppo F.** T-712</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Ogni chiamata LLM extra registrata</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -7769,7 +7823,7 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr"/>
@@ -7796,17 +7850,17 @@
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
-          <t>T-801</t>
+          <t>T-712</t>
         </is>
       </c>
       <c r="U40" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V40" s="10" t="inlineStr">
         <is>
-          <t>agents/policy/llm-registry.json</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7873,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>H-802</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -7829,22 +7883,22 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Wrapper AgentShield</t>
+          <t>Analisi degli hook ECC</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
+          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
+          <t>Decisione motivata per ognuno dei 27 hook</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -7877,7 +7931,7 @@
       <c r="Q41" s="10" t="n"/>
       <c r="R41" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO (o anticipo)</t>
         </is>
       </c>
       <c r="S41" s="12" t="n">
@@ -7885,7 +7939,7 @@
       </c>
       <c r="T41" s="10" t="inlineStr">
         <is>
-          <t>T-802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U41" s="10" t="inlineStr">
@@ -7895,7 +7949,7 @@
       </c>
       <c r="V41" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>docs/ecc-hooks-analysis.md</t>
         </is>
       </c>
     </row>
@@ -7908,32 +7962,32 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>H-803</t>
+          <t>H-800b</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Setup KB `HLS_*`</t>
+          <t>Replica sicura hook utili</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
+          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
+          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204 [P]</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -7974,17 +8028,17 @@
       </c>
       <c r="T42" s="10" t="inlineStr">
         <is>
-          <t>T-803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -7997,32 +8051,32 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>H-804</t>
+          <t>H-801</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Accesso agenti alla KB</t>
+          <t>Registro chiamate LLM (C05)</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-804</t>
+          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
+          <t>Ogni chiamata LLM extra registrata</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-611 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -8063,57 +8117,55 @@
       </c>
       <c r="T43" s="10" t="inlineStr">
         <is>
-          <t>T-804</t>
+          <t>T-801</t>
         </is>
       </c>
       <c r="U43" s="10" t="inlineStr">
         <is>
-          <t>H-611, H-803</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V43" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>agents/policy/llm-registry.json</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A44" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B44" s="9" t="n">
         <v>62</v>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-802</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>`api/` loopback e hardening</t>
+          <t>Wrapper AgentShield</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b01…T-8b04</t>
+          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
+          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -8154,57 +8206,55 @@
       </c>
       <c r="T44" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04</t>
+          <t>T-802</t>
         </is>
       </c>
       <c r="U44" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V44" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A45" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>63</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-803</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Read model derivato</t>
+          <t>Setup KB `HLS_*`</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b05</t>
+          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Cache rigenerabile, fonte unica (C27)</t>
+          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-202, H-204 [P]</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
@@ -8245,57 +8295,55 @@
       </c>
       <c r="T45" s="10" t="inlineStr">
         <is>
-          <t>T-8b05</t>
+          <t>T-803</t>
         </is>
       </c>
       <c r="U45" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-202, H-204</t>
         </is>
       </c>
       <c r="V45" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
     <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A46" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B46" s="9" t="n">
         <v>64</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>H-8b05</t>
+          <t>H-804</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Gate solo da sessione umana</t>
+          <t>Accesso agenti alla KB</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
+          <t>**Fase 8.** T-804</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git</t>
+          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-403</t>
+          <t>H-803, H-611 [P]</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -8336,17 +8384,17 @@
       </c>
       <c r="T46" s="10" t="inlineStr">
         <is>
-          <t>T-8b08</t>
+          <t>T-804</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>H-403, H-8b01</t>
+          <t>H-611, H-803</t>
         </is>
       </c>
       <c r="V46" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
@@ -8361,32 +8409,32 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>`ui/` viste</t>
+          <t>`api/` loopback e hardening</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b06</t>
+          <t>**Fase 8b.** T-8b01…T-8b04</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
+          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-303, H-401 [P]</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
@@ -8400,7 +8448,7 @@
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr"/>
@@ -8427,17 +8475,17 @@
       </c>
       <c r="T47" s="10" t="inlineStr">
         <is>
-          <t>T-8b06</t>
+          <t>T-8b01, T-8b04</t>
         </is>
       </c>
       <c r="U47" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-303, H-401</t>
         </is>
       </c>
       <c r="V47" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8452,32 +8500,32 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>H-8b04</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Vista Permessi agenti</t>
+          <t>Read model derivato</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-405, T-8b07</t>
+          <t>**Fase 8b.** T-8b05</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Conferma, motivazione, audit, rollback</t>
+          <t>Cache rigenerabile, fonte unica (C27)</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -8491,7 +8539,7 @@
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr"/>
@@ -8518,17 +8566,17 @@
       </c>
       <c r="T48" s="10" t="inlineStr">
         <is>
-          <t>T-405, T-8b07</t>
+          <t>T-8b05</t>
         </is>
       </c>
       <c r="U48" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="V48" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8543,32 +8591,32 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>H-8b06</t>
+          <t>H-8b05</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Grafica e accessibilità</t>
+          <t>Gate solo da sessione umana</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b09</t>
+          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
+          <t>La UI non esegue build/test/git</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b01, H-403</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -8582,7 +8630,7 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr"/>
@@ -8609,17 +8657,17 @@
       </c>
       <c r="T49" s="10" t="inlineStr">
         <is>
-          <t>T-8b09</t>
+          <t>T-8b08</t>
         </is>
       </c>
       <c r="U49" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-403, H-8b01</t>
         </is>
       </c>
       <c r="V49" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8682,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>H-8b07</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -8644,22 +8692,22 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>Governance dipendenze npm</t>
+          <t>`ui/` viste</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b10</t>
+          <t>**Fase 8b.** T-8b06</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Lockfile, licenze, audit, SBOM (C25)</t>
+          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -8700,12 +8748,12 @@
       </c>
       <c r="T50" s="10" t="inlineStr">
         <is>
-          <t>T-8b10</t>
+          <t>T-8b06</t>
         </is>
       </c>
       <c r="U50" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="V50" s="10" t="inlineStr">
@@ -8725,7 +8773,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>H-8b08</t>
+          <t>H-8b04</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -8735,22 +8783,22 @@
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione launcher :8799</t>
+          <t>Vista Permessi agenti</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-304</t>
+          <t>**Fase 8b.** T-405, T-8b07</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Tramite shim</t>
+          <t>Conferma, motivazione, audit, rollback</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -8791,12 +8839,12 @@
       </c>
       <c r="T51" s="10" t="inlineStr">
         <is>
-          <t>T-304</t>
+          <t>T-405, T-8b07</t>
         </is>
       </c>
       <c r="U51" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="V51" s="10" t="inlineStr">
@@ -8816,32 +8864,32 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b06</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>Grafica e accessibilità</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
+          <t>**Fase 8b.** T-8b09</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
+          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -8874,7 +8922,7 @@
       <c r="Q52" s="10" t="n"/>
       <c r="R52" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S52" s="12" t="n">
@@ -8882,17 +8930,17 @@
       </c>
       <c r="T52" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-8b09</t>
         </is>
       </c>
       <c r="U52" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V52" s="10" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
@@ -8907,32 +8955,32 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b07</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Avvio del run non presidiato dalla dashboard</t>
+          <t>Governance dipendenze npm</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
+          <t>**Fase 8b.** T-8b10</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
+          <t>Lockfile, licenze, audit, SBOM (C25)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
@@ -8965,7 +9013,7 @@
       <c r="Q53" s="10" t="n"/>
       <c r="R53" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003 §9</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S53" s="12" t="n">
@@ -8973,55 +9021,57 @@
       </c>
       <c r="T53" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b10</t>
         </is>
       </c>
       <c r="U53" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V53" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
-      <c r="A54" s="9" t="n">
-        <v>9</v>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B54" s="9" t="n">
         <v>72</v>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b08</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E ALA V1–V24</t>
+          <t>Sostituzione launcher :8799</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
+          <t>**Fase 8b.** T-304</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Catena completa su 3 OS, progetto pilota</t>
+          <t>Tramite shim</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
@@ -9035,7 +9085,7 @@
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr"/>
@@ -9062,55 +9112,57 @@
       </c>
       <c r="T54" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="U54" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="V54" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
-      <c r="A55" s="9" t="n">
-        <v>9</v>
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B55" s="9" t="n">
         <v>73</v>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>H-902</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>README e troubleshooting plugin</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `agents/plugin/README.md`</t>
+          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Installazione, configurazione, errori</t>
+          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>H-901 [P]</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
@@ -9143,7 +9195,7 @@
       <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S55" s="12" t="n">
@@ -9151,55 +9203,57 @@
       </c>
       <c r="T55" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="U55" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="V55" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md</t>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
-      <c r="A56" s="9" t="n">
-        <v>11</v>
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B56" s="9" t="n">
         <v>74</v>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>H-1101</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Manuali, NOTICE, runbook</t>
+          <t>Avvio del run non presidiato dalla dashboard</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>**Fase 11.** Revisione approvata</t>
+          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Documentazione finale</t>
+          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr">
@@ -9232,7 +9286,7 @@
       <c r="Q56" s="10" t="n"/>
       <c r="R56" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §9</t>
         </is>
       </c>
       <c r="S56" s="12" t="n">
@@ -9240,55 +9294,55 @@
       </c>
       <c r="T56" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="U56" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="V56" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="9" t="n">
         <v>75</v>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-27</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Scenari E2E ALA V1–V24</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Log immutabili, sandbox, SBOM, audit</t>
+          <t>Catena completa su 3 OS, progetto pilota</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>Fasi 5–8</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
@@ -9334,50 +9388,50 @@
       </c>
       <c r="U57" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="V57" s="10" t="inlineStr">
         <is>
-          <t>docs/audit-hardening.md</t>
+          <t>E2E_VERIFICATION.md</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B58" s="9" t="n">
         <v>76</v>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>H-1201</t>
+          <t>H-902</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>PK-30</t>
+          <t>PK-28</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Rollout sul pilota</t>
+          <t>README e troubleshooting plugin</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>**Fase 12.** Parere legale **[N]**</t>
+          <t>**Fase 9.** `agents/plugin/README.md`</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Metriche, rollback, parere legale</t>
+          <t>Installazione, configurazione, errori</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>H-1001, H-1101</t>
+          <t>H-901 [P]</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
@@ -9423,21 +9477,288 @@
       </c>
       <c r="U58" s="10" t="inlineStr">
         <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V58" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="58" customHeight="1">
+      <c r="A59" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>H-1101</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Manuali, NOTICE, runbook</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 11.** Revisione approvata</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Documentazione finale</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J59" s="9">
+        <f>IF(I59="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr"/>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O59" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V59" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Log immutabili, sandbox, SBOM, audit</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J60" s="9">
+        <f>IF(I60="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="10" t="inlineStr"/>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U60" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V60" s="10" t="inlineStr">
+        <is>
+          <t>docs/audit-hardening.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="58" customHeight="1">
+      <c r="A61" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>H-1201</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>PK-30</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 12.** Parere legale **[N]**</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>Metriche, rollback, parere legale</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
           <t>H-1001, H-1101</t>
         </is>
       </c>
-      <c r="V58" s="10" t="inlineStr">
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J61" s="9">
+        <f>IF(I61="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr"/>
+      <c r="M61" s="10" t="inlineStr"/>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O61" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U61" s="10" t="inlineStr">
+        <is>
+          <t>H-1001, H-1101</t>
+        </is>
+      </c>
+      <c r="V61" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V58"/>
+  <autoFilter ref="A4:V61"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:S58">
+  <conditionalFormatting sqref="A5:S61">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($S5=1,$I5&lt;&gt;"Fatto")</formula>
     </cfRule>
@@ -9445,7 +9766,7 @@
       <formula>$I5="Fatto"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I58">
+  <conditionalFormatting sqref="I5:I61">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -9462,7 +9783,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K58">
+  <conditionalFormatting sqref="K5:K61">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
@@ -9473,7 +9794,7 @@
       <formula>"SUPERVISORE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S58">
+  <conditionalFormatting sqref="S5:S61">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -9483,19 +9804,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="I5:I58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Da fare,In corso,In review,Fatto,Bloccato"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NARO,SCIBETTA,SUPERVISORE,Da assegnare"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,M,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="S5:S61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -9511,7 +9832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9638,15 +9959,15 @@
         </is>
       </c>
       <c r="E5" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D58,A5)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D61,A5)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A5,'Post-GO'!I5:I58,"In review")+F5&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"In review")+F5&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -9707,15 +10028,15 @@
         </is>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D58,A6)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D61,A6)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A6,'Post-GO'!I5:I58,"In review")+F6&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"In review")+F6&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -9776,15 +10097,15 @@
         </is>
       </c>
       <c r="E7" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D58,A7)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D61,A7)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A7,'Post-GO'!I5:I58,"In review")+F7&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"In review")+F7&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -9845,15 +10166,15 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D58,A8)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D61,A8)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A8,'Post-GO'!I5:I58,"In review")+F8&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"In review")+F8&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -9914,15 +10235,15 @@
         </is>
       </c>
       <c r="E9" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D58,A9)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D61,A9)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A9,'Post-GO'!I5:I58,"In review")+F9&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"In review")+F9&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -9983,15 +10304,15 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D58,A10)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D61,A10)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A10,'Post-GO'!I5:I58,"In review")+F10&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"In review")+F10&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -10052,15 +10373,15 @@
         </is>
       </c>
       <c r="E11" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D58,A11)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D61,A11)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A11,'Post-GO'!I5:I58,"In review")+F11&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"In review")+F11&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -10121,15 +10442,15 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D58,A12)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D61,A12)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A12,'Post-GO'!I5:I58,"In review")+F12&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"In review")+F12&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -10190,15 +10511,15 @@
         </is>
       </c>
       <c r="E13" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D58,A13)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D61,A13)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A13,'Post-GO'!I5:I58,"In review")+F13&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"In review")+F13&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -10259,15 +10580,15 @@
         </is>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D58,A14)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D61,A14)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A14,'Post-GO'!I5:I58,"In review")+F14&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"In review")+F14&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -10328,15 +10649,15 @@
         </is>
       </c>
       <c r="E15" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D58,A15)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D61,A15)</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A15,'Post-GO'!I5:I58,"In review")+F15&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"In review")+F15&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -10397,15 +10718,15 @@
         </is>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D58,A16)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D61,A16)</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A16,'Post-GO'!I5:I58,"In review")+F16&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"In review")+F16&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -10466,15 +10787,15 @@
         </is>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D58,A17)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D61,A17)</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A17,'Post-GO'!I5:I58,"In review")+F17&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"In review")+F17&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -10535,15 +10856,15 @@
         </is>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D58,A18)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D61,A18)</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A18,'Post-GO'!I5:I58,"In review")+F18&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"In review")+F18&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -10604,15 +10925,15 @@
         </is>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D58,A19)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D61,A19)</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A19,'Post-GO'!I5:I58,"In review")+F19&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"In review")+F19&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -10673,15 +10994,15 @@
         </is>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D58,A20)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D61,A20)</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A20,'Post-GO'!I5:I58,"In review")+F20&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"In review")+F20&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -10742,15 +11063,15 @@
         </is>
       </c>
       <c r="E21" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D58,A21)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D61,A21)</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G21" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A21,'Post-GO'!I5:I58,"In review")+F21&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"In review")+F21&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -10811,15 +11132,15 @@
         </is>
       </c>
       <c r="E22" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D58,A22)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D61,A22)</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G22" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A22,'Post-GO'!I5:I58,"In review")+F22&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"In review")+F22&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -10880,15 +11201,15 @@
         </is>
       </c>
       <c r="E23" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D58,A23)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D61,A23)</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G23" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A23,'Post-GO'!I5:I58,"In review")+F23&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"In review")+F23&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -10930,7 +11251,7 @@
     <row r="24" ht="62" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16b</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -10940,24 +11261,24 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Ruoli di sviluppo</t>
+          <t>Architettura viva (documenti + test di integrita)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>H-602, H-603, H-604, H-605</t>
+          <t>H-504</t>
         </is>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D58,A24)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D61,A24)</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A24,'Post-GO'!I5:I58,"In review")+F24&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"In review")+F24&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -10967,39 +11288,39 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S8b</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>T-601, T-602, T-603, T-604</t>
+          <t>T-504</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/{analyst,developer,tester,integrator}.md</t>
+          <t>docs-limet/architecture.md, docs-limet/module-map.md, tests/test_architecture_docs.py</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>PK-14, PK-15, PK-09</t>
+          <t>GO; PK-14</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>PK-16, PK-18</t>
+          <t>PK-16, PK-17</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>Stessa cartella di PK-18 ma file distinti.</t>
+          <t>Aggiornamento obbligatorio alla chiusura di ogni fase successiva (6, 7, 8, 8b, 9): non e' un documento una tantum. Indicizzati in CRB_helios (re-index a cura del SUPERVISORE). Verifica: T-504.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="62" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PK-18</t>
+          <t>PK-16c</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -11009,24 +11330,24 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Ruoli di controllo</t>
+          <t>Guida d'uso e documenti di contesto per gli agenti</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>H-606, H-607, H-608, H-609, H-610, H-601</t>
+          <t>H-505, H-506</t>
         </is>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D58,A25)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D61,A25)</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A25,'Post-GO'!I5:I58,"In review")+F25&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"In review")+F25&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -11036,66 +11357,66 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>N9</t>
+          <t>N8b</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>T-605, T-606, T-607, T-608, T-609, T-403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
+          <t>docs/USER_GUIDE.md, docs-limet/glossary.md, docs-limet/conventions.md, docs-limet/NON_TECHNICAL_SUMMARY.md</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>PK-14, PK-15, PK-09</t>
+          <t>PK-16b (H-504); H-505 dopo H-407</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>PK-17</t>
+          <t>PK-16b, PK-18</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>Stessa cartella di PK-17 ma file distinti.</t>
+          <t>USER_GUIDE.md e' per chi USA HELIOS, distinto da guides/ (collaboratori) e dal README del plugin (H-902, PK-28). Verifica: comandi eseguiti davvero (V13) e quattro criteri binari per H-506.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 4 (dopo GO)</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Workflow core e permessi tool</t>
+          <t>Ruoli di sviluppo</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>H-701, H-703, H-704, H-705, H-707, H-708, H-710</t>
+          <t>H-602, H-603, H-604, H-605</t>
         </is>
       </c>
       <c r="E26" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D58,A26)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D61,A26)</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A26,'Post-GO'!I5:I58,"In review")+F26&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"In review")+F26&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -11105,66 +11426,66 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>T-701, T-703, T-704, T-705, T-707, T-708, T-710</t>
+          <t>T-601, T-602, T-603, T-604</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
+          <t>agents/plugin/agents/{analyst,developer,tester,integrator}.md</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-18, H-407</t>
+          <t>PK-14, PK-15, PK-09</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>PK-20, PK-22</t>
+          <t>PK-16, PK-18</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>[N] se limet-change.js è un file unico va scritto da una sola persona (SCIBETTA).</t>
+          <t>Stessa cartella di PK-18 ma file distinti.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="62" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PK-20</t>
+          <t>PK-18</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 4 (dopo GO)</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Stato/eventi, report e gate di merge</t>
+          <t>Ruoli di controllo</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>H-706, H-709, H-711</t>
+          <t>H-606, H-607, H-608, H-609, H-610, H-601</t>
         </is>
       </c>
       <c r="E27" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D58,A27)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D61,A27)</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A27,'Post-GO'!I5:I58,"In review")+F27&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"In review")+F27&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -11174,66 +11495,66 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N9</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>T-706, T-709, T-711</t>
+          <t>T-605, T-606, T-607, T-608, T-609, T-403</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
+          <t>agents/plugin/agents/{test-reader,reviewer,validator,metrics-observer,e2e-designer,e2e-reader}.md, agents/metrics/</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-18, H-407</t>
+          <t>PK-14, PK-15, PK-09</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-17</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto state.json / events.jsonl di H-308. NARO non modifica limet-change.js.</t>
+          <t>Stessa cartella di PK-17 ma file distinti.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="62" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PK-19b</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Onda 5+ (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Modalità non presidiata: motore e allow-list dei ruoli</t>
+          <t>Workflow core e permessi tool</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-715</t>
+          <t>H-701, H-703, H-704, H-705, H-707, H-708, H-710</t>
         </is>
       </c>
       <c r="E28" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D58,A28)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D61,A28)</f>
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G28" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A28,'Post-GO'!I5:I58,"In review")+F28&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"In review")+F28&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -11243,66 +11564,66 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>S9b</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>T-713, T-1, T-2, T-715</t>
+          <t>T-701, T-703, T-704, T-705, T-707, T-708, T-710</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
+          <t>agents/plugin/ (limet-change.js, [N] file per onde/gate), agents/policy/</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>PK-19 (H-707, H-708), PK-20 (H-706), PK-21 (H-612)</t>
+          <t>PK-14…PK-18, H-407</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>PK-20b</t>
+          <t>PK-20, PK-22</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>ADR 0003. **Neutralità dei permessi**: la modalità non amplia MAI i permessi (C02, C24, pavimento H-404). Stessi file di PK-19: stessa persona. Verifica: T-713, T-715, E2E-AUT-1, E2E-AUT-2.</t>
+          <t>[N] se limet-change.js è un file unico va scritto da una sola persona (SCIBETTA).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="62" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PK-20b</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Onda 5+ (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Registro delle decisioni autonome e report notturno</t>
+          <t>Stato/eventi, report e gate di merge</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>H-714</t>
+          <t>H-706, H-709, H-711</t>
         </is>
       </c>
       <c r="E29" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D58,A29)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D61,A29)</f>
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G29" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A29,'Post-GO'!I5:I58,"In review")+F29&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"In review")+F29&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -11312,135 +11633,135 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>N10b</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>T-714, T-1</t>
+          <t>T-706, T-709, T-711</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
+          <t>[N] file di stato, report e gate di merge (da fissare in H-308/H-701)</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>PK-19b (H-713), PK-20 (H-709)</t>
+          <t>PK-14…PK-18, H-407</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>PK-19b</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>ADR 0003 §8 (prova a posteriori, R18). Contatto: formato del registro definito in H-713. Verifica: T-714, E2E-AUT-1.</t>
+          <t>Contatto: contratto state.json / events.jsonl di H-308. NARO non modifica limet-change.js.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="62" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi di prodotto (C28)</t>
+          <t>Modalità non presidiata: motore e allow-list dei ruoli</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-713, H-715</t>
         </is>
       </c>
       <c r="E30" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D58,A30)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D61,A30)</f>
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G30" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A30,'Post-GO'!I5:I58,"In review")+F30&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"In review")+F30&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>S9b</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-713, T-1, T-2, T-715</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (sezione night di limits.json, macchina a stati, kill switch, dead-man switch), agents/policy/ (allow-list ruoli)</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
+          <t>PK-19 (H-707, H-708), PK-20 (H-706), PK-21 (H-612)</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>PK-23, PK-24, PK-25</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>risk-assessor ≠ developer, sola lettura.</t>
+          <t>ADR 0003. **Neutralità dei permessi**: la modalità non amplia MAI i permessi (C02, C24, pavimento H-404). Stessi file di PK-19: stessa persona. Verifica: T-713, T-715, E2E-AUT-1, E2E-AUT-2.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="62" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-20b</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Installer e modifiche documentali a LIMET</t>
+          <t>Registro delle decisioni autonome e report notturno</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>H-702, H-712</t>
+          <t>H-714</t>
         </is>
       </c>
       <c r="E31" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D58,A31)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D61,A31)</f>
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G31" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A31,'Post-GO'!I5:I58,"In review")+F31&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"In review")+F31&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -11450,177 +11771,177 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N10b</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>T-702, T-712</t>
+          <t>T-714, T-1</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>[N] registro decisioni autonome, REPORT_NOTTURNO.md (sezione «decisioni autonome»)</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
+          <t>PK-19b (H-713), PK-20 (H-709)</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-19b</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
+          <t>ADR 0003 §8 (prova a posteriori, R18). Contatto: formato del registro definito in H-713. Verifica: T-714, E2E-AUT-1.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="62" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Hook ECC e registro chiamate LLM</t>
+          <t>Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>H-800, H-800b, H-801, H-802</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="E32" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D58,A32)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D61,A32)</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G32" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A32,'Post-GO'!I5:I58,"In review")+F32&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"In review")+F32&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>T-801, T-802</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-08</t>
+          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-22</t>
+          <t>PK-23, PK-24, PK-25</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
+          <t>risk-assessor ≠ developer, sola lettura.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="62" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Knowledge base HLS_* e accesso agenti</t>
+          <t>Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-804</t>
+          <t>H-702, H-712</t>
         </is>
       </c>
       <c r="E33" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D58,A33)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D61,A33)</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G33" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A33,'Post-GO'!I5:I58,"In review")+F33&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"In review")+F33&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>T-803, T-804</t>
+          <t>T-702, T-712</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>PK-03, PK-15</t>
+          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -11630,24 +11951,24 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>API loopback e read model</t>
+          <t>Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-8b02, H-8b05</t>
+          <t>H-800, H-800b, H-801, H-802</t>
         </is>
       </c>
       <c r="E34" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D58,A34)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D61,A34)</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G34" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A34,'Post-GO'!I5:I58,"In review")+F34&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"In review")+F34&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -11657,204 +11978,204 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
+          <t>T-801, T-802</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-06, PK-08</t>
+          <t>GO; PK-08</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>PK-26 (dopo contratto API)</t>
+          <t>PK-14…PK-22</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
+          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="62" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Onda 4+ (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
+          <t>H-803, H-804</t>
         </is>
       </c>
       <c r="E35" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D58,A35)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D61,A35)</f>
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G35" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A35,'Post-GO'!I5:I58,"In review")+F35&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"In review")+F35&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>N13</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
+          <t>T-803, T-804</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>PK-25, PK-08, PK-06</t>
+          <t>PK-03, PK-15</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>PK-25 (dopo contratto API)</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git (C23–C24).</t>
+          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Onda 4+ (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>API loopback e read model</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b01, H-8b02, H-8b05</t>
         </is>
       </c>
       <c r="E36" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D58,A36)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D61,A36)</f>
         <v/>
       </c>
       <c r="F36" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G36" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A36,'Post-GO'!I5:I58,"In review")+F36&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"In review")+F36&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>N13b</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
+          <t>api/</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
+          <t>GO; PK-06, PK-08</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PK-26 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
+          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="62" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Onda 5+ (dopo GO)</t>
+          <t>Onda 4+ (dopo GO)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Pannello di avvio del run non presidiato</t>
+          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
         </is>
       </c>
       <c r="E37" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D58,A37)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D61,A37)</f>
         <v/>
       </c>
       <c r="F37" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G37" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A37,'Post-GO'!I5:I58,"In review")+F37&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"In review")+F37&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -11864,135 +12185,135 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>N13c</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
+          <t>PK-25, PK-08, PK-06</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PK-25 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
+          <t>La UI non esegue build/test/git (C23–C24).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="62" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 4+ (dopo GO)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E V1–V24</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="E38" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D58,A38)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D61,A38)</f>
         <v/>
       </c>
       <c r="F38" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G38" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A38,'Post-GO'!I5:I58,"In review")+F38&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"In review")+F38&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>N13b</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
+          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>README plugin e manuali</t>
+          <t>Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>H-902, H-1101</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="E39" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D58,A39)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D61,A39)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A39,'Post-GO'!I5:I58,"In review")+F39&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"In review")+F39&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -12002,66 +12323,66 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>N14</t>
+          <t>N13c</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>Revisione approvata dal SUPERVISORE.</t>
+          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-27</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Onda 8 (dopo GO)</t>
+          <t>Onda 7 (dopo GO)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Scenari E2E V1–V24</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="E40" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D58,A40)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D61,A40)</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"Fatto")</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A40,'Post-GO'!I5:I58,"In review")+F40&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"In review")+F40&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -12071,7 +12392,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
@@ -12081,12 +12402,12 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>[N] log immutabili, sandbox, SBOM</t>
+          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>Fasi 5–8</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -12096,86 +12417,224 @@
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>README plugin e manuali</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>H-902, H-1101</t>
+        </is>
+      </c>
+      <c r="E41" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D61,A41)</f>
+        <v/>
+      </c>
+      <c r="F41" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G41" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"In review")+F41&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>Revisione approvata dal SUPERVISORE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="62" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Onda 8 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="E42" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A42)+COUNTIF('Post-GO'!D5:D61,A42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G42" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F42=E42,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"In review")+F42&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>[N] log immutabili, sandbox, SBOM</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
           <t>PK-30</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Onda 9 (dopo GO)</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Rollout sul pilota</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>H-1201</t>
         </is>
       </c>
-      <c r="E41" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D58,A41)</f>
-        <v/>
-      </c>
-      <c r="F41" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G41" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D58,A41,'Post-GO'!I5:I58,"In review")+F41&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="E43" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A43)+COUNTIF('Post-GO'!D5:D61,A43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G43" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F43=E43,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"In review")+F43&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>NARO</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>N15</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>PK-28, PK-29</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>[N] parere legale; pilota da scegliere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N41"/>
+  <autoFilter ref="A4:N43"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G41">
+  <conditionalFormatting sqref="G5:G43">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -12189,7 +12648,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H41">
+  <conditionalFormatting sqref="H5:H43">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>

--- a/log/HELIOS_Distribuzione_task.xlsx
+++ b/log/HELIOS_Distribuzione_task.xlsx
@@ -13069,7 +13069,7 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>Foglio di distribuzione e tracciamento dei task H-xxx tra NARO e SCIBETTA (Pre-GO / Post-GO / Pacchetti). Fonte: TASK_LIST.md, PLAN_helios-poc.md (§5.4–5.5), TEST_PLAN.md in limet/changes/0001-helios-poc/.</t>
+          <t>Foglio di distribuzione e tracciamento dei task H-xxx tra NARO e SCIBETTA (Pre-GO / Post-GO / Pacchetti). Fonte: TASK_LIST.md, PLAN_helios.md (§5.4–5.5), TEST_PLAN.md in limet/changes/0001-helios/.</t>
         </is>
       </c>
     </row>

--- a/log/HELIOS_Distribuzione_task.xlsx
+++ b/log/HELIOS_Distribuzione_task.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-GO'!$A$4:$V$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIF('Post-GO'!I5:I61,A4)</f>
+        <f>COUNTIF('Post-GO'!I5:I62,A4)</f>
         <v/>
       </c>
       <c r="D4">
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIF('Post-GO'!I5:I61,A5)</f>
+        <f>COUNTIF('Post-GO'!I5:I62,A5)</f>
         <v/>
       </c>
       <c r="D5">
@@ -677,7 +677,7 @@
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIF('Post-GO'!I5:I61,A6)</f>
+        <f>COUNTIF('Post-GO'!I5:I62,A6)</f>
         <v/>
       </c>
       <c r="D6">
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIF('Post-GO'!I5:I61,A7)</f>
+        <f>COUNTIF('Post-GO'!I5:I62,A7)</f>
         <v/>
       </c>
       <c r="D7">
@@ -715,7 +715,7 @@
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIF('Post-GO'!I5:I61,A8)</f>
+        <f>COUNTIF('Post-GO'!I5:I62,A8)</f>
         <v/>
       </c>
       <c r="D8">
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIF('Post-GO'!K5:K61,A14)</f>
+        <f>COUNTIF('Post-GO'!K5:K62,A14)</f>
         <v/>
       </c>
       <c r="D14">
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A14,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A14,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIF('Post-GO'!K5:K61,A15)</f>
+        <f>COUNTIF('Post-GO'!K5:K62,A15)</f>
         <v/>
       </c>
       <c r="D15">
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A15,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A15,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIF('Post-GO'!K5:K61,A16)</f>
+        <f>COUNTIF('Post-GO'!K5:K62,A16)</f>
         <v/>
       </c>
       <c r="D16">
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A16,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A16,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIF('Post-GO'!K5:K61,A17)</f>
+        <f>COUNTIF('Post-GO'!K5:K62,A17)</f>
         <v/>
       </c>
       <c r="D17">
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K61,A17,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A17,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D61,"PK-00")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D62,"PK-00")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-00",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="B22">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D61,"PK-01")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D62,"PK-01")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-01",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B23">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D61,"PK-02")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D62,"PK-02")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-02",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B24">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D61,"PK-03")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D62,"PK-03")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-03",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B25">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D61,"PK-04")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D62,"PK-04")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-04",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B26">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D61,"PK-05")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D62,"PK-05")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-05",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="B27">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D61,"PK-05b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D62,"PK-05b")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-05b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="B28">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D61,"PK-06")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D62,"PK-06")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-06",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B29">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D61,"PK-07")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D62,"PK-07")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-07",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="B30">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D61,"PK-07b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D62,"PK-07b")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-07b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -1189,19 +1189,19 @@
         </is>
       </c>
       <c r="B31">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D61,"PK-08")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D62,"PK-08")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-08",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B32">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D61,"PK-09")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D62,"PK-09")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-09",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D61,"PK-10")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D62,"PK-10")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-10",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D61,"PK-11")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D62,"PK-11")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-11",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D61,"PK-12")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D62,"PK-12")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-12",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D61,"PK-13")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D62,"PK-13")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-13",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D61,"PK-14")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D62,"PK-14")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-14",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="B38">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D61,"PK-15")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D62,"PK-15")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-15",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F38" s="5">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="B39">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D61,"PK-16")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D62,"PK-16")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F39" s="5">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="B40">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16b")+COUNTIF('Post-GO'!D5:D61,"PK-16b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16b")+COUNTIF('Post-GO'!D5:D62,"PK-16b")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F40" s="5">
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="B41">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16c")+COUNTIF('Post-GO'!D5:D61,"PK-16c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16c")+COUNTIF('Post-GO'!D5:D62,"PK-16c")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-16c",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F41" s="5">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B42">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D61,"PK-17")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D62,"PK-17")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-17",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F42" s="5">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="B43">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D61,"PK-18")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D62,"PK-18")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-18",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F43" s="5">
@@ -1540,19 +1540,19 @@
         </is>
       </c>
       <c r="B44">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D61,"PK-19")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D62,"PK-19")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-19",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F44" s="5">
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B45">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D61,"PK-20")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D62,"PK-20")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-20",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F45" s="5">
@@ -1594,19 +1594,19 @@
         </is>
       </c>
       <c r="B46">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D61,"PK-19b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D62,"PK-19b")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-19b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F46" s="5">
@@ -1621,19 +1621,19 @@
         </is>
       </c>
       <c r="B47">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D61,"PK-20b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D62,"PK-20b")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-20b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F47" s="5">
@@ -1644,23 +1644,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
+          <t>PK-19c · Ciclo di rilavorazione dei findings di code review</t>
         </is>
       </c>
       <c r="B48">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D61,"PK-21")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19c")+COUNTIF('Post-GO'!D5:D62,"PK-19c")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-21",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F48" s="5">
@@ -1671,23 +1671,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
+          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="B49">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D61,"PK-22")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D62,"PK-21")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-22",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F49" s="5">
@@ -1698,23 +1698,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
+          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="B50">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D61,"PK-23")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D62,"PK-22")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-23",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F50" s="5">
@@ -1725,23 +1725,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
+          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D61,"PK-24")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D62,"PK-23")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-24",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F51" s="5">
@@ -1752,23 +1752,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PK-25 · API loopback e read model</t>
+          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D61,"PK-25")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D62,"PK-24")</f>
         <v/>
       </c>
       <c r="C52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-25",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F52" s="5">
@@ -1779,23 +1779,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>PK-25 · API loopback e read model</t>
         </is>
       </c>
       <c r="B53">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D61,"PK-26")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D62,"PK-25")</f>
         <v/>
       </c>
       <c r="C53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F53" s="5">
@@ -1806,23 +1806,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
+          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="B54">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D61,"PK-26b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D62,"PK-26")</f>
         <v/>
       </c>
       <c r="C54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26b",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F54" s="5">
@@ -1833,23 +1833,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PK-26c · Pannello di avvio del run non presidiato</t>
+          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="B55">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D61,"PK-26c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D62,"PK-26b")</f>
         <v/>
       </c>
       <c r="C55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-26c",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F55" s="5">
@@ -1860,23 +1860,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PK-27 · Scenari E2E V1–V24</t>
+          <t>PK-26c · Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="B56">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D61,"PK-27")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D62,"PK-26c")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-27",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F56" s="5">
@@ -1887,23 +1887,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PK-28 · README plugin e manuali</t>
+          <t>PK-27 · Scenari E2E V1–V24</t>
         </is>
       </c>
       <c r="B57">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D61,"PK-28")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D62,"PK-27")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-28",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F57" s="5">
@@ -1914,23 +1914,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PK-29 · Hardening</t>
+          <t>PK-28 · README plugin e manuali</t>
         </is>
       </c>
       <c r="B58">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D61,"PK-29")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D62,"PK-28")</f>
         <v/>
       </c>
       <c r="C58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-29",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F58" s="5">
@@ -1941,23 +1941,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PK-30 · Rollout sul pilota</t>
+          <t>PK-29 · Hardening</t>
         </is>
       </c>
       <c r="B59">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D61,"PK-30")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D62,"PK-29")</f>
         <v/>
       </c>
       <c r="C59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D61,"PK-30",'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F59" s="5">
@@ -1965,88 +1965,90 @@
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PK-30 · Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="B60">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D62,"PK-30")</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F60" s="5">
+        <f>IF(B60=0,0,C60/B60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Avanzamento per fase</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Fatti</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>In corso</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63)+COUNTIFS('Post-GO'!A5:A61,$A63)</f>
-        <v/>
-      </c>
-      <c r="C63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E63">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A63,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A63,'Post-GO'!I5:I61,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F63" s="5">
-        <f>IF(B63=0,0,C63/B63)</f>
-        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A61,$A64)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A62,$A64)</f>
         <v/>
       </c>
       <c r="C64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A64,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F64" s="5">
@@ -2056,22 +2058,22 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A61,$A65)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A62,$A65)</f>
         <v/>
       </c>
       <c r="C65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A65,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F65" s="5">
@@ -2081,22 +2083,22 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A61,$A66)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A62,$A66)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A66,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F66" s="5">
@@ -2106,22 +2108,22 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A61,$A67)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A62,$A67)</f>
         <v/>
       </c>
       <c r="C67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A67,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F67" s="5">
@@ -2131,22 +2133,22 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A61,$A68)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A62,$A68)</f>
         <v/>
       </c>
       <c r="C68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A68,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F68" s="5">
@@ -2156,22 +2158,22 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A61,$A69)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A62,$A69)</f>
         <v/>
       </c>
       <c r="C69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A69,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F69" s="5">
@@ -2181,22 +2183,22 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A61,$A70)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A62,$A70)</f>
         <v/>
       </c>
       <c r="C70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A70,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F70" s="5">
@@ -2205,25 +2207,23 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A71" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="B71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A61,$A71)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A62,$A71)</f>
         <v/>
       </c>
       <c r="C71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A71,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F71" s="5">
@@ -2232,23 +2232,25 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n">
-        <v>9</v>
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A61,$A72)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A62,$A72)</f>
         <v/>
       </c>
       <c r="C72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A72,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F72" s="5">
@@ -2258,22 +2260,22 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A61,$A73)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A62,$A73)</f>
         <v/>
       </c>
       <c r="C73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A73,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F73" s="5">
@@ -2283,22 +2285,22 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74)+COUNTIFS('Post-GO'!A5:A61,$A74)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74)+COUNTIFS('Post-GO'!A5:A62,$A74)</f>
         <v/>
       </c>
       <c r="C74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A74,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F74" s="5">
@@ -2308,26 +2310,51 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75)+COUNTIFS('Post-GO'!A5:A61,$A75)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75)+COUNTIFS('Post-GO'!A5:A62,$A75)</f>
         <v/>
       </c>
       <c r="C75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="D75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"In corso")</f>
         <v/>
       </c>
       <c r="E75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A61,$A75,'Post-GO'!I5:I61,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"Da fare")</f>
         <v/>
       </c>
       <c r="F75" s="5">
         <f>IF(B75=0,0,C75/B75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B76">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76)+COUNTIFS('Post-GO'!A5:A62,$A76)</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>IF(B76=0,0,C76/B76)</f>
         <v/>
       </c>
     </row>
@@ -2344,7 +2371,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F59">
+  <conditionalFormatting sqref="F21:F60">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2353,7 +2380,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F63:F75">
+  <conditionalFormatting sqref="F64:F76">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4499,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4540,11 +4567,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(I5:I61,"Fatto")/COUNTA(C5:C61)</f>
+        <f>COUNTIF(I5:I62,"Fatto")/COUNTA(C5:C62)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(I5:I61,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C61)&amp;" task · "&amp;COUNTIF(I5:I61,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I61,"Bloccato")&amp;" bloccati"</f>
+        <f>COUNTIF(I5:I62,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C62)&amp;" task · "&amp;COUNTIF(I5:I62,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I62,"Bloccato")&amp;" bloccati"</f>
         <v/>
       </c>
     </row>
@@ -6024,7 +6051,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Findings con severità/file/riga; non corregge</t>
+          <t>Findings con severità/file/riga **dall'enum di H-308** (Q-19); assegna la severità, **non decide cosa blocca**; non corregge; **può essere richiamato** sullo stesso task ai giri di rilavorazione (Q-20), dove verifica i *propri* findings e apre nuovi findings solo sul diff della correzione</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -7092,7 +7119,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>`state.json`/`events.jsonl`, `STALE` dopo merge</t>
+          <t>`state.json`/`events.jsonl`, `STALE` dopo merge; lo stato include il **contatore dei giri di revisione** (Q-20), distinto da `maxAttempts`</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -7270,7 +7297,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Merge solo con tutti i gate; regressione fallisce prima del fix</t>
+          <t>Merge solo con tutti i gate; regressione fallisce prima del fix; **soglia di severità letta dalla policy** (Q-19)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -7599,39 +7626,39 @@
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="9" t="n">
         <v>56</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-716</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19c</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi post-task (prodotto)</t>
+          <t>Ciclo di rilavorazione dei findings</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6, gruppo E.** T-611</t>
+          <t>**Fase 7.** Contatore **distinto** da R12 `maxAttempts`. T-716, E2E-REV-1</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
+          <t>`reviewer → developer → reviewer`, **max 2 correzioni**; al superamento `WAITING_SUPERVISOR`</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-607, H-711, H-308, H-706</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -7645,7 +7672,7 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr"/>
@@ -7664,7 +7691,7 @@
       <c r="Q38" s="10" t="n"/>
       <c r="R38" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Q-20. Dopo GO</t>
         </is>
       </c>
       <c r="S38" s="12" t="n">
@@ -7672,55 +7699,55 @@
       </c>
       <c r="T38" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-716</t>
         </is>
       </c>
       <c r="U38" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-308, H-607, H-706, H-711</t>
         </is>
       </c>
       <c r="V38" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (ciclo reviewer-&gt;developer-&gt;reviewer, contatore dei giri), agents/policy/ (tetto dei giri)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>57</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>H-702</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Installer `limet-agents.ps1/.sh`</t>
+          <t>Valutazione rischi post-task (prodotto)</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-702</t>
+          <t>**Fase 6, gruppo E.** T-611</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>`init|update` idempotente, plugin facoltativo</t>
+          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -7761,17 +7788,17 @@
       </c>
       <c r="T39" s="10" t="inlineStr">
         <is>
-          <t>T-702</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="U39" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="V39" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7811,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>H-712</t>
+          <t>H-702</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -7794,22 +7821,22 @@
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Modifiche documentali a LIMET M.1–M.9</t>
+          <t>Installer `limet-agents.ps1/.sh`</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7, gruppo F.** T-712</t>
+          <t>**Fase 7.** T-702</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
+          <t>`init|update` idempotente, plugin facoltativo</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -7850,7 +7877,7 @@
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
-          <t>T-712</t>
+          <t>T-702</t>
         </is>
       </c>
       <c r="U40" s="10" t="inlineStr">
@@ -7866,39 +7893,39 @@
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41" s="9" t="n">
         <v>59</v>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-712</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Analisi degli hook ECC</t>
+          <t>Modifiche documentali a LIMET M.1–M.9</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
+          <t>**Fase 7, gruppo F.** T-712</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Decisione motivata per ognuno dei 27 hook</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
+          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -7912,7 +7939,7 @@
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr"/>
@@ -7931,7 +7958,7 @@
       <c r="Q41" s="10" t="n"/>
       <c r="R41" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO (o anticipo)</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S41" s="12" t="n">
@@ -7939,17 +7966,17 @@
       </c>
       <c r="T41" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-712</t>
         </is>
       </c>
       <c r="U41" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V41" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7989,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>H-800b</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -7972,22 +7999,22 @@
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Replica sicura hook utili</t>
+          <t>Analisi degli hook ECC</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
+          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
+          <t>Decisione motivata per ognuno dei 27 hook</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -8020,7 +8047,7 @@
       <c r="Q42" s="10" t="n"/>
       <c r="R42" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO (o anticipo)</t>
         </is>
       </c>
       <c r="S42" s="12" t="n">
@@ -8033,12 +8060,12 @@
       </c>
       <c r="U42" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>docs/ecc-hooks-analysis.md</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8078,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>H-801</t>
+          <t>H-800b</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -8061,22 +8088,22 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Registro chiamate LLM (C05)</t>
+          <t>Replica sicura hook utili</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
+          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Ogni chiamata LLM extra registrata</t>
+          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -8117,17 +8144,17 @@
       </c>
       <c r="T43" s="10" t="inlineStr">
         <is>
-          <t>T-801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="V43" s="10" t="inlineStr">
         <is>
-          <t>agents/policy/llm-registry.json</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8167,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>H-802</t>
+          <t>H-801</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -8150,17 +8177,17 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Wrapper AgentShield</t>
+          <t>Registro chiamate LLM (C05)</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
+          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
+          <t>Ogni chiamata LLM extra registrata</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -8206,7 +8233,7 @@
       </c>
       <c r="T44" s="10" t="inlineStr">
         <is>
-          <t>T-802</t>
+          <t>T-801</t>
         </is>
       </c>
       <c r="U44" s="10" t="inlineStr">
@@ -8216,7 +8243,7 @@
       </c>
       <c r="V44" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>agents/policy/llm-registry.json</t>
         </is>
       </c>
     </row>
@@ -8229,32 +8256,32 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>H-803</t>
+          <t>H-802</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Setup KB `HLS_*`</t>
+          <t>Wrapper AgentShield</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
+          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
+          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
@@ -8295,17 +8322,17 @@
       </c>
       <c r="T45" s="10" t="inlineStr">
         <is>
-          <t>T-803</t>
+          <t>T-802</t>
         </is>
       </c>
       <c r="U45" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V45" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8345,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>H-804</t>
+          <t>H-803</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -8328,22 +8355,22 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Accesso agenti alla KB</t>
+          <t>Setup KB `HLS_*`</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-804</t>
+          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
+          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-611 [P]</t>
+          <t>H-202, H-204 [P]</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -8384,12 +8411,12 @@
       </c>
       <c r="T46" s="10" t="inlineStr">
         <is>
-          <t>T-804</t>
+          <t>T-803</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>H-611, H-803</t>
+          <t>H-202, H-204</t>
         </is>
       </c>
       <c r="V46" s="10" t="inlineStr">
@@ -8399,42 +8426,40 @@
       </c>
     </row>
     <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A47" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B47" s="9" t="n">
         <v>65</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-804</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>`api/` loopback e hardening</t>
+          <t>Accesso agenti alla KB</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b01…T-8b04</t>
+          <t>**Fase 8.** T-804</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
+          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401 [P]</t>
+          <t>H-803, H-611 [P]</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
@@ -8475,17 +8500,17 @@
       </c>
       <c r="T47" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04</t>
+          <t>T-804</t>
         </is>
       </c>
       <c r="U47" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401</t>
+          <t>H-611, H-803</t>
         </is>
       </c>
       <c r="V47" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8525,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -8510,22 +8535,22 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Read model derivato</t>
+          <t>`api/` loopback e hardening</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b05</t>
+          <t>**Fase 8b.** T-8b01…T-8b04</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Cache rigenerabile, fonte unica (C27)</t>
+          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-303, H-401 [P]</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -8566,12 +8591,12 @@
       </c>
       <c r="T48" s="10" t="inlineStr">
         <is>
-          <t>T-8b05</t>
+          <t>T-8b01, T-8b04</t>
         </is>
       </c>
       <c r="U48" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-303, H-401</t>
         </is>
       </c>
       <c r="V48" s="10" t="inlineStr">
@@ -8591,7 +8616,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>H-8b05</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -8601,22 +8626,22 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Gate solo da sessione umana</t>
+          <t>Read model derivato</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
+          <t>**Fase 8b.** T-8b05</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git</t>
+          <t>Cache rigenerabile, fonte unica (C27)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-403</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -8657,12 +8682,12 @@
       </c>
       <c r="T49" s="10" t="inlineStr">
         <is>
-          <t>T-8b08</t>
+          <t>T-8b05</t>
         </is>
       </c>
       <c r="U49" s="10" t="inlineStr">
         <is>
-          <t>H-403, H-8b01</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="V49" s="10" t="inlineStr">
@@ -8682,32 +8707,32 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b05</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>`ui/` viste</t>
+          <t>Gate solo da sessione umana</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b06</t>
+          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
+          <t>La UI non esegue build/test/git</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-8b01, H-403</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -8721,7 +8746,7 @@
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr"/>
@@ -8748,17 +8773,17 @@
       </c>
       <c r="T50" s="10" t="inlineStr">
         <is>
-          <t>T-8b06</t>
+          <t>T-8b08</t>
         </is>
       </c>
       <c r="U50" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-403, H-8b01</t>
         </is>
       </c>
       <c r="V50" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8798,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>H-8b04</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -8783,22 +8808,22 @@
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Vista Permessi agenti</t>
+          <t>`ui/` viste</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-405, T-8b07</t>
+          <t>**Fase 8b.** T-8b06</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Conferma, motivazione, audit, rollback</t>
+          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -8839,12 +8864,12 @@
       </c>
       <c r="T51" s="10" t="inlineStr">
         <is>
-          <t>T-405, T-8b07</t>
+          <t>T-8b06</t>
         </is>
       </c>
       <c r="U51" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="V51" s="10" t="inlineStr">
@@ -8864,7 +8889,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>H-8b06</t>
+          <t>H-8b04</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -8874,22 +8899,22 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Grafica e accessibilità</t>
+          <t>Vista Permessi agenti</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b09</t>
+          <t>**Fase 8b.** T-405, T-8b07</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
+          <t>Conferma, motivazione, audit, rollback</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -8930,12 +8955,12 @@
       </c>
       <c r="T52" s="10" t="inlineStr">
         <is>
-          <t>T-8b09</t>
+          <t>T-405, T-8b07</t>
         </is>
       </c>
       <c r="U52" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="V52" s="10" t="inlineStr">
@@ -8955,7 +8980,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>H-8b07</t>
+          <t>H-8b06</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -8965,17 +8990,17 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Governance dipendenze npm</t>
+          <t>Grafica e accessibilità</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b10</t>
+          <t>**Fase 8b.** T-8b09</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Lockfile, licenze, audit, SBOM (C25)</t>
+          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -9021,7 +9046,7 @@
       </c>
       <c r="T53" s="10" t="inlineStr">
         <is>
-          <t>T-8b10</t>
+          <t>T-8b09</t>
         </is>
       </c>
       <c r="U53" s="10" t="inlineStr">
@@ -9046,7 +9071,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>H-8b08</t>
+          <t>H-8b07</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -9056,22 +9081,22 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione launcher :8799</t>
+          <t>Governance dipendenze npm</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-304</t>
+          <t>**Fase 8b.** T-8b10</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Tramite shim</t>
+          <t>Lockfile, licenze, audit, SBOM (C25)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
@@ -9112,12 +9137,12 @@
       </c>
       <c r="T54" s="10" t="inlineStr">
         <is>
-          <t>T-304</t>
+          <t>T-8b10</t>
         </is>
       </c>
       <c r="U54" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V54" s="10" t="inlineStr">
@@ -9137,32 +9162,32 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b08</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>Sostituzione launcher :8799</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
+          <t>**Fase 8b.** T-304</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
+          <t>Tramite shim</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
@@ -9195,7 +9220,7 @@
       <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S55" s="12" t="n">
@@ -9203,17 +9228,17 @@
       </c>
       <c r="T55" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="U55" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="V55" s="10" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
@@ -9228,32 +9253,32 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Avvio del run non presidiato dalla dashboard</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
+          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
+          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr">
@@ -9286,7 +9311,7 @@
       <c r="Q56" s="10" t="n"/>
       <c r="R56" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003 §9</t>
+          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S56" s="12" t="n">
@@ -9294,55 +9319,57 @@
       </c>
       <c r="T56" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="U56" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="V56" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
-      <c r="A57" s="9" t="n">
-        <v>9</v>
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B57" s="9" t="n">
         <v>75</v>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E ALA V1–V24</t>
+          <t>Avvio del run non presidiato dalla dashboard</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
+          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Catena completa su 3 OS, progetto pilota</t>
+          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
@@ -9356,7 +9383,7 @@
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr"/>
@@ -9375,7 +9402,7 @@
       <c r="Q57" s="10" t="n"/>
       <c r="R57" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §9</t>
         </is>
       </c>
       <c r="S57" s="12" t="n">
@@ -9383,17 +9410,17 @@
       </c>
       <c r="T57" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="U57" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="V57" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
     </row>
@@ -9406,32 +9433,32 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>H-902</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-27</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>README e troubleshooting plugin</t>
+          <t>Scenari E2E ALA V1–V24</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `agents/plugin/README.md`</t>
+          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Installazione, configurazione, errori</t>
+          <t>Catena completa su 3 OS, progetto pilota</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>H-901 [P]</t>
+          <t>Fasi 5–8</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
@@ -9445,7 +9472,7 @@
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr"/>
@@ -9477,25 +9504,25 @@
       </c>
       <c r="U58" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="V58" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md</t>
+          <t>E2E_VERIFICATION.md</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B59" s="9" t="n">
         <v>77</v>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>H-1101</t>
+          <t>H-902</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -9505,22 +9532,22 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Manuali, NOTICE, runbook</t>
+          <t>README e troubleshooting plugin</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>**Fase 11.** Revisione approvata</t>
+          <t>**Fase 9.** `agents/plugin/README.md`</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Documentazione finale</t>
+          <t>Installazione, configurazione, errori</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-901 [P]</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
@@ -9571,40 +9598,40 @@
       </c>
       <c r="V59" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>agents/plugin/README.md</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="9" t="n">
         <v>78</v>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-1101</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-28</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Manuali, NOTICE, runbook</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+          <t>**Fase 11.** Revisione approvata</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Log immutabili, sandbox, SBOM, audit</t>
+          <t>Documentazione finale</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -9623,7 +9650,7 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr"/>
@@ -9660,45 +9687,45 @@
       </c>
       <c r="V60" s="10" t="inlineStr">
         <is>
-          <t>docs/audit-hardening.md</t>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>79</v>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>H-1201</t>
+          <t>H-1001</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>PK-30</t>
+          <t>PK-29</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Rollout sul pilota</t>
+          <t>Hardening</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>**Fase 12.** Parere legale **[N]**</t>
+          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Metriche, rollback, parere legale</t>
+          <t>Log immutabili, sandbox, SBOM, audit</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>H-1001, H-1101</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
@@ -9712,7 +9739,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -9744,21 +9771,110 @@
       </c>
       <c r="U61" s="10" t="inlineStr">
         <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V61" s="10" t="inlineStr">
+        <is>
+          <t>docs/audit-hardening.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="58" customHeight="1">
+      <c r="A62" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>H-1201</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>PK-30</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 12.** Parere legale **[N]**</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Metriche, rollback, parere legale</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
           <t>H-1001, H-1101</t>
         </is>
       </c>
-      <c r="V61" s="10" t="inlineStr">
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J62" s="9">
+        <f>IF(I62="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="10" t="inlineStr"/>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U62" s="10" t="inlineStr">
+        <is>
+          <t>H-1001, H-1101</t>
+        </is>
+      </c>
+      <c r="V62" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V61"/>
+  <autoFilter ref="A4:V62"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:S61">
+  <conditionalFormatting sqref="A5:S62">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($S5=1,$I5&lt;&gt;"Fatto")</formula>
     </cfRule>
@@ -9766,7 +9882,7 @@
       <formula>$I5="Fatto"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I61">
+  <conditionalFormatting sqref="I5:I62">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -9783,7 +9899,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K61">
+  <conditionalFormatting sqref="K5:K62">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
@@ -9794,7 +9910,7 @@
       <formula>"SUPERVISORE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S61">
+  <conditionalFormatting sqref="S5:S62">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -9804,19 +9920,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="I5:I61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Da fare,In corso,In review,Fatto,Bloccato"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NARO,SCIBETTA,SUPERVISORE,Da assegnare"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,M,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="S5:S62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -9832,7 +9948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9959,15 +10075,15 @@
         </is>
       </c>
       <c r="E5" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D61,A5)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D62,A5)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A5,'Post-GO'!I5:I61,"In review")+F5&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"In review")+F5&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -10028,15 +10144,15 @@
         </is>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D61,A6)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D62,A6)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A6,'Post-GO'!I5:I61,"In review")+F6&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"In review")+F6&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -10097,15 +10213,15 @@
         </is>
       </c>
       <c r="E7" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D61,A7)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D62,A7)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A7,'Post-GO'!I5:I61,"In review")+F7&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"In review")+F7&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -10166,15 +10282,15 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D61,A8)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D62,A8)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A8,'Post-GO'!I5:I61,"In review")+F8&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"In review")+F8&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -10235,15 +10351,15 @@
         </is>
       </c>
       <c r="E9" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D61,A9)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D62,A9)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A9,'Post-GO'!I5:I61,"In review")+F9&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"In review")+F9&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -10304,15 +10420,15 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D61,A10)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D62,A10)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A10,'Post-GO'!I5:I61,"In review")+F10&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"In review")+F10&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -10373,15 +10489,15 @@
         </is>
       </c>
       <c r="E11" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D61,A11)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D62,A11)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A11,'Post-GO'!I5:I61,"In review")+F11&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"In review")+F11&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -10442,15 +10558,15 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D61,A12)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D62,A12)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A12,'Post-GO'!I5:I61,"In review")+F12&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"In review")+F12&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -10511,15 +10627,15 @@
         </is>
       </c>
       <c r="E13" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D61,A13)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D62,A13)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A13,'Post-GO'!I5:I61,"In review")+F13&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"In review")+F13&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -10580,15 +10696,15 @@
         </is>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D61,A14)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D62,A14)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A14,'Post-GO'!I5:I61,"In review")+F14&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"In review")+F14&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -10649,15 +10765,15 @@
         </is>
       </c>
       <c r="E15" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D61,A15)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D62,A15)</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A15,'Post-GO'!I5:I61,"In review")+F15&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"In review")+F15&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -10718,15 +10834,15 @@
         </is>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D61,A16)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D62,A16)</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A16,'Post-GO'!I5:I61,"In review")+F16&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"In review")+F16&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -10787,15 +10903,15 @@
         </is>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D61,A17)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D62,A17)</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A17,'Post-GO'!I5:I61,"In review")+F17&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"In review")+F17&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -10856,15 +10972,15 @@
         </is>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D61,A18)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D62,A18)</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A18,'Post-GO'!I5:I61,"In review")+F18&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"In review")+F18&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -10925,15 +11041,15 @@
         </is>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D61,A19)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D62,A19)</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A19,'Post-GO'!I5:I61,"In review")+F19&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"In review")+F19&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -10994,15 +11110,15 @@
         </is>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D61,A20)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D62,A20)</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A20,'Post-GO'!I5:I61,"In review")+F20&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"In review")+F20&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -11063,15 +11179,15 @@
         </is>
       </c>
       <c r="E21" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D61,A21)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D62,A21)</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G21" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A21,'Post-GO'!I5:I61,"In review")+F21&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"In review")+F21&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -11132,15 +11248,15 @@
         </is>
       </c>
       <c r="E22" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D61,A22)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D62,A22)</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G22" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A22,'Post-GO'!I5:I61,"In review")+F22&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"In review")+F22&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -11201,15 +11317,15 @@
         </is>
       </c>
       <c r="E23" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D61,A23)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D62,A23)</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G23" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A23,'Post-GO'!I5:I61,"In review")+F23&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"In review")+F23&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -11270,15 +11386,15 @@
         </is>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D61,A24)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D62,A24)</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A24,'Post-GO'!I5:I61,"In review")+F24&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"In review")+F24&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -11339,15 +11455,15 @@
         </is>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D61,A25)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D62,A25)</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A25,'Post-GO'!I5:I61,"In review")+F25&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"In review")+F25&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -11408,15 +11524,15 @@
         </is>
       </c>
       <c r="E26" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D61,A26)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D62,A26)</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A26,'Post-GO'!I5:I61,"In review")+F26&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"In review")+F26&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -11477,15 +11593,15 @@
         </is>
       </c>
       <c r="E27" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D61,A27)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D62,A27)</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A27,'Post-GO'!I5:I61,"In review")+F27&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"In review")+F27&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -11546,15 +11662,15 @@
         </is>
       </c>
       <c r="E28" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D61,A28)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D62,A28)</f>
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G28" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A28,'Post-GO'!I5:I61,"In review")+F28&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"In review")+F28&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -11615,15 +11731,15 @@
         </is>
       </c>
       <c r="E29" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D61,A29)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D62,A29)</f>
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G29" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A29,'Post-GO'!I5:I61,"In review")+F29&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"In review")+F29&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -11684,15 +11800,15 @@
         </is>
       </c>
       <c r="E30" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D61,A30)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D62,A30)</f>
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G30" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A30,'Post-GO'!I5:I61,"In review")+F30&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"In review")+F30&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -11753,15 +11869,15 @@
         </is>
       </c>
       <c r="E31" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D61,A31)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D62,A31)</f>
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G31" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A31,'Post-GO'!I5:I61,"In review")+F31&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"In review")+F31&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -11803,103 +11919,103 @@
     <row r="32" ht="62" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19c</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi di prodotto (C28)</t>
+          <t>Ciclo di rilavorazione dei findings di code review</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-716</t>
         </is>
       </c>
       <c r="E32" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D61,A32)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D62,A32)</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G32" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A32,'Post-GO'!I5:I61,"In review")+F32&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"In review")+F32&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>S9c</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-716</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (ciclo reviewer-&gt;developer-&gt;reviewer, contatore dei giri), agents/policy/ (tetto dei giri)</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
+          <t>PK-18 (H-607), PK-19 (H-701), PK-20 (H-706, H-711)</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>PK-23, PK-24, PK-25</t>
+          <t>PK-20</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>risk-assessor ≠ developer, sola lettura.</t>
+          <t>Q-20. Max 2 correzioni, poi WAITING_SUPERVISOR. Contatore dei giri DISTINTO da R12 maxAttempts. Stessi file di PK-19 (limet-change.js): stessa persona. Contatto con PK-20 sul contratto di stato. Verifica: T-716, E2E-REV-1.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="62" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Installer e modifiche documentali a LIMET</t>
+          <t>Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>H-702, H-712</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="E33" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D61,A33)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D62,A33)</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G33" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A33,'Post-GO'!I5:I61,"In review")+F33&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"In review")+F33&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H33" s="9" t="inlineStr">
@@ -11909,135 +12025,135 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>T-702, T-712</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
+          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-23, PK-24, PK-25</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
+          <t>risk-assessor ≠ developer, sola lettura.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Hook ECC e registro chiamate LLM</t>
+          <t>Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>H-800, H-800b, H-801, H-802</t>
+          <t>H-702, H-712</t>
         </is>
       </c>
       <c r="E34" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D61,A34)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D62,A34)</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G34" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A34,'Post-GO'!I5:I61,"In review")+F34&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"In review")+F34&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>T-801, T-802</t>
+          <t>T-702, T-712</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-08</t>
+          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-22</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="62" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Knowledge base HLS_* e accesso agenti</t>
+          <t>Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-804</t>
+          <t>H-800, H-800b, H-801, H-802</t>
         </is>
       </c>
       <c r="E35" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D61,A35)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D62,A35)</f>
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G35" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A35,'Post-GO'!I5:I61,"In review")+F35&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"In review")+F35&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -12047,66 +12163,66 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>T-803, T-804</t>
+          <t>T-801, T-802</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>PK-03, PK-15</t>
+          <t>GO; PK-08</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-14…PK-22</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
+          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>API loopback e read model</t>
+          <t>Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-8b02, H-8b05</t>
+          <t>H-803, H-804</t>
         </is>
       </c>
       <c r="E36" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D61,A36)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D62,A36)</f>
         <v/>
       </c>
       <c r="F36" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G36" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A36,'Post-GO'!I5:I61,"In review")+F36&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"In review")+F36&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -12116,108 +12232,108 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
+          <t>T-803, T-804</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-06, PK-08</t>
+          <t>PK-03, PK-15</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>PK-26 (dopo contratto API)</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
+          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="62" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Onda 4+ (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>API loopback e read model</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
+          <t>H-8b01, H-8b02, H-8b05</t>
         </is>
       </c>
       <c r="E37" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D61,A37)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D62,A37)</f>
         <v/>
       </c>
       <c r="F37" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G37" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A37,'Post-GO'!I5:I61,"In review")+F37&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"In review")+F37&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>N13</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
+          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>PK-25, PK-08, PK-06</t>
+          <t>GO; PK-06, PK-08</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>PK-25 (dopo contratto API)</t>
+          <t>PK-26 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git (C23–C24).</t>
+          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="62" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -12227,24 +12343,24 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
         </is>
       </c>
       <c r="E38" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D61,A38)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D62,A38)</f>
         <v/>
       </c>
       <c r="F38" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G38" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A38,'Post-GO'!I5:I61,"In review")+F38&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"In review")+F38&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -12254,66 +12370,66 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>N13b</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
+          <t>PK-25, PK-08, PK-06</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PK-25 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
+          <t>La UI non esegue build/test/git (C23–C24).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Onda 5+ (dopo GO)</t>
+          <t>Onda 4+ (dopo GO)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Pannello di avvio del run non presidiato</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="E39" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D61,A39)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D62,A39)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A39,'Post-GO'!I5:I61,"In review")+F39&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"In review")+F39&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -12323,22 +12439,22 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>N13c</t>
+          <t>N13b</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
+          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
@@ -12348,293 +12464,362 @@
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
+          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E V1–V24</t>
+          <t>Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="E40" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D61,A40)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D62,A40)</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"Fatto")</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A40,'Post-GO'!I5:I61,"In review")+F40&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"In review")+F40&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>N13c</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
+          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Scenari E2E V1–V24</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="E41" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D62,A41)</f>
+        <v/>
+      </c>
+      <c r="F41" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G41" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"In review")+F41&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Fasi 5–8</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
           <t>PK-28</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Onda 7 (dopo GO)</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>README plugin e manuali</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>H-902, H-1101</t>
-        </is>
-      </c>
-      <c r="E41" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D61,A41)</f>
-        <v/>
-      </c>
-      <c r="F41" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G41" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A41,'Post-GO'!I5:I61,"In review")+F41&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>NARO</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>N14</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>PK-27</t>
-        </is>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>PK-29</t>
-        </is>
-      </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>Revisione approvata dal SUPERVISORE.</t>
+          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="62" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>README plugin e manuali</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>H-902, H-1101</t>
+        </is>
+      </c>
+      <c r="E42" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A42)+COUNTIF('Post-GO'!D5:D62,A42)</f>
+        <v/>
+      </c>
+      <c r="F42" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G42" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F42=E42,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"In review")+F42&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
           <t>PK-29</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Onda 8 (dopo GO)</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Hardening</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>H-1001</t>
-        </is>
-      </c>
-      <c r="E42" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A42)+COUNTIF('Post-GO'!D5:D61,A42)</f>
-        <v/>
-      </c>
-      <c r="F42" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G42" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F42=E42,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A42,'Post-GO'!I5:I61,"In review")+F42&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>SCIBETTA</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>S14</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>[N] log immutabili, sandbox, SBOM</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>PK-27</t>
-        </is>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>PK-28</t>
-        </is>
-      </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+          <t>Revisione approvata dal SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="62" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Onda 8 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="E43" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A43)+COUNTIF('Post-GO'!D5:D62,A43)</f>
+        <v/>
+      </c>
+      <c r="F43" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G43" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F43=E43,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"In review")+F43&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>[N] log immutabili, sandbox, SBOM</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
           <t>PK-30</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Onda 9 (dopo GO)</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Rollout sul pilota</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>H-1201</t>
         </is>
       </c>
-      <c r="E43" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A43)+COUNTIF('Post-GO'!D5:D61,A43)</f>
-        <v/>
-      </c>
-      <c r="F43" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G43" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"Bloccato")&gt;0,"Bloccato",IF(F43=E43,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D61,A43,'Post-GO'!I5:I61,"In review")+F43&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="E44" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A44)+COUNTIF('Post-GO'!D5:D62,A44)</f>
+        <v/>
+      </c>
+      <c r="F44" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G44" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F44=E44,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"In review")+F44&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>NARO</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>N15</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>PK-28, PK-29</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>[N] parere legale; pilota da scegliere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N43"/>
+  <autoFilter ref="A4:N44"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G43">
+  <conditionalFormatting sqref="G5:G44">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -12648,7 +12833,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H43">
+  <conditionalFormatting sqref="H5:H44">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>

--- a/log/HELIOS_Distribuzione_task.xlsx
+++ b/log/HELIOS_Distribuzione_task.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pre-GO'!$A$4:$V$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Post-GO'!$A$4:$V$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pacchetti'!$A$4:$N$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIF('Post-GO'!I5:I62,A4)</f>
+        <f>COUNTIF('Post-GO'!I5:I64,A4)</f>
         <v/>
       </c>
       <c r="D4">
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIF('Post-GO'!I5:I62,A5)</f>
+        <f>COUNTIF('Post-GO'!I5:I64,A5)</f>
         <v/>
       </c>
       <c r="D5">
@@ -677,7 +677,7 @@
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIF('Post-GO'!I5:I62,A6)</f>
+        <f>COUNTIF('Post-GO'!I5:I64,A6)</f>
         <v/>
       </c>
       <c r="D6">
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIF('Post-GO'!I5:I62,A7)</f>
+        <f>COUNTIF('Post-GO'!I5:I64,A7)</f>
         <v/>
       </c>
       <c r="D7">
@@ -715,7 +715,7 @@
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIF('Post-GO'!I5:I62,A8)</f>
+        <f>COUNTIF('Post-GO'!I5:I64,A8)</f>
         <v/>
       </c>
       <c r="D8">
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIF('Post-GO'!K5:K62,A14)</f>
+        <f>COUNTIF('Post-GO'!K5:K64,A14)</f>
         <v/>
       </c>
       <c r="D14">
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A14,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K64,A14,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIF('Post-GO'!K5:K62,A15)</f>
+        <f>COUNTIF('Post-GO'!K5:K64,A15)</f>
         <v/>
       </c>
       <c r="D15">
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A15,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K64,A15,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -845,7 +845,7 @@
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIF('Post-GO'!K5:K62,A16)</f>
+        <f>COUNTIF('Post-GO'!K5:K64,A16)</f>
         <v/>
       </c>
       <c r="D16">
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A16,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K64,A16,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIF('Post-GO'!K5:K62,A17)</f>
+        <f>COUNTIF('Post-GO'!K5:K64,A17)</f>
         <v/>
       </c>
       <c r="D17">
@@ -876,7 +876,7 @@
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K62,A17,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!K5:K26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!K5:K64,A17,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
     </row>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D62,"PK-00")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-00")+COUNTIF('Post-GO'!D5:D64,"PK-00")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-00",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-00",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E21">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-00",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-00",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-00",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="B22">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D62,"PK-01")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-01")+COUNTIF('Post-GO'!D5:D64,"PK-01")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-01",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-01",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E22">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-01",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-01",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-01",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B23">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D62,"PK-02")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-02")+COUNTIF('Post-GO'!D5:D64,"PK-02")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-02",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-02",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E23">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-02",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-02",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-02",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -1000,19 +1000,19 @@
         </is>
       </c>
       <c r="B24">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D62,"PK-03")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-03")+COUNTIF('Post-GO'!D5:D64,"PK-03")</f>
         <v/>
       </c>
       <c r="C24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-03",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-03",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E24">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-03",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-03",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-03",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B25">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D62,"PK-04")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-04")+COUNTIF('Post-GO'!D5:D64,"PK-04")</f>
         <v/>
       </c>
       <c r="C25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-04",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-04",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E25">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-04",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-04",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-04",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B26">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D62,"PK-05")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05")+COUNTIF('Post-GO'!D5:D64,"PK-05")</f>
         <v/>
       </c>
       <c r="C26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-05",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-05",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E26">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-05",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-05",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="B27">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D62,"PK-05b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-05b")+COUNTIF('Post-GO'!D5:D64,"PK-05b")</f>
         <v/>
       </c>
       <c r="C27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-05b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-05b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E27">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-05b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-05b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-05b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="B28">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D62,"PK-06")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-06")+COUNTIF('Post-GO'!D5:D64,"PK-06")</f>
         <v/>
       </c>
       <c r="C28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-06",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-06",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E28">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-06",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-06",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-06",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B29">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D62,"PK-07")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07")+COUNTIF('Post-GO'!D5:D64,"PK-07")</f>
         <v/>
       </c>
       <c r="C29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-07",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-07",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E29">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-07",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-07",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -1162,19 +1162,19 @@
         </is>
       </c>
       <c r="B30">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D62,"PK-07b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-07b")+COUNTIF('Post-GO'!D5:D64,"PK-07b")</f>
         <v/>
       </c>
       <c r="C30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-07b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-07b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E30">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-07b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-07b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-07b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -1189,19 +1189,19 @@
         </is>
       </c>
       <c r="B31">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D62,"PK-08")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-08")+COUNTIF('Post-GO'!D5:D64,"PK-08")</f>
         <v/>
       </c>
       <c r="C31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-08",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-08",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E31">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-08",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-08",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-08",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B32">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D62,"PK-09")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-09")+COUNTIF('Post-GO'!D5:D64,"PK-09")</f>
         <v/>
       </c>
       <c r="C32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-09",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-09",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E32">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-09",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-09",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-09",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D62,"PK-10")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-10")+COUNTIF('Post-GO'!D5:D64,"PK-10")</f>
         <v/>
       </c>
       <c r="C33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-10",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-10",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E33">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-10",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-10",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-10",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="B34">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D62,"PK-11")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-11")+COUNTIF('Post-GO'!D5:D64,"PK-11")</f>
         <v/>
       </c>
       <c r="C34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-11",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-11",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E34">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-11",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-11",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-11",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="B35">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D62,"PK-12")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-12")+COUNTIF('Post-GO'!D5:D64,"PK-12")</f>
         <v/>
       </c>
       <c r="C35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-12",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-12",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E35">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-12",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-12",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-12",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B36">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D62,"PK-13")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-13")+COUNTIF('Post-GO'!D5:D64,"PK-13")</f>
         <v/>
       </c>
       <c r="C36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-13",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-13",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E36">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-13",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-13",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-13",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="B37">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D62,"PK-14")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-14")+COUNTIF('Post-GO'!D5:D64,"PK-14")</f>
         <v/>
       </c>
       <c r="C37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-14",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-14",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E37">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-14",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-14",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-14",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -1378,19 +1378,19 @@
         </is>
       </c>
       <c r="B38">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D62,"PK-15")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-15")+COUNTIF('Post-GO'!D5:D64,"PK-15")</f>
         <v/>
       </c>
       <c r="C38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-15",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-15",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E38">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-15",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-15",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-15",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F38" s="5">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="B39">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D62,"PK-16")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16")+COUNTIF('Post-GO'!D5:D64,"PK-16")</f>
         <v/>
       </c>
       <c r="C39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-16",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-16",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E39">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-16",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F39" s="5">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="B40">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16b")+COUNTIF('Post-GO'!D5:D62,"PK-16b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16b")+COUNTIF('Post-GO'!D5:D64,"PK-16b")</f>
         <v/>
       </c>
       <c r="C40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-16b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-16b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E40">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-16b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F40" s="5">
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="B41">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16c")+COUNTIF('Post-GO'!D5:D62,"PK-16c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-16c")+COUNTIF('Post-GO'!D5:D64,"PK-16c")</f>
         <v/>
       </c>
       <c r="C41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-16c",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-16c",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E41">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-16c",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-16c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-16c",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F41" s="5">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B42">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D62,"PK-17")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-17")+COUNTIF('Post-GO'!D5:D64,"PK-17")</f>
         <v/>
       </c>
       <c r="C42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-17",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-17",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E42">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-17",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-17",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-17",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F42" s="5">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="B43">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D62,"PK-18")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-18")+COUNTIF('Post-GO'!D5:D64,"PK-18")</f>
         <v/>
       </c>
       <c r="C43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-18",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-18",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E43">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-18",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-18",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-18",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F43" s="5">
@@ -1540,19 +1540,19 @@
         </is>
       </c>
       <c r="B44">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D62,"PK-19")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19")+COUNTIF('Post-GO'!D5:D64,"PK-19")</f>
         <v/>
       </c>
       <c r="C44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-19",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-19",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E44">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-19",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F44" s="5">
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B45">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D62,"PK-20")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20")+COUNTIF('Post-GO'!D5:D64,"PK-20")</f>
         <v/>
       </c>
       <c r="C45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-20",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-20",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E45">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-20",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-20",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F45" s="5">
@@ -1594,19 +1594,19 @@
         </is>
       </c>
       <c r="B46">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D62,"PK-19b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19b")+COUNTIF('Post-GO'!D5:D64,"PK-19b")</f>
         <v/>
       </c>
       <c r="C46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-19b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-19b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E46">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-19b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F46" s="5">
@@ -1621,19 +1621,19 @@
         </is>
       </c>
       <c r="B47">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D62,"PK-20b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-20b")+COUNTIF('Post-GO'!D5:D64,"PK-20b")</f>
         <v/>
       </c>
       <c r="C47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-20b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-20b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E47">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-20b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-20b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-20b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F47" s="5">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B48">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19c")+COUNTIF('Post-GO'!D5:D62,"PK-19c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19c")+COUNTIF('Post-GO'!D5:D64,"PK-19c")</f>
         <v/>
       </c>
       <c r="C48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-19c",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-19c",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E48">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-19c",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-19c",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F48" s="5">
@@ -1671,23 +1671,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
+          <t>PK-19d · Revisione umana obbligatoria del diff (gate)</t>
         </is>
       </c>
       <c r="B49">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D62,"PK-21")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-19d")+COUNTIF('Post-GO'!D5:D64,"PK-19d")</f>
         <v/>
       </c>
       <c r="C49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19d",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-19d",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19d",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-19d",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E49">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-21",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-19d",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-19d",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F49" s="5">
@@ -1698,23 +1698,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
+          <t>PK-21 · Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="B50">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D62,"PK-22")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-21")+COUNTIF('Post-GO'!D5:D64,"PK-21")</f>
         <v/>
       </c>
       <c r="C50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-21",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-21",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E50">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-22",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-21",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-21",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F50" s="5">
@@ -1725,23 +1725,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
+          <t>PK-22 · Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D62,"PK-23")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-22")+COUNTIF('Post-GO'!D5:D64,"PK-22")</f>
         <v/>
       </c>
       <c r="C51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-22",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-22",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E51">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-23",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-22",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-22",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F51" s="5">
@@ -1752,23 +1752,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
+          <t>PK-23 · Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D62,"PK-24")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-23")+COUNTIF('Post-GO'!D5:D64,"PK-23")</f>
         <v/>
       </c>
       <c r="C52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-23",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-23",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E52">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-24",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-23",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-23",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F52" s="5">
@@ -1779,23 +1779,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PK-25 · API loopback e read model</t>
+          <t>PK-24 · Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="B53">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D62,"PK-25")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-24")+COUNTIF('Post-GO'!D5:D64,"PK-24")</f>
         <v/>
       </c>
       <c r="C53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-24",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-24",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E53">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-25",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-24",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-24",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F53" s="5">
@@ -1806,23 +1806,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>PK-25 · API loopback e read model</t>
         </is>
       </c>
       <c r="B54">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D62,"PK-26")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-25")+COUNTIF('Post-GO'!D5:D64,"PK-25")</f>
         <v/>
       </c>
       <c r="C54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-25",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-25",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E54">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-25",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-25",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F54" s="5">
@@ -1833,23 +1833,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
+          <t>PK-26 · UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="B55">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D62,"PK-26b")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26")+COUNTIF('Post-GO'!D5:D64,"PK-26")</f>
         <v/>
       </c>
       <c r="C55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-26",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-26",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E55">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26b",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-26",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F55" s="5">
@@ -1860,23 +1860,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PK-26c · Pannello di avvio del run non presidiato</t>
+          <t>PK-26b · Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="B56">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D62,"PK-26c")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26b")+COUNTIF('Post-GO'!D5:D64,"PK-26b")</f>
         <v/>
       </c>
       <c r="C56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-26b",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-26b",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E56">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-26c",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26b",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-26b",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F56" s="5">
@@ -1887,23 +1887,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PK-27 · Scenari E2E V1–V24</t>
+          <t>PK-26c · Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="B57">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D62,"PK-27")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26c")+COUNTIF('Post-GO'!D5:D64,"PK-26c")</f>
         <v/>
       </c>
       <c r="C57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-26c",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-26c",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E57">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-27",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26c",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-26c",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F57" s="5">
@@ -1914,23 +1914,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PK-28 · README plugin e manuali</t>
+          <t>PK-26d · Pannello di revisione umana del diff</t>
         </is>
       </c>
       <c r="B58">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D62,"PK-28")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-26d")+COUNTIF('Post-GO'!D5:D64,"PK-26d")</f>
         <v/>
       </c>
       <c r="C58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26d",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-26d",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26d",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-26d",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E58">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-28",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-26d",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-26d",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F58" s="5">
@@ -1941,23 +1941,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PK-29 · Hardening</t>
+          <t>PK-27 · Scenari E2E V1–V24</t>
         </is>
       </c>
       <c r="B59">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D62,"PK-29")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-27")+COUNTIF('Post-GO'!D5:D64,"PK-27")</f>
         <v/>
       </c>
       <c r="C59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-27",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-27",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E59">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-29",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-27",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-27",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F59" s="5">
@@ -1968,23 +1968,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PK-30 · Rollout sul pilota</t>
+          <t>PK-28 · README plugin e manuali</t>
         </is>
       </c>
       <c r="B60">
-        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D62,"PK-30")</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-28")+COUNTIF('Post-GO'!D5:D64,"PK-28")</f>
         <v/>
       </c>
       <c r="C60">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-28",'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D60">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-28",'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E60">
-        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D62,"PK-30",'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-28",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-28",'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F60" s="5">
@@ -1992,113 +1992,117 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PK-29 · Hardening</t>
+        </is>
+      </c>
+      <c r="B61">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-29")+COUNTIF('Post-GO'!D5:D64,"PK-29")</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-29",'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-29",'Post-GO'!I5:I64,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-29",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-29",'Post-GO'!I5:I64,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F61" s="5">
+        <f>IF(B61=0,0,C61/B61)</f>
+        <v/>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PK-30 · Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="B62">
+        <f>COUNTIF('Pre-GO'!D5:D26,"PK-30")+COUNTIF('Post-GO'!D5:D64,"PK-30")</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,"PK-30",'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,"PK-30",'Post-GO'!I5:I64,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>COUNTIFS('Pre-GO'!D5:D26,"PK-30",'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!D5:D64,"PK-30",'Post-GO'!I5:I64,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F62" s="5">
+        <f>IF(B62=0,0,C62/B62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Avanzamento per fase</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Fatti</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>In corso</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64)+COUNTIFS('Post-GO'!A5:A62,$A64)</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A64,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A64,'Post-GO'!I5:I62,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F64" s="5">
-        <f>IF(B64=0,0,C64/B64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65)+COUNTIFS('Post-GO'!A5:A62,$A65)</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="D65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"In corso")</f>
-        <v/>
-      </c>
-      <c r="E65">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A65,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A65,'Post-GO'!I5:I62,"Da fare")</f>
-        <v/>
-      </c>
-      <c r="F65" s="5">
-        <f>IF(B65=0,0,C65/B65)</f>
-        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A62,$A66)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66)+COUNTIFS('Post-GO'!A5:A64,$A66)</f>
         <v/>
       </c>
       <c r="C66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A66,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A66,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E66">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A66,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A66,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A66,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F66" s="5">
@@ -2108,22 +2112,22 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A62,$A67)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67)+COUNTIFS('Post-GO'!A5:A64,$A67)</f>
         <v/>
       </c>
       <c r="C67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A67,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A67,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E67">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A67,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A67,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A67,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F67" s="5">
@@ -2133,22 +2137,22 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A62,$A68)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68)+COUNTIFS('Post-GO'!A5:A64,$A68)</f>
         <v/>
       </c>
       <c r="C68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A68,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A68,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E68">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A68,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A68,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A68,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F68" s="5">
@@ -2158,22 +2162,22 @@
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A62,$A69)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69)+COUNTIFS('Post-GO'!A5:A64,$A69)</f>
         <v/>
       </c>
       <c r="C69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A69,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A69,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E69">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A69,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A69,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A69,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F69" s="5">
@@ -2183,22 +2187,22 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A62,$A70)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70)+COUNTIFS('Post-GO'!A5:A64,$A70)</f>
         <v/>
       </c>
       <c r="C70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A70,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A70,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E70">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A70,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A70,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A70,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F70" s="5">
@@ -2208,22 +2212,22 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A62,$A71)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71)+COUNTIFS('Post-GO'!A5:A64,$A71)</f>
         <v/>
       </c>
       <c r="C71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A71,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A71,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E71">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A71,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A71,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A71,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F71" s="5">
@@ -2232,25 +2236,23 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A72" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="B72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A62,$A72)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72)+COUNTIFS('Post-GO'!A5:A64,$A72)</f>
         <v/>
       </c>
       <c r="C72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A72,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A72,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E72">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A72,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A72,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A72,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F72" s="5">
@@ -2260,22 +2262,22 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A62,$A73)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73)+COUNTIFS('Post-GO'!A5:A64,$A73)</f>
         <v/>
       </c>
       <c r="C73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A73,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A73,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E73">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A73,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A73,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A73,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F73" s="5">
@@ -2284,23 +2286,25 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n">
-        <v>10</v>
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74)+COUNTIFS('Post-GO'!A5:A62,$A74)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74)+COUNTIFS('Post-GO'!A5:A64,$A74)</f>
         <v/>
       </c>
       <c r="C74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A74,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A74,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E74">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A74,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A74,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A74,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F74" s="5">
@@ -2310,22 +2314,22 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75)+COUNTIFS('Post-GO'!A5:A62,$A75)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75)+COUNTIFS('Post-GO'!A5:A64,$A75)</f>
         <v/>
       </c>
       <c r="C75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A75,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A75,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E75">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A75,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A75,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A75,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F75" s="5">
@@ -2335,26 +2339,76 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B76">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A76)+COUNTIFS('Post-GO'!A5:A62,$A76)</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76)+COUNTIFS('Post-GO'!A5:A64,$A76)</f>
         <v/>
       </c>
       <c r="C76">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A76,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="D76">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"In corso")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A76,'Post-GO'!I5:I64,"In corso")</f>
         <v/>
       </c>
       <c r="E76">
-        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A62,$A76,'Post-GO'!I5:I62,"Da fare")</f>
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A76,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A76,'Post-GO'!I5:I64,"Da fare")</f>
         <v/>
       </c>
       <c r="F76" s="5">
         <f>IF(B76=0,0,C76/B76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B77">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A77)+COUNTIFS('Post-GO'!A5:A64,$A77)</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A77,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A77,'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A77,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A77,'Post-GO'!I5:I64,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A77,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A77,'Post-GO'!I5:I64,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F77" s="5">
+        <f>IF(B77=0,0,C77/B77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B78">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A78)+COUNTIFS('Post-GO'!A5:A64,$A78)</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A78,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!A5:A64,$A78,'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A78,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!A5:A64,$A78,'Post-GO'!I5:I64,"In corso")</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>COUNTIFS('Pre-GO'!A5:A26,$A78,'Pre-GO'!I5:I26,"Da fare")+COUNTIFS('Post-GO'!A5:A64,$A78,'Post-GO'!I5:I64,"Da fare")</f>
+        <v/>
+      </c>
+      <c r="F78" s="5">
+        <f>IF(B78=0,0,C78/B78)</f>
         <v/>
       </c>
     </row>
@@ -2371,7 +2425,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F60">
+  <conditionalFormatting sqref="F21:F62">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2380,7 +2434,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F64:F76">
+  <conditionalFormatting sqref="F66:F78">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4526,7 +4580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4567,11 +4621,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(I5:I62,"Fatto")/COUNTA(C5:C62)</f>
+        <f>COUNTIF(I5:I64,"Fatto")/COUNTA(C5:C64)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(I5:I62,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C62)&amp;" task · "&amp;COUNTIF(I5:I62,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I62,"Bloccato")&amp;" bloccati"</f>
+        <f>COUNTIF(I5:I64,"Fatto")&amp;" fatti / "&amp;COUNTA(C5:C64)&amp;" task · "&amp;COUNTIF(I5:I64,"In corso")&amp;" in corso · "&amp;COUNTIF(I5:I64,"Bloccato")&amp;" bloccati"</f>
         <v/>
       </c>
     </row>
@@ -7715,39 +7769,39 @@
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>57</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-717</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19d</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi post-task (prodotto)</t>
+          <t>Revisione umana obbligatoria del diff</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>**Fase 6, gruppo E.** T-611</t>
+          <t>**Fase 7.** Nessun timeout che approva</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
+          <t>Task **sensibili** (lista di percorsi in configurazione) e a **rischio alto** (H-612) non si fondono senza approvazione umana **ancorata allo SHA**</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-711, H-612, H-706</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -7761,7 +7815,7 @@
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr"/>
@@ -7780,7 +7834,7 @@
       <c r="Q39" s="10" t="n"/>
       <c r="R39" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Q-21. Dopo GO</t>
         </is>
       </c>
       <c r="S39" s="12" t="n">
@@ -7788,55 +7842,55 @@
       </c>
       <c r="T39" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-717</t>
         </is>
       </c>
       <c r="U39" s="10" t="inlineStr">
         <is>
-          <t>H-308, H-701, H-706</t>
+          <t>H-612, H-706, H-711</t>
         </is>
       </c>
       <c r="V39" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (gate di merge: percorsi sensibili, rischio alto, firma su SHA), agents/policy/ (lista percorsi sensibili)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>58</v>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>H-702</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Installer `limet-agents.ps1/.sh`</t>
+          <t>Valutazione rischi post-task (prodotto)</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7.** T-702</t>
+          <t>**Fase 6, gruppo E.** T-611</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>`init|update` idempotente, plugin facoltativo</t>
+          <t>`risk-assessor` al passaggio a VERIFIED (C28), `RISK-&lt;task&gt;.json` + `QUESTIONS.md`</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>gruppi A e C, H-407</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -7877,17 +7931,17 @@
       </c>
       <c r="T40" s="10" t="inlineStr">
         <is>
-          <t>T-702</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="U40" s="10" t="inlineStr">
         <is>
-          <t>H-407</t>
+          <t>H-308, H-701, H-706</t>
         </is>
       </c>
       <c r="V40" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7954,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>H-712</t>
+          <t>H-702</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -7910,22 +7964,22 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Modifiche documentali a LIMET M.1–M.9</t>
+          <t>Installer `limet-agents.ps1/.sh`</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>**Fase 7, gruppo F.** T-712</t>
+          <t>**Fase 7.** T-702</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
+          <t>`init|update` idempotente, plugin facoltativo</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
+          <t>gruppi A e C, H-407</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -7966,7 +8020,7 @@
       </c>
       <c r="T41" s="10" t="inlineStr">
         <is>
-          <t>T-712</t>
+          <t>T-702</t>
         </is>
       </c>
       <c r="U41" s="10" t="inlineStr">
@@ -7982,39 +8036,39 @@
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B42" s="9" t="n">
         <v>60</v>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-712</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Analisi degli hook ECC</t>
+          <t>Modifiche documentali a LIMET M.1–M.9</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
+          <t>**Fase 7, gruppo F.** T-712</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Decisione motivata per ognuno dei 27 hook</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura dell'utente</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
+          <t>nessuna in IN; **[P]** dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -8028,7 +8082,7 @@
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr"/>
@@ -8047,7 +8101,7 @@
       <c r="Q42" s="10" t="n"/>
       <c r="R42" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO (o anticipo)</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S42" s="12" t="n">
@@ -8055,17 +8109,17 @@
       </c>
       <c r="T42" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-712</t>
         </is>
       </c>
       <c r="U42" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-407</t>
         </is>
       </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8132,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>H-800b</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -8088,22 +8142,22 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Replica sicura hook utili</t>
+          <t>Analisi degli hook ECC</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
+          <t>**Fase 8.** `docs/ecc-hooks-analysis.md`</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
+          <t>Decisione motivata per ognuno dei 27 hook</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-401 [P]; anticipabile in Fase 2 (IN §5)</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -8136,7 +8190,7 @@
       <c r="Q43" s="10" t="n"/>
       <c r="R43" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO (o anticipo)</t>
         </is>
       </c>
       <c r="S43" s="12" t="n">
@@ -8149,12 +8203,12 @@
       </c>
       <c r="U43" s="10" t="inlineStr">
         <is>
-          <t>H-800</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V43" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>docs/ecc-hooks-analysis.md</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8221,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>H-801</t>
+          <t>H-800b</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -8177,22 +8231,22 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Registro chiamate LLM (C05)</t>
+          <t>Replica sicura hook utili</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
+          <t>**Fase 8.** Verifica definita (audit A6): 5 criteri per hook — portabilità, nessuna rete, nessuna scrittura fuori workspace, log con hash, nessun file ECC in esecuzione. Nomi dei test dopo H-800 **[N]</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Ogni chiamata LLM extra registrata</t>
+          <t>Hook HELIOS propri, mai codice ECC eseguito</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>H-401 [P]</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -8233,17 +8287,17 @@
       </c>
       <c r="T44" s="10" t="inlineStr">
         <is>
-          <t>T-801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U44" s="10" t="inlineStr">
         <is>
-          <t>H-401</t>
+          <t>H-800</t>
         </is>
       </c>
       <c r="V44" s="10" t="inlineStr">
         <is>
-          <t>agents/policy/llm-registry.json</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8310,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>H-802</t>
+          <t>H-801</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -8266,17 +8320,17 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Wrapper AgentShield</t>
+          <t>Registro chiamate LLM (C05)</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
+          <t>**Fase 8.** `agents/policy/llm-registry.json`</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
+          <t>Ogni chiamata LLM extra registrata</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -8322,7 +8376,7 @@
       </c>
       <c r="T45" s="10" t="inlineStr">
         <is>
-          <t>T-802</t>
+          <t>T-801</t>
         </is>
       </c>
       <c r="U45" s="10" t="inlineStr">
@@ -8332,7 +8386,7 @@
       </c>
       <c r="V45" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>agents/policy/llm-registry.json</t>
         </is>
       </c>
     </row>
@@ -8345,32 +8399,32 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>H-803</t>
+          <t>H-802</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Setup KB `HLS_*`</t>
+          <t>Wrapper AgentShield</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
+          <t>**Fase 8.** T-802. **[N]** licenze delle dipendenze (Q-10)</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
+          <t>Pin, hash, SBOM, senza rete/`--opus`</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204 [P]</t>
+          <t>H-401 [P]</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -8411,17 +8465,17 @@
       </c>
       <c r="T46" s="10" t="inlineStr">
         <is>
-          <t>T-803</t>
+          <t>T-802</t>
         </is>
       </c>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>H-202, H-204</t>
+          <t>H-401</t>
         </is>
       </c>
       <c r="V46" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8488,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>H-804</t>
+          <t>H-803</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -8444,22 +8498,22 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Accesso agenti alla KB</t>
+          <t>Setup KB `HLS_*`</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8.** T-804</t>
+          <t>**Fase 8.** T-803 (Q9). Mai su collection esistenti</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
+          <t>Crea `HLS_*` solo con autorizzazione esplicita del SUPERVISORE</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-611 [P]</t>
+          <t>H-202, H-204 [P]</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
@@ -8500,12 +8554,12 @@
       </c>
       <c r="T47" s="10" t="inlineStr">
         <is>
-          <t>T-804</t>
+          <t>T-803</t>
         </is>
       </c>
       <c r="U47" s="10" t="inlineStr">
         <is>
-          <t>H-611, H-803</t>
+          <t>H-202, H-204</t>
         </is>
       </c>
       <c r="V47" s="10" t="inlineStr">
@@ -8515,42 +8569,40 @@
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>8b</t>
-        </is>
+      <c r="A48" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="B48" s="9" t="n">
         <v>66</v>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-804</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>`api/` loopback e hardening</t>
+          <t>Accesso agenti alla KB</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b01…T-8b04</t>
+          <t>**Fase 8.** T-804</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
+          <t>Solo MCP/CLI in sola lettura, eventi registrati, degrado senza contesto</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401 [P]</t>
+          <t>H-803, H-611 [P]</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -8591,17 +8643,17 @@
       </c>
       <c r="T48" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04</t>
+          <t>T-804</t>
         </is>
       </c>
       <c r="U48" s="10" t="inlineStr">
         <is>
-          <t>H-303, H-401</t>
+          <t>H-611, H-803</t>
         </is>
       </c>
       <c r="V48" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8668,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -8626,22 +8678,22 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Read model derivato</t>
+          <t>`api/` loopback e hardening</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b05</t>
+          <t>**Fase 8b.** T-8b01…T-8b04</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Cache rigenerabile, fonte unica (C27)</t>
+          <t>Token, Host/Origin, CSRF, CSP, limite body</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-303, H-401 [P]</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -8682,12 +8734,12 @@
       </c>
       <c r="T49" s="10" t="inlineStr">
         <is>
-          <t>T-8b05</t>
+          <t>T-8b01, T-8b04</t>
         </is>
       </c>
       <c r="U49" s="10" t="inlineStr">
         <is>
-          <t>H-8b01</t>
+          <t>H-303, H-401</t>
         </is>
       </c>
       <c r="V49" s="10" t="inlineStr">
@@ -8707,7 +8759,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>H-8b05</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -8717,22 +8769,22 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>Gate solo da sessione umana</t>
+          <t>Read model derivato</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
+          <t>**Fase 8b.** T-8b05</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git</t>
+          <t>Cache rigenerabile, fonte unica (C27)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-403</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -8773,12 +8825,12 @@
       </c>
       <c r="T50" s="10" t="inlineStr">
         <is>
-          <t>T-8b08</t>
+          <t>T-8b05</t>
         </is>
       </c>
       <c r="U50" s="10" t="inlineStr">
         <is>
-          <t>H-403, H-8b01</t>
+          <t>H-8b01</t>
         </is>
       </c>
       <c r="V50" s="10" t="inlineStr">
@@ -8798,32 +8850,32 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-8b05</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>`ui/` viste</t>
+          <t>Gate solo da sessione umana</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b06</t>
+          <t>**Fase 8b.** T-8b08 (C23–C24)</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
+          <t>La UI non esegue build/test/git</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-8b01, H-403</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -8837,7 +8889,7 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr"/>
@@ -8864,17 +8916,17 @@
       </c>
       <c r="T51" s="10" t="inlineStr">
         <is>
-          <t>T-8b06</t>
+          <t>T-8b08</t>
         </is>
       </c>
       <c r="U51" s="10" t="inlineStr">
         <is>
-          <t>H-8b02</t>
+          <t>H-403, H-8b01</t>
         </is>
       </c>
       <c r="V51" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8941,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>H-8b04</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -8899,22 +8951,22 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Vista Permessi agenti</t>
+          <t>`ui/` viste</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-405, T-8b07</t>
+          <t>**Fase 8b.** T-8b06</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Conferma, motivazione, audit, rollback</t>
+          <t>Portfolio, LIMET, HELIOS, CEREBRO, Criticità</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -8955,12 +9007,12 @@
       </c>
       <c r="T52" s="10" t="inlineStr">
         <is>
-          <t>T-405, T-8b07</t>
+          <t>T-8b06</t>
         </is>
       </c>
       <c r="U52" s="10" t="inlineStr">
         <is>
-          <t>H-404, H-8b03</t>
+          <t>H-8b02</t>
         </is>
       </c>
       <c r="V52" s="10" t="inlineStr">
@@ -8980,7 +9032,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>H-8b06</t>
+          <t>H-8b04</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -8990,22 +9042,22 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Grafica e accessibilità</t>
+          <t>Vista Permessi agenti</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b09</t>
+          <t>**Fase 8b.** T-405, T-8b07</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
+          <t>Conferma, motivazione, audit, rollback</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
@@ -9046,12 +9098,12 @@
       </c>
       <c r="T53" s="10" t="inlineStr">
         <is>
-          <t>T-8b09</t>
+          <t>T-405, T-8b07</t>
         </is>
       </c>
       <c r="U53" s="10" t="inlineStr">
         <is>
-          <t>H-8b03</t>
+          <t>H-404, H-8b03</t>
         </is>
       </c>
       <c r="V53" s="10" t="inlineStr">
@@ -9071,7 +9123,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>H-8b07</t>
+          <t>H-8b06</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -9081,17 +9133,17 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Governance dipendenze npm</t>
+          <t>Grafica e accessibilità</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-8b10</t>
+          <t>**Fase 8b.** T-8b09</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Lockfile, licenze, audit, SBOM (C25)</t>
+          <t>SVG/Canvas, WCAG 2.1 AA, budget prestazioni (C26)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -9137,7 +9189,7 @@
       </c>
       <c r="T54" s="10" t="inlineStr">
         <is>
-          <t>T-8b10</t>
+          <t>T-8b09</t>
         </is>
       </c>
       <c r="U54" s="10" t="inlineStr">
@@ -9162,7 +9214,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>H-8b08</t>
+          <t>H-8b07</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -9172,22 +9224,22 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Sostituzione launcher :8799</t>
+          <t>Governance dipendenze npm</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** T-304</t>
+          <t>**Fase 8b.** T-8b10</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Tramite shim</t>
+          <t>Lockfile, licenze, audit, SBOM (C25)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
@@ -9228,12 +9280,12 @@
       </c>
       <c r="T55" s="10" t="inlineStr">
         <is>
-          <t>T-304</t>
+          <t>T-8b10</t>
         </is>
       </c>
       <c r="U55" s="10" t="inlineStr">
         <is>
-          <t>H-304, H-8b03</t>
+          <t>H-8b03</t>
         </is>
       </c>
       <c r="V55" s="10" t="inlineStr">
@@ -9253,32 +9305,32 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b08</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>Sostituzione launcher :8799</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
+          <t>**Fase 8b.** T-304</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
+          <t>Tramite shim</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr">
@@ -9311,7 +9363,7 @@
       <c r="Q56" s="10" t="n"/>
       <c r="R56" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
+          <t>Dopo GO</t>
         </is>
       </c>
       <c r="S56" s="12" t="n">
@@ -9319,17 +9371,17 @@
       </c>
       <c r="T56" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-304</t>
         </is>
       </c>
       <c r="U56" s="10" t="inlineStr">
         <is>
-          <t>H-309, H-8b01, H-8b03</t>
+          <t>H-304, H-8b03</t>
         </is>
       </c>
       <c r="V56" s="10" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
     </row>
@@ -9344,32 +9396,32 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Avvio del run non presidiato dalla dashboard</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
+          <t>**Fase 8b.** Front-end del modulo H-309: stato `OK`/`INCOMPLETO`/`NON VALIDO`, dialog pre-compilata dall'autodiscovery, scrittura del file</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
+          <t>Nessuna operazione senza configurazione valida; dialog di prima configurazione</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
@@ -9402,7 +9454,7 @@
       <c r="Q57" s="10" t="n"/>
       <c r="R57" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO. ADR 0003 §9</t>
+          <t>Dopo GO. Richiesta SUPERVISORE 2026-10-30</t>
         </is>
       </c>
       <c r="S57" s="12" t="n">
@@ -9410,55 +9462,57 @@
       </c>
       <c r="T57" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="U57" s="10" t="inlineStr">
         <is>
-          <t>H-713, H-714, H-715, H-8b05</t>
+          <t>H-309, H-8b01, H-8b03</t>
         </is>
       </c>
       <c r="V57" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
-      <c r="A58" s="9" t="n">
-        <v>9</v>
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B58" s="9" t="n">
         <v>76</v>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E ALA V1–V24</t>
+          <t>Avvio del run non presidiato dalla dashboard</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
+          <t>**Fase 8b.** La UI non amplia i permessi (neutralità dei permessi, ADR 0003 §2). T-8b13, E2E-AUT-2</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Catena completa su 3 OS, progetto pilota</t>
+          <t>Perimetro e limiti mostrati **prima** dell'avvio; avvio solo da sessione umana (C24); kill switch raggiungibile durante il run</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
@@ -9472,7 +9526,7 @@
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr"/>
@@ -9491,7 +9545,7 @@
       <c r="Q58" s="10" t="n"/>
       <c r="R58" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. ADR 0003 §9</t>
         </is>
       </c>
       <c r="S58" s="12" t="n">
@@ -9499,55 +9553,57 @@
       </c>
       <c r="T58" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="U58" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-713, H-714, H-715, H-8b05</t>
         </is>
       </c>
       <c r="V58" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
-      <c r="A59" s="9" t="n">
-        <v>9</v>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
       </c>
       <c r="B59" s="9" t="n">
         <v>77</v>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>H-902</t>
+          <t>H-8b11b</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26d</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>README e troubleshooting plugin</t>
+          <t>Pannello di revisione umana del diff</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>**Fase 9.** `agents/plugin/README.md`</t>
+          <t>**Fase 8b.** La UI non può approvare al posto dell'umano né ampliare i permessi. T-8b14, E2E-REV-2</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Installazione, configurazione, errori</t>
+          <t>Mostra diff, findings del `reviewer` e rischio di H-612 **insieme**; approvazione firmata da sessione umana, ancorata allo SHA</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>H-901 [P]</t>
+          <t>H-717, H-8b05</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
@@ -9580,7 +9636,7 @@
       <c r="Q59" s="10" t="n"/>
       <c r="R59" s="10" t="inlineStr">
         <is>
-          <t>Dopo GO</t>
+          <t>Dopo GO. Q-21 (C24)</t>
         </is>
       </c>
       <c r="S59" s="12" t="n">
@@ -9588,55 +9644,55 @@
       </c>
       <c r="T59" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b14</t>
         </is>
       </c>
       <c r="U59" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-717, H-8b05</t>
         </is>
       </c>
       <c r="V59" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md</t>
+          <t>api/ (approvazione firmata con SHA), ui/ (pannello diff + findings + rischio)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B60" s="9" t="n">
         <v>78</v>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>H-1101</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-27</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Manuali, NOTICE, runbook</t>
+          <t>Scenari E2E ALA V1–V24</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>**Fase 11.** Revisione approvata</t>
+          <t>**Fase 9.** `E2E_VERIFICATION.md` (V1–V24)</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Documentazione finale</t>
+          <t>Catena completa su 3 OS, progetto pilota</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>Fasi 5–8</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
@@ -9650,7 +9706,7 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr"/>
@@ -9682,50 +9738,50 @@
       </c>
       <c r="U60" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="V60" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>E2E_VERIFICATION.md</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>79</v>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-902</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-28</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>README e troubleshooting plugin</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+          <t>**Fase 9.** `agents/plugin/README.md`</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Log immutabili, sandbox, SBOM, audit</t>
+          <t>Installazione, configurazione, errori</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-901 [P]</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
@@ -9739,7 +9795,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -9776,45 +9832,45 @@
       </c>
       <c r="V61" s="10" t="inlineStr">
         <is>
-          <t>docs/audit-hardening.md</t>
+          <t>agents/plugin/README.md</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="9" t="n">
         <v>80</v>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>H-1201</t>
+          <t>H-1101</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>PK-30</t>
+          <t>PK-28</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>Rollout sul pilota</t>
+          <t>Manuali, NOTICE, runbook</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>**Fase 12.** Parere legale **[N]**</t>
+          <t>**Fase 11.** Revisione approvata</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Metriche, rollback, parere legale</t>
+          <t>Documentazione finale</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>H-1001, H-1101</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">
@@ -9860,21 +9916,199 @@
       </c>
       <c r="U62" s="10" t="inlineStr">
         <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V62" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
+      <c r="A63" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 10.** Nessun T-xxx in IN §6 **[N]**: verifica = audit a 5 criteri osservabili (definita dall'audit A6), esito in `docs/audit-hardening.md`</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>Log immutabili, sandbox, SBOM, audit</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J63" s="9">
+        <f>IF(I63="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="10" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U63" s="10" t="inlineStr">
+        <is>
+          <t>H-901</t>
+        </is>
+      </c>
+      <c r="V63" s="10" t="inlineStr">
+        <is>
+          <t>docs/audit-hardening.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
+      <c r="A64" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>H-1201</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>PK-30</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Rollout sul pilota</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>**Fase 12.** Parere legale **[N]**</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>Metriche, rollback, parere legale</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
           <t>H-1001, H-1101</t>
         </is>
       </c>
-      <c r="V62" s="10" t="inlineStr">
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Da fare</t>
+        </is>
+      </c>
+      <c r="J64" s="9">
+        <f>IF(I64="Fatto","✔ Sì","✘ No")</f>
+        <v/>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
+      <c r="M64" s="10" t="inlineStr"/>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="inlineStr">
+        <is>
+          <t>Dopo GO</t>
+        </is>
+      </c>
+      <c r="S64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U64" s="10" t="inlineStr">
+        <is>
+          <t>H-1001, H-1101</t>
+        </is>
+      </c>
+      <c r="V64" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V62"/>
+  <autoFilter ref="A4:V64"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:S62">
+  <conditionalFormatting sqref="A5:S64">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($S5=1,$I5&lt;&gt;"Fatto")</formula>
     </cfRule>
@@ -9882,7 +10116,7 @@
       <formula>$I5="Fatto"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I62">
+  <conditionalFormatting sqref="I5:I64">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -9899,7 +10133,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K62">
+  <conditionalFormatting sqref="K5:K64">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
@@ -9910,7 +10144,7 @@
       <formula>"SUPERVISORE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S62">
+  <conditionalFormatting sqref="S5:S64">
     <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -9920,19 +10154,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="I5:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Da fare,In corso,In review,Fatto,Bloccato"</formula1>
     </dataValidation>
-    <dataValidation sqref="K5:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NARO,SCIBETTA,SUPERVISORE,Da assegnare"</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,M,L"</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sì,No,—"</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="S5:S64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -9948,7 +10182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10075,15 +10309,15 @@
         </is>
       </c>
       <c r="E5" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D62,A5)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A5)+COUNTIF('Post-GO'!D5:D64,A5)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A5,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A5,'Post-GO'!I5:I62,"In review")+F5&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A5,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F5=E5,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A5,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A5,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A5,'Post-GO'!I5:I64,"In review")+F5&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -10144,15 +10378,15 @@
         </is>
       </c>
       <c r="E6" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D62,A6)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A6)+COUNTIF('Post-GO'!D5:D64,A6)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A6,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A6,'Post-GO'!I5:I62,"In review")+F6&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A6,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F6=E6,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A6,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A6,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A6,'Post-GO'!I5:I64,"In review")+F6&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -10213,15 +10447,15 @@
         </is>
       </c>
       <c r="E7" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D62,A7)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A7)+COUNTIF('Post-GO'!D5:D64,A7)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A7,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A7,'Post-GO'!I5:I62,"In review")+F7&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A7,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F7=E7,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A7,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A7,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A7,'Post-GO'!I5:I64,"In review")+F7&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -10282,15 +10516,15 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D62,A8)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A8)+COUNTIF('Post-GO'!D5:D64,A8)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A8,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A8,'Post-GO'!I5:I62,"In review")+F8&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A8,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F8=E8,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A8,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A8,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A8,'Post-GO'!I5:I64,"In review")+F8&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -10351,15 +10585,15 @@
         </is>
       </c>
       <c r="E9" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D62,A9)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A9)+COUNTIF('Post-GO'!D5:D64,A9)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A9,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A9,'Post-GO'!I5:I62,"In review")+F9&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A9,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F9=E9,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A9,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A9,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A9,'Post-GO'!I5:I64,"In review")+F9&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -10420,15 +10654,15 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D62,A10)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A10)+COUNTIF('Post-GO'!D5:D64,A10)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A10,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A10,'Post-GO'!I5:I62,"In review")+F10&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A10,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F10=E10,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A10,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A10,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A10,'Post-GO'!I5:I64,"In review")+F10&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -10489,15 +10723,15 @@
         </is>
       </c>
       <c r="E11" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D62,A11)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A11)+COUNTIF('Post-GO'!D5:D64,A11)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A11,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A11,'Post-GO'!I5:I62,"In review")+F11&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A11,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F11=E11,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A11,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A11,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A11,'Post-GO'!I5:I64,"In review")+F11&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -10558,15 +10792,15 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D62,A12)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A12)+COUNTIF('Post-GO'!D5:D64,A12)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A12,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A12,'Post-GO'!I5:I62,"In review")+F12&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A12,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F12=E12,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A12,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A12,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A12,'Post-GO'!I5:I64,"In review")+F12&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -10627,15 +10861,15 @@
         </is>
       </c>
       <c r="E13" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D62,A13)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A13)+COUNTIF('Post-GO'!D5:D64,A13)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A13,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A13,'Post-GO'!I5:I62,"In review")+F13&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A13,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F13=E13,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A13,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A13,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A13,'Post-GO'!I5:I64,"In review")+F13&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -10696,15 +10930,15 @@
         </is>
       </c>
       <c r="E14" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D62,A14)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A14)+COUNTIF('Post-GO'!D5:D64,A14)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A14,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A14,'Post-GO'!I5:I62,"In review")+F14&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A14,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F14=E14,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A14,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A14,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A14,'Post-GO'!I5:I64,"In review")+F14&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -10765,15 +10999,15 @@
         </is>
       </c>
       <c r="E15" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D62,A15)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A15)+COUNTIF('Post-GO'!D5:D64,A15)</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A15,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A15,'Post-GO'!I5:I62,"In review")+F15&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A15,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F15=E15,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A15,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A15,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A15,'Post-GO'!I5:I64,"In review")+F15&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -10834,15 +11068,15 @@
         </is>
       </c>
       <c r="E16" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D62,A16)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A16)+COUNTIF('Post-GO'!D5:D64,A16)</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A16,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A16,'Post-GO'!I5:I62,"In review")+F16&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A16,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F16=E16,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A16,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A16,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A16,'Post-GO'!I5:I64,"In review")+F16&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -10903,15 +11137,15 @@
         </is>
       </c>
       <c r="E17" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D62,A17)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A17)+COUNTIF('Post-GO'!D5:D64,A17)</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A17,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A17,'Post-GO'!I5:I62,"In review")+F17&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A17,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F17=E17,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A17,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A17,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A17,'Post-GO'!I5:I64,"In review")+F17&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -10972,15 +11206,15 @@
         </is>
       </c>
       <c r="E18" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D62,A18)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A18)+COUNTIF('Post-GO'!D5:D64,A18)</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A18,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A18,'Post-GO'!I5:I62,"In review")+F18&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A18,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F18=E18,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A18,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A18,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A18,'Post-GO'!I5:I64,"In review")+F18&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -11041,15 +11275,15 @@
         </is>
       </c>
       <c r="E19" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D62,A19)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A19)+COUNTIF('Post-GO'!D5:D64,A19)</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A19,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A19,'Post-GO'!I5:I62,"In review")+F19&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A19,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F19=E19,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A19,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A19,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A19,'Post-GO'!I5:I64,"In review")+F19&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -11110,15 +11344,15 @@
         </is>
       </c>
       <c r="E20" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D62,A20)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A20)+COUNTIF('Post-GO'!D5:D64,A20)</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A20,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A20,'Post-GO'!I5:I62,"In review")+F20&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A20,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F20=E20,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A20,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A20,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A20,'Post-GO'!I5:I64,"In review")+F20&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -11179,15 +11413,15 @@
         </is>
       </c>
       <c r="E21" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D62,A21)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A21)+COUNTIF('Post-GO'!D5:D64,A21)</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A21,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G21" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A21,'Post-GO'!I5:I62,"In review")+F21&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A21,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F21=E21,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A21,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A21,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A21,'Post-GO'!I5:I64,"In review")+F21&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -11248,15 +11482,15 @@
         </is>
       </c>
       <c r="E22" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D62,A22)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A22)+COUNTIF('Post-GO'!D5:D64,A22)</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A22,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G22" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A22,'Post-GO'!I5:I62,"In review")+F22&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A22,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F22=E22,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A22,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A22,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A22,'Post-GO'!I5:I64,"In review")+F22&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -11317,15 +11551,15 @@
         </is>
       </c>
       <c r="E23" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D62,A23)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A23)+COUNTIF('Post-GO'!D5:D64,A23)</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A23,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G23" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A23,'Post-GO'!I5:I62,"In review")+F23&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A23,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F23=E23,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A23,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A23,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A23,'Post-GO'!I5:I64,"In review")+F23&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -11386,15 +11620,15 @@
         </is>
       </c>
       <c r="E24" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D62,A24)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A24)+COUNTIF('Post-GO'!D5:D64,A24)</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A24,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A24,'Post-GO'!I5:I62,"In review")+F24&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A24,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F24=E24,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A24,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A24,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A24,'Post-GO'!I5:I64,"In review")+F24&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -11455,15 +11689,15 @@
         </is>
       </c>
       <c r="E25" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D62,A25)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A25)+COUNTIF('Post-GO'!D5:D64,A25)</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A25,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A25,'Post-GO'!I5:I62,"In review")+F25&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A25,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F25=E25,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A25,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A25,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A25,'Post-GO'!I5:I64,"In review")+F25&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -11524,15 +11758,15 @@
         </is>
       </c>
       <c r="E26" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D62,A26)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A26)+COUNTIF('Post-GO'!D5:D64,A26)</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A26,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A26,'Post-GO'!I5:I62,"In review")+F26&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A26,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F26=E26,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A26,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A26,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A26,'Post-GO'!I5:I64,"In review")+F26&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -11593,15 +11827,15 @@
         </is>
       </c>
       <c r="E27" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D62,A27)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A27)+COUNTIF('Post-GO'!D5:D64,A27)</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A27,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A27,'Post-GO'!I5:I62,"In review")+F27&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A27,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F27=E27,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A27,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A27,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A27,'Post-GO'!I5:I64,"In review")+F27&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -11662,15 +11896,15 @@
         </is>
       </c>
       <c r="E28" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D62,A28)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A28)+COUNTIF('Post-GO'!D5:D64,A28)</f>
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A28,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G28" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A28,'Post-GO'!I5:I62,"In review")+F28&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A28,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F28=E28,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A28,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A28,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A28,'Post-GO'!I5:I64,"In review")+F28&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -11731,15 +11965,15 @@
         </is>
       </c>
       <c r="E29" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D62,A29)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A29)+COUNTIF('Post-GO'!D5:D64,A29)</f>
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A29,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G29" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A29,'Post-GO'!I5:I62,"In review")+F29&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A29,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F29=E29,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A29,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A29,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A29,'Post-GO'!I5:I64,"In review")+F29&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -11800,15 +12034,15 @@
         </is>
       </c>
       <c r="E30" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D62,A30)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A30)+COUNTIF('Post-GO'!D5:D64,A30)</f>
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A30,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G30" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A30,'Post-GO'!I5:I62,"In review")+F30&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A30,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F30=E30,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A30,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A30,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A30,'Post-GO'!I5:I64,"In review")+F30&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -11869,15 +12103,15 @@
         </is>
       </c>
       <c r="E31" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D62,A31)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A31)+COUNTIF('Post-GO'!D5:D64,A31)</f>
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A31,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G31" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A31,'Post-GO'!I5:I62,"In review")+F31&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A31,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F31=E31,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A31,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A31,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A31,'Post-GO'!I5:I64,"In review")+F31&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -11938,15 +12172,15 @@
         </is>
       </c>
       <c r="E32" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D62,A32)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A32)+COUNTIF('Post-GO'!D5:D64,A32)</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A32,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G32" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A32,'Post-GO'!I5:I62,"In review")+F32&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A32,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F32=E32,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A32,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A32,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A32,'Post-GO'!I5:I64,"In review")+F32&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -11988,103 +12222,103 @@
     <row r="33" ht="62" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-19d</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Valutazione rischi di prodotto (C28)</t>
+          <t>Revisione umana obbligatoria del diff (gate)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>H-612</t>
+          <t>H-717</t>
         </is>
       </c>
       <c r="E33" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D62,A33)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A33)+COUNTIF('Post-GO'!D5:D64,A33)</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A33,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G33" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A33,'Post-GO'!I5:I62,"In review")+F33&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A33,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F33=E33,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A33,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A33,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A33,'Post-GO'!I5:I64,"In review")+F33&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>S9d</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>T-611</t>
+          <t>T-717</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
+          <t>agents/plugin/ (gate di merge: percorsi sensibili, rischio alto, firma su SHA), agents/policy/ (lista percorsi sensibili)</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
+          <t>PK-19c (H-716), PK-20 (H-706, H-711), PK-21 (H-612)</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>PK-23, PK-24, PK-25</t>
+          <t>PK-26d</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>risk-assessor ≠ developer, sola lettura.</t>
+          <t>Q-21. Nessun timeout che approva; approvazione ancorata allo SHA (decade se il ramo avanza, come R15). Stessi file di PK-19/PK-19c: stessa persona. Verifica: T-717, E2E-REV-2.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="62" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>PK-22</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Onda 5 (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Installer e modifiche documentali a LIMET</t>
+          <t>Valutazione rischi di prodotto (C28)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>H-702, H-712</t>
+          <t>H-612</t>
         </is>
       </c>
       <c r="E34" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D62,A34)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A34)+COUNTIF('Post-GO'!D5:D64,A34)</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A34,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G34" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A34,'Post-GO'!I5:I62,"In review")+F34&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A34,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F34=E34,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A34,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A34,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A34,'Post-GO'!I5:I64,"In review")+F34&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -12094,135 +12328,135 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>T-702, T-712</t>
+          <t>T-611</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
+          <t>agents/plugin/agents/risk-assessor.md, RISK-&lt;task&gt;.json</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
+          <t>PK-19 (H-701), PK-20 (H-706), H-308</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>PK-19</t>
+          <t>PK-23, PK-24, PK-25</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
+          <t>risk-assessor ≠ developer, sola lettura.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="62" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PK-23</t>
+          <t>PK-22</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 5 (dopo GO)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Hook ECC e registro chiamate LLM</t>
+          <t>Installer e modifiche documentali a LIMET</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>H-800, H-800b, H-801, H-802</t>
+          <t>H-702, H-712</t>
         </is>
       </c>
       <c r="E35" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D62,A35)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A35)+COUNTIF('Post-GO'!D5:D64,A35)</f>
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A35,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G35" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A35,'Post-GO'!I5:I62,"In review")+F35&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A35,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F35=E35,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A35,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A35,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A35,'Post-GO'!I5:I64,"In review")+F35&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>T-801, T-802</t>
+          <t>T-702, T-712</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
+          <t>scripts/limet-agents.ps1/.sh, limet/ (documentazione) [P]</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-08</t>
+          <t>H-407; H-712 dopo H-407 (ALA §7)</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>PK-14…PK-22</t>
+          <t>PK-19</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
+          <t>Ciclo LIMET IT/EN; re-index a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="62" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>PK-24</t>
+          <t>PK-23</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Onda 6 (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Knowledge base HLS_* e accesso agenti</t>
+          <t>Hook ECC e registro chiamate LLM</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>H-803, H-804</t>
+          <t>H-800, H-800b, H-801, H-802</t>
         </is>
       </c>
       <c r="E36" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D62,A36)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A36)+COUNTIF('Post-GO'!D5:D64,A36)</f>
         <v/>
       </c>
       <c r="F36" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A36,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G36" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A36,'Post-GO'!I5:I62,"In review")+F36&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A36,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F36=E36,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A36,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A36,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A36,'Post-GO'!I5:I64,"In review")+F36&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -12232,66 +12466,66 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>T-803, T-804</t>
+          <t>T-801, T-802</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>[N] script KB / MCP in sola lettura</t>
+          <t>docs/ecc-hooks-analysis.md, agents/policy/llm-registry.json, [N] wrapper AgentShield</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>PK-03, PK-15</t>
+          <t>GO; PK-08</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>PK-21</t>
+          <t>PK-14…PK-22</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
+          <t>H-800 anticipabile in Fase 2 (IN §5). [N] Q-10 licenze AgentShield.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="62" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PK-25</t>
+          <t>PK-24</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Onda 3+ (dopo GO)</t>
+          <t>Onda 6 (dopo GO)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>API loopback e read model</t>
+          <t>Knowledge base HLS_* e accesso agenti</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>H-8b01, H-8b02, H-8b05</t>
+          <t>H-803, H-804</t>
         </is>
       </c>
       <c r="E37" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D62,A37)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A37)+COUNTIF('Post-GO'!D5:D64,A37)</f>
         <v/>
       </c>
       <c r="F37" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A37,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G37" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A37,'Post-GO'!I5:I62,"In review")+F37&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A37,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F37=E37,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A37,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A37,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A37,'Post-GO'!I5:I64,"In review")+F37&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -12301,108 +12535,108 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
+          <t>T-803, T-804</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>api/</t>
+          <t>[N] script KB / MCP in sola lettura</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>GO; PK-06, PK-08</t>
+          <t>PK-03, PK-15</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>PK-26 (dopo contratto API)</t>
+          <t>PK-21</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
+          <t>HLS_* creata solo con autorizzazione esplicita (Q9); mai su collection esistenti.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="62" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>PK-26</t>
+          <t>PK-25</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Onda 4+ (dopo GO)</t>
+          <t>Onda 3+ (dopo GO)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
+          <t>API loopback e read model</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
+          <t>H-8b01, H-8b02, H-8b05</t>
         </is>
       </c>
       <c r="E38" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D62,A38)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A38)+COUNTIF('Post-GO'!D5:D64,A38)</f>
         <v/>
       </c>
       <c r="F38" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A38,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G38" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A38,'Post-GO'!I5:I62,"In review")+F38&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A38,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F38=E38,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A38,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A38,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A38,'Post-GO'!I5:I64,"In review")+F38&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>NARO</t>
+          <t>SCIBETTA</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>N13</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
+          <t>T-8b01, T-8b04, T-8b05, T-8b08</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>ui/, [N] shim launcher :8799</t>
+          <t>api/</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>PK-25, PK-08, PK-06</t>
+          <t>GO; PK-06, PK-08</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>PK-25 (dopo contratto API)</t>
+          <t>PK-26 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>La UI non esegue build/test/git (C23–C24).</t>
+          <t>Contatto: contratto API/OpenAPI di H-8b01 da congelare prima di PK-26.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="62" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PK-26b</t>
+          <t>PK-26</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -12412,24 +12646,24 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Gate di configurazione all'avvio della dashboard</t>
+          <t>UI (viste, permessi, grafica, npm) e sostituzione launcher</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>H-8b09</t>
+          <t>H-8b03, H-8b04, H-8b06, H-8b07, H-8b08</t>
         </is>
       </c>
       <c r="E39" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D62,A39)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A39)+COUNTIF('Post-GO'!D5:D64,A39)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A39,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A39,'Post-GO'!I5:I62,"In review")+F39&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A39,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F39=E39,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A39,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A39,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A39,'Post-GO'!I5:I64,"In review")+F39&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -12439,66 +12673,66 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>N13b</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>T-8b11</t>
+          <t>T-8b06, T-405, T-8b07, T-8b09, T-8b10, T-304</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
+          <t>ui/, [N] shim launcher :8799</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
+          <t>PK-25, PK-08, PK-06</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PK-25 (dopo contratto API)</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
+          <t>La UI non esegue build/test/git (C23–C24).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="62" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>PK-26c</t>
+          <t>PK-26b</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Onda 5+ (dopo GO)</t>
+          <t>Onda 4+ (dopo GO)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Pannello di avvio del run non presidiato</t>
+          <t>Gate di configurazione all'avvio della dashboard</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>H-8b10</t>
+          <t>H-8b09</t>
         </is>
       </c>
       <c r="E40" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D62,A40)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A40)+COUNTIF('Post-GO'!D5:D64,A40)</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A40,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A40,'Post-GO'!I5:I62,"In review")+F40&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A40,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F40=E40,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A40,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A40,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A40,'Post-GO'!I5:I64,"In review")+F40&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -12508,22 +12742,22 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>N13c</t>
+          <t>N13b</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>T-8b13, T-2</t>
+          <t>T-8b11</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
+          <t>api/ (gate), ui/ (dialog di prima configurazione)</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
+          <t>PK-07b (H-309), PK-25 (H-8b01), PK-26 (H-8b03)</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -12533,110 +12767,110 @@
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
+          <t>Il gate chiama il modulo di H-309: nessuna logica duplicata. Non aggirabile da chiamata diretta all'API (C23). Verifica: T-8b11, T-8b12, E2E-CFG-1.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="62" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-26c</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Scenari E2E V1–V24</t>
+          <t>Pannello di avvio del run non presidiato</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>H-901</t>
+          <t>H-8b10</t>
         </is>
       </c>
       <c r="E41" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D62,A41)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A41)+COUNTIF('Post-GO'!D5:D64,A41)</f>
         <v/>
       </c>
       <c r="F41" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A41,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G41" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A41,'Post-GO'!I5:I62,"In review")+F41&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A41,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F41=E41,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A41,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A41,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A41,'Post-GO'!I5:I64,"In review")+F41&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>SCIBETTA</t>
+          <t>NARO</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>N13c</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b13, T-2</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
+          <t>api/ (avvio run non presidiato), ui/ (pannello perimetro, limiti, kill switch)</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>Fasi 5–8</t>
+          <t>PK-19b (H-713), PK-20b (H-714), PK-26 (H-8b03), PK-26b (H-8b09)</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
+          <t>C24: il run non presidiato lo avvia SEMPRE una sessione umana. Mostra perimetro e limiti prima dell'avvio; kill switch raggiungibile a run in corso. Verifica: T-8b13, E2E-AUT-2.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="62" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>PK-28</t>
+          <t>PK-26d</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Onda 7 (dopo GO)</t>
+          <t>Onda 5+ (dopo GO)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>README plugin e manuali</t>
+          <t>Pannello di revisione umana del diff</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>H-902, H-1101</t>
+          <t>H-8b11b</t>
         </is>
       </c>
       <c r="E42" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A42)+COUNTIF('Post-GO'!D5:D62,A42)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A42)+COUNTIF('Post-GO'!D5:D64,A42)</f>
         <v/>
       </c>
       <c r="F42" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A42,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G42" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F42=E42,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A42,'Post-GO'!I5:I62,"In review")+F42&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A42,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F42=E42,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A42,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A42,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A42,'Post-GO'!I5:I64,"In review")+F42&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -12646,66 +12880,66 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>N14</t>
+          <t>N13d</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-8b14</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+          <t>api/ (approvazione firmata con SHA), ui/ (pannello diff + findings + rischio)</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>PK-19d (H-717), PK-26 (H-8b05)</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>Revisione approvata dal SUPERVISORE.</t>
+          <t>Q-21 / C24: approva SEMPRE una sessione umana. Diff, findings con severita e rischio nella stessa vista; firma ancorata allo SHA mostrato. Verifica: T-8b14, E2E-REV-2.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="62" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PK-29</t>
+          <t>PK-27</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Onda 8 (dopo GO)</t>
+          <t>Onda 7 (dopo GO)</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Hardening</t>
+          <t>Scenari E2E V1–V24</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>H-1001</t>
+          <t>H-901</t>
         </is>
       </c>
       <c r="E43" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A43)+COUNTIF('Post-GO'!D5:D62,A43)</f>
+        <f>COUNTIF('Pre-GO'!D5:D26,A43)+COUNTIF('Post-GO'!D5:D64,A43)</f>
         <v/>
       </c>
       <c r="F43" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"Fatto")</f>
+        <f>COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A43,'Post-GO'!I5:I64,"Fatto")</f>
         <v/>
       </c>
       <c r="G43" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F43=E43,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A43,'Post-GO'!I5:I62,"In review")+F43&gt;0,"In corso","Da fare")))</f>
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A43,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F43=E43,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A43,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A43,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A43,'Post-GO'!I5:I64,"In review")+F43&gt;0,"In corso","Da fare")))</f>
         <v/>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -12715,7 +12949,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
@@ -12725,12 +12959,12 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>[N] log immutabili, sandbox, SBOM</t>
+          <t>E2E_VERIFICATION.md, [N] repo pilota test\</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>PK-27</t>
+          <t>Fasi 5–8</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
@@ -12740,86 +12974,224 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+          <t>Esecuzione su 3 OS a cura del SUPERVISORE.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="62" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Onda 7 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>README plugin e manuali</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>H-902, H-1101</t>
+        </is>
+      </c>
+      <c r="E44" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A44)+COUNTIF('Post-GO'!D5:D64,A44)</f>
+        <v/>
+      </c>
+      <c r="F44" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A44,'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G44" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A44,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F44=E44,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A44,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A44,'Post-GO'!I5:I64,"In review")+F44&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>NARO</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>N14</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>agents/plugin/README.md, docs/ (manuali, NOTICE, runbook)</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>Revisione approvata dal SUPERVISORE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>PK-29</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Onda 8 (dopo GO)</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Hardening</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>H-1001</t>
+        </is>
+      </c>
+      <c r="E45" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A45)+COUNTIF('Post-GO'!D5:D64,A45)</f>
+        <v/>
+      </c>
+      <c r="F45" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A45,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A45,'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G45" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A45,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A45,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F45=E45,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A45,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A45,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A45,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A45,'Post-GO'!I5:I64,"In review")+F45&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>SCIBETTA</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>[N] log immutabili, sandbox, SBOM</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>PK-27</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>PK-28</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>[N] nessun T-xxx in IN §6: verifica = audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="62" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>PK-30</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Onda 9 (dopo GO)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Rollout sul pilota</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>H-1201</t>
         </is>
       </c>
-      <c r="E44" s="9">
-        <f>COUNTIF('Pre-GO'!D5:D26,A44)+COUNTIF('Post-GO'!D5:D62,A44)</f>
-        <v/>
-      </c>
-      <c r="F44" s="9">
-        <f>COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"Fatto")</f>
-        <v/>
-      </c>
-      <c r="G44" s="9">
-        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"Bloccato")&gt;0,"Bloccato",IF(F44=E44,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A44,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D62,A44,'Post-GO'!I5:I62,"In review")+F44&gt;0,"In corso","Da fare")))</f>
-        <v/>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="E46" s="9">
+        <f>COUNTIF('Pre-GO'!D5:D26,A46)+COUNTIF('Post-GO'!D5:D64,A46)</f>
+        <v/>
+      </c>
+      <c r="F46" s="9">
+        <f>COUNTIFS('Pre-GO'!D5:D26,A46,'Pre-GO'!I5:I26,"Fatto")+COUNTIFS('Post-GO'!D5:D64,A46,'Post-GO'!I5:I64,"Fatto")</f>
+        <v/>
+      </c>
+      <c r="G46" s="9">
+        <f>IF(COUNTIFS('Pre-GO'!D5:D26,A46,'Pre-GO'!I5:I26,"Bloccato")+COUNTIFS('Post-GO'!D5:D64,A46,'Post-GO'!I5:I64,"Bloccato")&gt;0,"Bloccato",IF(F46=E46,"Fatto",IF(COUNTIFS('Pre-GO'!D5:D26,A46,'Pre-GO'!I5:I26,"In corso")+COUNTIFS('Post-GO'!D5:D64,A46,'Post-GO'!I5:I64,"In corso")+COUNTIFS('Pre-GO'!D5:D26,A46,'Pre-GO'!I5:I26,"In review")+COUNTIFS('Post-GO'!D5:D64,A46,'Post-GO'!I5:I64,"In review")+F46&gt;0,"In corso","Da fare")))</f>
+        <v/>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>NARO</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>N15</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>docs/ (metriche, rollback)</t>
         </is>
       </c>
-      <c r="L44" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>PK-28, PK-29</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>[N] parere legale; pilota da scegliere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N44"/>
+  <autoFilter ref="A4:N46"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G44">
+  <conditionalFormatting sqref="G5:G46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"Fatto"</formula>
     </cfRule>
@@ -12833,7 +13205,7 @@
       <formula>"Da fare"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H44">
+  <conditionalFormatting sqref="H5:H46">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="7">
       <formula>"NARO"</formula>
     </cfRule>
